--- a/Project_CNN/Main/Results/Experimento 15 - ResNet/training_metrics.xlsx
+++ b/Project_CNN/Main/Results/Experimento 15 - ResNet/training_metrics.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\marci_wawp\Desktop\Arquivos\Mestrado\Projeto-Classificadores\Project_CNN\Main\Results\Experimento 15 - ResNet\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1BE7B7B6-105F-4A7D-AA98-0E3A1CB4387B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{334D4FF6-D8E0-4E93-A344-34FA4E59A802}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -13635,6 +13635,6989 @@
 </c:chartSpace>
 </file>
 
+<file path=xl/charts/chart6.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="pt-BR"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="pt-BR" sz="1600" b="0" baseline="0"/>
+              <a:t>Accuracy curve: ResNet-34, Batch size = 32</a:t>
+            </a:r>
+            <a:endParaRPr lang="pt-BR" sz="1600" b="0"/>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="pt-BR"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:scatterChart>
+        <c:scatterStyle val="smoothMarker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Worksheet!$B$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>accuracy</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:yVal>
+            <c:numRef>
+              <c:f>Worksheet!$B$2:$B$504</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="503"/>
+                <c:pt idx="0">
+                  <c:v>0.44797688722610002</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.45263537764549</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.45281651616096003</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.45245426893233998</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.46187284588813998</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.46576708555222002</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0.46513313055038003</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0.46884623169898998</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0.48052889108657998</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0.49329832196236001</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>0.49728310108184998</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>0.50932800769805997</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>0.51602971553802002</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>0.52354645729064997</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>0.55805104970931996</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>0.58205032348633001</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>0.58621627092360995</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>0.59817063808440996</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>0.59798949956893999</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>0.60414779186249001</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>0.61175513267517001</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>0.62597358226776001</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>0.62814706563949996</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>0.64526355266571001</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>0.65214633941650002</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>0.65812355279921997</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>0.66998732089996005</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>0.67931532859802002</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>0.68809998035430997</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>0.69308096170425004</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>0.72052162885666005</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>0.74107950925827004</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>0.75004529953002996</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>0.75022643804550004</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>0.74823403358458995</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>0.75611305236815995</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>0.75674694776535001</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>0.76344865560532005</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>0.76136571168900002</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>0.76516938209534002</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>0.76453542709350997</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>0.76625609397887995</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>0.76553159952163996</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>0.77268612384795998</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>0.77096539735794001</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>0.77250498533249001</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>0.77449738979339999</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>0.78174245357512995</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>0.77802932262420998</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>0.78509330749511996</c:v>
+                </c:pt>
+                <c:pt idx="50">
+                  <c:v>0.77956891059875</c:v>
+                </c:pt>
+                <c:pt idx="51">
+                  <c:v>0.77993118762970004</c:v>
+                </c:pt>
+                <c:pt idx="52">
+                  <c:v>0.78808188438416005</c:v>
+                </c:pt>
+                <c:pt idx="53">
+                  <c:v>0.79242891073226995</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>0.78255748748778997</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>0.78409707546233998</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>0.79125159978866999</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>0.79288172721863004</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>0.78817242383956998</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>0.79215723276137995</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>0.80329650640488004</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>0.80809634923935003</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>0.81017929315567005</c:v>
+                </c:pt>
+                <c:pt idx="63">
+                  <c:v>0.81036043167114002</c:v>
+                </c:pt>
+                <c:pt idx="64">
+                  <c:v>0.81262451410294001</c:v>
+                </c:pt>
+                <c:pt idx="65">
+                  <c:v>0.81099438667296997</c:v>
+                </c:pt>
+                <c:pt idx="66">
+                  <c:v>0.80836802721024004</c:v>
+                </c:pt>
+                <c:pt idx="67">
+                  <c:v>0.81045103073119995</c:v>
+                </c:pt>
+                <c:pt idx="68">
+                  <c:v>0.81552255153655995</c:v>
+                </c:pt>
+                <c:pt idx="69">
+                  <c:v>0.81724327802658003</c:v>
+                </c:pt>
+                <c:pt idx="70">
+                  <c:v>0.81280565261840998</c:v>
+                </c:pt>
+                <c:pt idx="71">
+                  <c:v>0.81878280639648005</c:v>
+                </c:pt>
+                <c:pt idx="72">
+                  <c:v>0.81697154045105003</c:v>
+                </c:pt>
+                <c:pt idx="73">
+                  <c:v>0.81190001964569003</c:v>
+                </c:pt>
+                <c:pt idx="74">
+                  <c:v>0.81316792964935003</c:v>
+                </c:pt>
+                <c:pt idx="75">
+                  <c:v>0.81679046154021995</c:v>
+                </c:pt>
+                <c:pt idx="76">
+                  <c:v>0.81180948019027999</c:v>
+                </c:pt>
+                <c:pt idx="77">
+                  <c:v>0.81724327802658003</c:v>
+                </c:pt>
+                <c:pt idx="78">
+                  <c:v>0.8108132481575</c:v>
+                </c:pt>
+                <c:pt idx="79">
+                  <c:v>0.81597536802292003</c:v>
+                </c:pt>
+                <c:pt idx="80">
+                  <c:v>0.81679046154021995</c:v>
+                </c:pt>
+                <c:pt idx="81">
+                  <c:v>0.81787717342376998</c:v>
+                </c:pt>
+                <c:pt idx="82">
+                  <c:v>0.8158848285675</c:v>
+                </c:pt>
+                <c:pt idx="83">
+                  <c:v>0.81416410207748002</c:v>
+                </c:pt>
+                <c:pt idx="84">
+                  <c:v>0.82240533828734996</c:v>
+                </c:pt>
+                <c:pt idx="85">
+                  <c:v>0.81679046154021995</c:v>
+                </c:pt>
+                <c:pt idx="86">
+                  <c:v>0.81805831193923995</c:v>
+                </c:pt>
+                <c:pt idx="87">
+                  <c:v>0.81769609451294001</c:v>
+                </c:pt>
+                <c:pt idx="88">
+                  <c:v>0.81715267896652</c:v>
+                </c:pt>
+                <c:pt idx="89">
+                  <c:v>0.82204312086105003</c:v>
+                </c:pt>
+                <c:pt idx="90">
+                  <c:v>0.81742435693741</c:v>
+                </c:pt>
+                <c:pt idx="91">
+                  <c:v>0.81706213951110995</c:v>
+                </c:pt>
+                <c:pt idx="92">
+                  <c:v>0.82122802734375</c:v>
+                </c:pt>
+                <c:pt idx="93">
+                  <c:v>0.81932622194289995</c:v>
+                </c:pt>
+                <c:pt idx="94">
+                  <c:v>0.81914508342742998</c:v>
+                </c:pt>
+                <c:pt idx="95">
+                  <c:v>0.81552255153655995</c:v>
+                </c:pt>
+                <c:pt idx="96">
+                  <c:v>0.82349210977553999</c:v>
+                </c:pt>
+                <c:pt idx="97">
+                  <c:v>0.82312989234924006</c:v>
+                </c:pt>
+                <c:pt idx="98">
+                  <c:v>0.82258647680283004</c:v>
+                </c:pt>
+                <c:pt idx="99">
+                  <c:v>0.82874476909636996</c:v>
+                </c:pt>
+                <c:pt idx="100">
+                  <c:v>0.82394492626189997</c:v>
+                </c:pt>
+                <c:pt idx="101">
+                  <c:v>0.82177144289017001</c:v>
+                </c:pt>
+                <c:pt idx="102">
+                  <c:v>0.82684296369553001</c:v>
+                </c:pt>
+                <c:pt idx="103">
+                  <c:v>0.82140916585921997</c:v>
+                </c:pt>
+                <c:pt idx="104">
+                  <c:v>0.82285815477371005</c:v>
+                </c:pt>
+                <c:pt idx="105">
+                  <c:v>0.82149970531464001</c:v>
+                </c:pt>
+                <c:pt idx="106">
+                  <c:v>0.82711464166641002</c:v>
+                </c:pt>
+                <c:pt idx="107">
+                  <c:v>0.82485055923462003</c:v>
+                </c:pt>
+                <c:pt idx="108">
+                  <c:v>0.82684296369553001</c:v>
+                </c:pt>
+                <c:pt idx="109">
+                  <c:v>0.82050353288651001</c:v>
+                </c:pt>
+                <c:pt idx="110">
+                  <c:v>0.82530337572098</c:v>
+                </c:pt>
+                <c:pt idx="111">
+                  <c:v>0.82666182518005005</c:v>
+                </c:pt>
+                <c:pt idx="112">
+                  <c:v>0.82068467140197998</c:v>
+                </c:pt>
+                <c:pt idx="113">
+                  <c:v>0.82802027463912997</c:v>
+                </c:pt>
+                <c:pt idx="114">
+                  <c:v>0.82548451423644997</c:v>
+                </c:pt>
+                <c:pt idx="115">
+                  <c:v>0.82657128572464</c:v>
+                </c:pt>
+                <c:pt idx="116">
+                  <c:v>0.83082777261733998</c:v>
+                </c:pt>
+                <c:pt idx="117">
+                  <c:v>0.82756745815277</c:v>
+                </c:pt>
+                <c:pt idx="118">
+                  <c:v>0.82974100112914995</c:v>
+                </c:pt>
+                <c:pt idx="119">
+                  <c:v>0.82376378774643</c:v>
+                </c:pt>
+                <c:pt idx="120">
+                  <c:v>0.82593733072280995</c:v>
+                </c:pt>
+                <c:pt idx="121">
+                  <c:v>0.83182394504546997</c:v>
+                </c:pt>
+                <c:pt idx="122">
+                  <c:v>0.82901650667190996</c:v>
+                </c:pt>
+                <c:pt idx="123">
+                  <c:v>0.82620900869369995</c:v>
+                </c:pt>
+                <c:pt idx="124">
+                  <c:v>0.82974100112914995</c:v>
+                </c:pt>
+                <c:pt idx="125">
+                  <c:v>0.83463138341903997</c:v>
+                </c:pt>
+                <c:pt idx="126">
+                  <c:v>0.83055603504180997</c:v>
+                </c:pt>
+                <c:pt idx="127">
+                  <c:v>0.82847309112548995</c:v>
+                </c:pt>
+                <c:pt idx="128">
+                  <c:v>0.82910704612732</c:v>
+                </c:pt>
+                <c:pt idx="129">
+                  <c:v>0.82457888126373002</c:v>
+                </c:pt>
+                <c:pt idx="130">
+                  <c:v>0.82756745815277</c:v>
+                </c:pt>
+                <c:pt idx="131">
+                  <c:v>0.82892590761185003</c:v>
+                </c:pt>
+                <c:pt idx="132">
+                  <c:v>0.83137112855911</c:v>
+                </c:pt>
+                <c:pt idx="133">
+                  <c:v>0.82910704612732</c:v>
+                </c:pt>
+                <c:pt idx="134">
+                  <c:v>0.83309185504912997</c:v>
+                </c:pt>
+                <c:pt idx="135">
+                  <c:v>0.82802027463912997</c:v>
+                </c:pt>
+                <c:pt idx="136">
+                  <c:v>0.82955986261367998</c:v>
+                </c:pt>
+                <c:pt idx="137">
+                  <c:v>0.82783913612366</c:v>
+                </c:pt>
+                <c:pt idx="138">
+                  <c:v>0.83490312099456998</c:v>
+                </c:pt>
+                <c:pt idx="139">
+                  <c:v>0.83091831207275002</c:v>
+                </c:pt>
+                <c:pt idx="140">
+                  <c:v>0.83236730098723999</c:v>
+                </c:pt>
+                <c:pt idx="141">
+                  <c:v>0.83118999004364003</c:v>
+                </c:pt>
+                <c:pt idx="142">
+                  <c:v>0.83508419990539995</c:v>
+                </c:pt>
+                <c:pt idx="143">
+                  <c:v>0.83173340559006004</c:v>
+                </c:pt>
+                <c:pt idx="144">
+                  <c:v>0.83481252193451005</c:v>
+                </c:pt>
+                <c:pt idx="145">
+                  <c:v>0.82919758558273005</c:v>
+                </c:pt>
+                <c:pt idx="146">
+                  <c:v>0.83445030450821001</c:v>
+                </c:pt>
+                <c:pt idx="147">
+                  <c:v>0.83309185504912997</c:v>
+                </c:pt>
+                <c:pt idx="148">
+                  <c:v>0.83454084396362005</c:v>
+                </c:pt>
+                <c:pt idx="149">
+                  <c:v>0.83064663410187001</c:v>
+                </c:pt>
+                <c:pt idx="150">
+                  <c:v>0.83146166801453003</c:v>
+                </c:pt>
+                <c:pt idx="151">
+                  <c:v>0.83834451436996005</c:v>
+                </c:pt>
+                <c:pt idx="152">
+                  <c:v>0.83562761545180997</c:v>
+                </c:pt>
+                <c:pt idx="153">
+                  <c:v>0.83490312099456998</c:v>
+                </c:pt>
+                <c:pt idx="154">
+                  <c:v>0.83372575044632002</c:v>
+                </c:pt>
+                <c:pt idx="155">
+                  <c:v>0.83644264936446999</c:v>
+                </c:pt>
+                <c:pt idx="156">
+                  <c:v>0.83200508356094005</c:v>
+                </c:pt>
+                <c:pt idx="157">
+                  <c:v>0.83218622207642001</c:v>
+                </c:pt>
+                <c:pt idx="158">
+                  <c:v>0.84124255180358998</c:v>
+                </c:pt>
+                <c:pt idx="159">
+                  <c:v>0.83888787031173995</c:v>
+                </c:pt>
+                <c:pt idx="160">
+                  <c:v>0.83834451436996005</c:v>
+                </c:pt>
+                <c:pt idx="161">
+                  <c:v>0.84133309125900002</c:v>
+                </c:pt>
+                <c:pt idx="162">
+                  <c:v>0.83671438694</c:v>
+                </c:pt>
+                <c:pt idx="163">
+                  <c:v>0.83888787031173995</c:v>
+                </c:pt>
+                <c:pt idx="164">
+                  <c:v>0.83970296382903997</c:v>
+                </c:pt>
+                <c:pt idx="165">
+                  <c:v>0.84223872423171997</c:v>
+                </c:pt>
+                <c:pt idx="166">
+                  <c:v>0.84060859680176003</c:v>
+                </c:pt>
+                <c:pt idx="167">
+                  <c:v>0.83897846937179998</c:v>
+                </c:pt>
+                <c:pt idx="168">
+                  <c:v>0.84450280666350996</c:v>
+                </c:pt>
+                <c:pt idx="169">
+                  <c:v>0.84368771314621005</c:v>
+                </c:pt>
+                <c:pt idx="170">
+                  <c:v>0.83807283639908003</c:v>
+                </c:pt>
+                <c:pt idx="171">
+                  <c:v>0.84006518125534002</c:v>
+                </c:pt>
+                <c:pt idx="172">
+                  <c:v>0.84241986274719005</c:v>
+                </c:pt>
+                <c:pt idx="173">
+                  <c:v>0.84223872423171997</c:v>
+                </c:pt>
+                <c:pt idx="174">
+                  <c:v>0.84178590774536</c:v>
+                </c:pt>
+                <c:pt idx="175">
+                  <c:v>0.84495562314987005</c:v>
+                </c:pt>
+                <c:pt idx="176">
+                  <c:v>0.84160476922989003</c:v>
+                </c:pt>
+                <c:pt idx="177">
+                  <c:v>0.84278208017348999</c:v>
+                </c:pt>
+                <c:pt idx="178">
+                  <c:v>0.83716720342635997</c:v>
+                </c:pt>
+                <c:pt idx="179">
+                  <c:v>0.84287267923355003</c:v>
+                </c:pt>
+                <c:pt idx="180">
+                  <c:v>0.84160476922989003</c:v>
+                </c:pt>
+                <c:pt idx="181">
+                  <c:v>0.84694802761078003</c:v>
+                </c:pt>
+                <c:pt idx="182">
+                  <c:v>0.84133309125900002</c:v>
+                </c:pt>
+                <c:pt idx="183">
+                  <c:v>0.84731024503707997</c:v>
+                </c:pt>
+                <c:pt idx="184">
+                  <c:v>0.84993660449982</c:v>
+                </c:pt>
+                <c:pt idx="185">
+                  <c:v>0.84314435720444003</c:v>
+                </c:pt>
+                <c:pt idx="186">
+                  <c:v>0.84767252206802002</c:v>
+                </c:pt>
+                <c:pt idx="187">
+                  <c:v>0.84613293409348</c:v>
+                </c:pt>
+                <c:pt idx="188">
+                  <c:v>0.84269154071807995</c:v>
+                </c:pt>
+                <c:pt idx="189">
+                  <c:v>0.84441226720810003</c:v>
+                </c:pt>
+                <c:pt idx="190">
+                  <c:v>0.84260100126266002</c:v>
+                </c:pt>
+                <c:pt idx="191">
+                  <c:v>0.84558957815169999</c:v>
+                </c:pt>
+                <c:pt idx="192">
+                  <c:v>0.84794420003891002</c:v>
+                </c:pt>
+                <c:pt idx="193">
+                  <c:v>0.84296321868895996</c:v>
+                </c:pt>
+                <c:pt idx="194">
+                  <c:v>0.84984606504439997</c:v>
+                </c:pt>
+                <c:pt idx="195">
+                  <c:v>0.84712916612625</c:v>
+                </c:pt>
+                <c:pt idx="196">
+                  <c:v>0.85292518138884998</c:v>
+                </c:pt>
+                <c:pt idx="197">
+                  <c:v>0.84694802761078003</c:v>
+                </c:pt>
+                <c:pt idx="198">
+                  <c:v>0.84477448463439997</c:v>
+                </c:pt>
+                <c:pt idx="199">
+                  <c:v>0.84676688909530995</c:v>
+                </c:pt>
+                <c:pt idx="200">
+                  <c:v>0.84586125612259</c:v>
+                </c:pt>
+                <c:pt idx="201">
+                  <c:v>0.84540843963623002</c:v>
+                </c:pt>
+                <c:pt idx="202">
+                  <c:v>0.85319685935973999</c:v>
+                </c:pt>
+                <c:pt idx="203">
+                  <c:v>0.84993660449982</c:v>
+                </c:pt>
+                <c:pt idx="204">
+                  <c:v>0.84441226720810003</c:v>
+                </c:pt>
+                <c:pt idx="205">
+                  <c:v>0.85084223747252996</c:v>
+                </c:pt>
+                <c:pt idx="206">
+                  <c:v>0.85473644733428999</c:v>
+                </c:pt>
+                <c:pt idx="207">
+                  <c:v>0.85410249233246005</c:v>
+                </c:pt>
+                <c:pt idx="208">
+                  <c:v>0.85020828247070002</c:v>
+                </c:pt>
+                <c:pt idx="209">
+                  <c:v>0.84894043207169001</c:v>
+                </c:pt>
+                <c:pt idx="210">
+                  <c:v>0.85120451450348</c:v>
+                </c:pt>
+                <c:pt idx="211">
+                  <c:v>0.85835897922516002</c:v>
+                </c:pt>
+                <c:pt idx="212">
+                  <c:v>0.85455530881882003</c:v>
+                </c:pt>
+                <c:pt idx="213">
+                  <c:v>0.84676688909530995</c:v>
+                </c:pt>
+                <c:pt idx="214">
+                  <c:v>0.85238182544707997</c:v>
+                </c:pt>
+                <c:pt idx="215">
+                  <c:v>0.85138559341430997</c:v>
+                </c:pt>
+                <c:pt idx="216">
+                  <c:v>0.85129505395889005</c:v>
+                </c:pt>
+                <c:pt idx="217">
+                  <c:v>0.85355913639069003</c:v>
+                </c:pt>
+                <c:pt idx="218">
+                  <c:v>0.85718166828155995</c:v>
+                </c:pt>
+                <c:pt idx="219">
+                  <c:v>0.85654771327972001</c:v>
+                </c:pt>
+                <c:pt idx="220">
+                  <c:v>0.85645717382430997</c:v>
+                </c:pt>
+                <c:pt idx="221">
+                  <c:v>0.85817784070969005</c:v>
+                </c:pt>
+                <c:pt idx="222">
+                  <c:v>0.85763448476791004</c:v>
+                </c:pt>
+                <c:pt idx="223">
+                  <c:v>0.85047996044159002</c:v>
+                </c:pt>
+                <c:pt idx="224">
+                  <c:v>0.85256296396255005</c:v>
+                </c:pt>
+                <c:pt idx="225">
+                  <c:v>0.85899293422698997</c:v>
+                </c:pt>
+                <c:pt idx="226">
+                  <c:v>0.8575439453125</c:v>
+                </c:pt>
+                <c:pt idx="227">
+                  <c:v>0.85727220773696999</c:v>
+                </c:pt>
+                <c:pt idx="228">
+                  <c:v>0.85374027490616</c:v>
+                </c:pt>
+                <c:pt idx="229">
+                  <c:v>0.85817784070969005</c:v>
+                </c:pt>
+                <c:pt idx="230">
+                  <c:v>0.85844957828521995</c:v>
+                </c:pt>
+                <c:pt idx="231">
+                  <c:v>0.85537040233612005</c:v>
+                </c:pt>
+                <c:pt idx="232">
+                  <c:v>0.86288714408875</c:v>
+                </c:pt>
+                <c:pt idx="233">
+                  <c:v>0.8575439453125</c:v>
+                </c:pt>
+                <c:pt idx="234">
+                  <c:v>0.85337799787520996</c:v>
+                </c:pt>
+                <c:pt idx="235">
+                  <c:v>0.85944575071335005</c:v>
+                </c:pt>
+                <c:pt idx="236">
+                  <c:v>0.85718166828155995</c:v>
+                </c:pt>
+                <c:pt idx="237">
+                  <c:v>0.86252492666244995</c:v>
+                </c:pt>
+                <c:pt idx="238">
+                  <c:v>0.85537040233612005</c:v>
+                </c:pt>
+                <c:pt idx="239">
+                  <c:v>0.85844957828521995</c:v>
+                </c:pt>
+                <c:pt idx="240">
+                  <c:v>0.86433619260787997</c:v>
+                </c:pt>
+                <c:pt idx="241">
+                  <c:v>0.86497008800507003</c:v>
+                </c:pt>
+                <c:pt idx="242">
+                  <c:v>0.85863065719604004</c:v>
+                </c:pt>
+                <c:pt idx="243">
+                  <c:v>0.86026084423064997</c:v>
+                </c:pt>
+                <c:pt idx="244">
+                  <c:v>0.86352109909057995</c:v>
+                </c:pt>
+                <c:pt idx="245">
+                  <c:v>0.86071366071701005</c:v>
+                </c:pt>
+                <c:pt idx="246">
+                  <c:v>0.86261546611786</c:v>
+                </c:pt>
+                <c:pt idx="247">
+                  <c:v>0.86288714408875</c:v>
+                </c:pt>
+                <c:pt idx="248">
+                  <c:v>0.86388337612152</c:v>
+                </c:pt>
+                <c:pt idx="249">
+                  <c:v>0.85718166828155995</c:v>
+                </c:pt>
+                <c:pt idx="250">
+                  <c:v>0.86433619260787997</c:v>
+                </c:pt>
+                <c:pt idx="251">
+                  <c:v>0.86433619260787997</c:v>
+                </c:pt>
+                <c:pt idx="252">
+                  <c:v>0.86424559354782005</c:v>
+                </c:pt>
+                <c:pt idx="253">
+                  <c:v>0.86515122652054</c:v>
+                </c:pt>
+                <c:pt idx="254">
+                  <c:v>0.86216264963150002</c:v>
+                </c:pt>
+                <c:pt idx="255">
+                  <c:v>0.86524182558060003</c:v>
+                </c:pt>
+                <c:pt idx="256">
+                  <c:v>0.86614745855330999</c:v>
+                </c:pt>
+                <c:pt idx="257">
+                  <c:v>0.86795872449875</c:v>
+                </c:pt>
+                <c:pt idx="258">
+                  <c:v>0.86986052989960005</c:v>
+                </c:pt>
+                <c:pt idx="259">
+                  <c:v>0.86623799800873003</c:v>
+                </c:pt>
+                <c:pt idx="260">
+                  <c:v>0.86587572097777998</c:v>
+                </c:pt>
+                <c:pt idx="261">
+                  <c:v>0.86397391557693004</c:v>
+                </c:pt>
+                <c:pt idx="262">
+                  <c:v>0.86650967597961004</c:v>
+                </c:pt>
+                <c:pt idx="263">
+                  <c:v>0.86986052989960005</c:v>
+                </c:pt>
+                <c:pt idx="264">
+                  <c:v>0.86333996057509999</c:v>
+                </c:pt>
+                <c:pt idx="265">
+                  <c:v>0.86406445503234997</c:v>
+                </c:pt>
+                <c:pt idx="266">
+                  <c:v>0.86614745855330999</c:v>
+                </c:pt>
+                <c:pt idx="267">
+                  <c:v>0.86669081449509</c:v>
+                </c:pt>
+                <c:pt idx="268">
+                  <c:v>0.86795872449875</c:v>
+                </c:pt>
+                <c:pt idx="269">
+                  <c:v>0.86714363098144998</c:v>
+                </c:pt>
+                <c:pt idx="270">
+                  <c:v>0.86098533868789995</c:v>
+                </c:pt>
+                <c:pt idx="271">
+                  <c:v>0.86623799800873003</c:v>
+                </c:pt>
+                <c:pt idx="272">
+                  <c:v>0.86759644746779996</c:v>
+                </c:pt>
+                <c:pt idx="273">
+                  <c:v>0.87284910678864003</c:v>
+                </c:pt>
+                <c:pt idx="274">
+                  <c:v>0.87112843990326005</c:v>
+                </c:pt>
+                <c:pt idx="275">
+                  <c:v>0.86578518152237005</c:v>
+                </c:pt>
+                <c:pt idx="276">
+                  <c:v>0.86895489692687999</c:v>
+                </c:pt>
+                <c:pt idx="277">
+                  <c:v>0.86687195301055997</c:v>
+                </c:pt>
+                <c:pt idx="278">
+                  <c:v>0.87221515178679998</c:v>
+                </c:pt>
+                <c:pt idx="279">
+                  <c:v>0.87547546625136996</c:v>
+                </c:pt>
+                <c:pt idx="280">
+                  <c:v>0.86678135395050004</c:v>
+                </c:pt>
+                <c:pt idx="281">
+                  <c:v>0.87194347381591997</c:v>
+                </c:pt>
+                <c:pt idx="282">
+                  <c:v>0.87484151124954002</c:v>
+                </c:pt>
+                <c:pt idx="283">
+                  <c:v>0.87194347381591997</c:v>
+                </c:pt>
+                <c:pt idx="284">
+                  <c:v>0.87384533882141002</c:v>
+                </c:pt>
+                <c:pt idx="285">
+                  <c:v>0.87257742881775002</c:v>
+                </c:pt>
+                <c:pt idx="286">
+                  <c:v>0.87058502435684004</c:v>
+                </c:pt>
+                <c:pt idx="287">
+                  <c:v>0.87112843990326005</c:v>
+                </c:pt>
+                <c:pt idx="288">
+                  <c:v>0.87411701679230003</c:v>
+                </c:pt>
+                <c:pt idx="289">
+                  <c:v>0.87384533882141002</c:v>
+                </c:pt>
+                <c:pt idx="290">
+                  <c:v>0.87248688936233998</c:v>
+                </c:pt>
+                <c:pt idx="291">
+                  <c:v>0.87176233530045</c:v>
+                </c:pt>
+                <c:pt idx="292">
+                  <c:v>0.87629050016402998</c:v>
+                </c:pt>
+                <c:pt idx="293">
+                  <c:v>0.87393587827681996</c:v>
+                </c:pt>
+                <c:pt idx="294">
+                  <c:v>0.87529432773589999</c:v>
+                </c:pt>
+                <c:pt idx="295">
+                  <c:v>0.87121897935866999</c:v>
+                </c:pt>
+                <c:pt idx="296">
+                  <c:v>0.87447923421859997</c:v>
+                </c:pt>
+                <c:pt idx="297">
+                  <c:v>0.87384533882141002</c:v>
+                </c:pt>
+                <c:pt idx="298">
+                  <c:v>0.87040388584136996</c:v>
+                </c:pt>
+                <c:pt idx="299">
+                  <c:v>0.87076616287231001</c:v>
+                </c:pt>
+                <c:pt idx="300">
+                  <c:v>0.87366420030594005</c:v>
+                </c:pt>
+                <c:pt idx="301">
+                  <c:v>0.87303024530411</c:v>
+                </c:pt>
+                <c:pt idx="302">
+                  <c:v>0.87348306179046997</c:v>
+                </c:pt>
+                <c:pt idx="303">
+                  <c:v>0.87130951881409002</c:v>
+                </c:pt>
+                <c:pt idx="304">
+                  <c:v>0.87619996070862005</c:v>
+                </c:pt>
+                <c:pt idx="305">
+                  <c:v>0.87420755624770996</c:v>
+                </c:pt>
+                <c:pt idx="306">
+                  <c:v>0.87918853759766002</c:v>
+                </c:pt>
+                <c:pt idx="307">
+                  <c:v>0.87764894962311002</c:v>
+                </c:pt>
+                <c:pt idx="308">
+                  <c:v>0.87619996070862005</c:v>
+                </c:pt>
+                <c:pt idx="309">
+                  <c:v>0.87094730138778997</c:v>
+                </c:pt>
+                <c:pt idx="310">
+                  <c:v>0.88136208057403997</c:v>
+                </c:pt>
+                <c:pt idx="311">
+                  <c:v>0.87755841016768998</c:v>
+                </c:pt>
+                <c:pt idx="312">
+                  <c:v>0.88072812557220004</c:v>
+                </c:pt>
+                <c:pt idx="313">
+                  <c:v>0.87936967611312999</c:v>
+                </c:pt>
+                <c:pt idx="314">
+                  <c:v>0.88018476963043002</c:v>
+                </c:pt>
+                <c:pt idx="315">
+                  <c:v>0.87891685962677002</c:v>
+                </c:pt>
+                <c:pt idx="316">
+                  <c:v>0.88453179597855003</c:v>
+                </c:pt>
+                <c:pt idx="317">
+                  <c:v>0.88235825300216997</c:v>
+                </c:pt>
+                <c:pt idx="318">
+                  <c:v>0.87583768367767001</c:v>
+                </c:pt>
+                <c:pt idx="319">
+                  <c:v>0.87973195314407004</c:v>
+                </c:pt>
+                <c:pt idx="320">
+                  <c:v>0.87792068719864003</c:v>
+                </c:pt>
+                <c:pt idx="321">
+                  <c:v>0.88081866502761996</c:v>
+                </c:pt>
+                <c:pt idx="322">
+                  <c:v>0.88598078489304</c:v>
+                </c:pt>
+                <c:pt idx="323">
+                  <c:v>0.87964135408401001</c:v>
+                </c:pt>
+                <c:pt idx="324">
+                  <c:v>0.87773954868316995</c:v>
+                </c:pt>
+                <c:pt idx="325">
+                  <c:v>0.87665277719498003</c:v>
+                </c:pt>
+                <c:pt idx="326">
+                  <c:v>0.88027530908585006</c:v>
+                </c:pt>
+                <c:pt idx="327">
+                  <c:v>0.87810176610946999</c:v>
+                </c:pt>
+                <c:pt idx="328">
+                  <c:v>0.88072812557220004</c:v>
+                </c:pt>
+                <c:pt idx="329">
+                  <c:v>0.88045644760132002</c:v>
+                </c:pt>
+                <c:pt idx="330">
+                  <c:v>0.88317334651946999</c:v>
+                </c:pt>
+                <c:pt idx="331">
+                  <c:v>0.87891685962677002</c:v>
+                </c:pt>
+                <c:pt idx="332">
+                  <c:v>0.87719613313675004</c:v>
+                </c:pt>
+                <c:pt idx="333">
+                  <c:v>0.88072812557220004</c:v>
+                </c:pt>
+                <c:pt idx="334">
+                  <c:v>0.87891685962677002</c:v>
+                </c:pt>
+                <c:pt idx="335">
+                  <c:v>0.88507515192032005</c:v>
+                </c:pt>
+                <c:pt idx="336">
+                  <c:v>0.88063758611678999</c:v>
+                </c:pt>
+                <c:pt idx="337">
+                  <c:v>0.88697701692580999</c:v>
+                </c:pt>
+                <c:pt idx="338">
+                  <c:v>0.88299220800400002</c:v>
+                </c:pt>
+                <c:pt idx="339">
+                  <c:v>0.88770151138305997</c:v>
+                </c:pt>
+                <c:pt idx="340">
+                  <c:v>0.88987499475479004</c:v>
+                </c:pt>
+                <c:pt idx="341">
+                  <c:v>0.88244885206223</c:v>
+                </c:pt>
+                <c:pt idx="342">
+                  <c:v>0.88480347394943004</c:v>
+                </c:pt>
+                <c:pt idx="343">
+                  <c:v>0.88661473989487005</c:v>
+                </c:pt>
+                <c:pt idx="344">
+                  <c:v>0.87927913665770996</c:v>
+                </c:pt>
+                <c:pt idx="345">
+                  <c:v>0.88407897949219005</c:v>
+                </c:pt>
+                <c:pt idx="346">
+                  <c:v>0.88507515192032005</c:v>
+                </c:pt>
+                <c:pt idx="347">
+                  <c:v>0.88638007640839001</c:v>
+                </c:pt>
+                <c:pt idx="348">
+                  <c:v>0.88208657503127996</c:v>
+                </c:pt>
+                <c:pt idx="349">
+                  <c:v>0.88362616300582997</c:v>
+                </c:pt>
+                <c:pt idx="350">
+                  <c:v>0.88779205083847001</c:v>
+                </c:pt>
+                <c:pt idx="351">
+                  <c:v>0.88869768381118996</c:v>
+                </c:pt>
+                <c:pt idx="352">
+                  <c:v>0.88679587841034002</c:v>
+                </c:pt>
+                <c:pt idx="353">
+                  <c:v>0.89286363124847001</c:v>
+                </c:pt>
+                <c:pt idx="354">
+                  <c:v>0.88109040260314997</c:v>
+                </c:pt>
+                <c:pt idx="355">
+                  <c:v>0.88752037286758001</c:v>
+                </c:pt>
+                <c:pt idx="356">
+                  <c:v>0.88887882232666005</c:v>
+                </c:pt>
+                <c:pt idx="357">
+                  <c:v>0.88525629043579002</c:v>
+                </c:pt>
+                <c:pt idx="358">
+                  <c:v>0.88896936178206998</c:v>
+                </c:pt>
+                <c:pt idx="359">
+                  <c:v>0.88815432786941995</c:v>
+                </c:pt>
+                <c:pt idx="360">
+                  <c:v>0.88362616300582997</c:v>
+                </c:pt>
+                <c:pt idx="361">
+                  <c:v>0.88905996084213001</c:v>
+                </c:pt>
+                <c:pt idx="362">
+                  <c:v>0.88607138395309004</c:v>
+                </c:pt>
+                <c:pt idx="363">
+                  <c:v>0.88978445529937999</c:v>
+                </c:pt>
+                <c:pt idx="364">
+                  <c:v>0.88507515192032005</c:v>
+                </c:pt>
+                <c:pt idx="365">
+                  <c:v>0.88643360137938998</c:v>
+                </c:pt>
+                <c:pt idx="366">
+                  <c:v>0.88652420043945002</c:v>
+                </c:pt>
+                <c:pt idx="367">
+                  <c:v>0.89005613327026001</c:v>
+                </c:pt>
+                <c:pt idx="368">
+                  <c:v>0.89069008827208995</c:v>
+                </c:pt>
+                <c:pt idx="369">
+                  <c:v>0.88715809583663996</c:v>
+                </c:pt>
+                <c:pt idx="370">
+                  <c:v>0.89548993110657005</c:v>
+                </c:pt>
+                <c:pt idx="371">
+                  <c:v>0.89159572124481001</c:v>
+                </c:pt>
+                <c:pt idx="372">
+                  <c:v>0.89322584867476995</c:v>
+                </c:pt>
+                <c:pt idx="373">
+                  <c:v>0.88625246286392001</c:v>
+                </c:pt>
+                <c:pt idx="374">
+                  <c:v>0.89059954881668002</c:v>
+                </c:pt>
+                <c:pt idx="375">
+                  <c:v>0.88942217826842995</c:v>
+                </c:pt>
+                <c:pt idx="376">
+                  <c:v>0.89376926422118996</c:v>
+                </c:pt>
+                <c:pt idx="377">
+                  <c:v>0.89123344421386996</c:v>
+                </c:pt>
+                <c:pt idx="378">
+                  <c:v>0.89141458272934004</c:v>
+                </c:pt>
+                <c:pt idx="379">
+                  <c:v>0.89168626070023005</c:v>
+                </c:pt>
+                <c:pt idx="380">
+                  <c:v>0.89404094219207997</c:v>
+                </c:pt>
+                <c:pt idx="381">
+                  <c:v>0.89078062772750999</c:v>
+                </c:pt>
+                <c:pt idx="382">
+                  <c:v>0.89014673233032005</c:v>
+                </c:pt>
+                <c:pt idx="383">
+                  <c:v>0.89322584867476995</c:v>
+                </c:pt>
+                <c:pt idx="384">
+                  <c:v>0.89358812570571999</c:v>
+                </c:pt>
+                <c:pt idx="385">
+                  <c:v>0.89168626070023005</c:v>
+                </c:pt>
+                <c:pt idx="386">
+                  <c:v>0.88924109935759998</c:v>
+                </c:pt>
+                <c:pt idx="387">
+                  <c:v>0.89675784111023005</c:v>
+                </c:pt>
+                <c:pt idx="388">
+                  <c:v>0.89304471015929998</c:v>
+                </c:pt>
+                <c:pt idx="389">
+                  <c:v>0.89802569150925005</c:v>
+                </c:pt>
+                <c:pt idx="390">
+                  <c:v>0.89358812570571999</c:v>
+                </c:pt>
+                <c:pt idx="391">
+                  <c:v>0.89232021570205999</c:v>
+                </c:pt>
+                <c:pt idx="392">
+                  <c:v>0.89956527948380005</c:v>
+                </c:pt>
+                <c:pt idx="393">
+                  <c:v>0.89684838056563998</c:v>
+                </c:pt>
+                <c:pt idx="394">
+                  <c:v>0.89467489719391002</c:v>
+                </c:pt>
+                <c:pt idx="395">
+                  <c:v>0.89884078502654996</c:v>
+                </c:pt>
+                <c:pt idx="396">
+                  <c:v>0.89856910705565995</c:v>
+                </c:pt>
+                <c:pt idx="397">
+                  <c:v>0.89413148164749001</c:v>
+                </c:pt>
+                <c:pt idx="398">
+                  <c:v>0.89413148164749001</c:v>
+                </c:pt>
+                <c:pt idx="399">
+                  <c:v>0.89693897962570002</c:v>
+                </c:pt>
+                <c:pt idx="400">
+                  <c:v>0.89331644773482999</c:v>
+                </c:pt>
+                <c:pt idx="401">
+                  <c:v>0.89422208070755005</c:v>
+                </c:pt>
+                <c:pt idx="402">
+                  <c:v>0.89521825313568004</c:v>
+                </c:pt>
+                <c:pt idx="403">
+                  <c:v>0.89893132448196</c:v>
+                </c:pt>
+                <c:pt idx="404">
+                  <c:v>0.89132404327393</c:v>
+                </c:pt>
+                <c:pt idx="405">
+                  <c:v>0.89793515205383001</c:v>
+                </c:pt>
+                <c:pt idx="406">
+                  <c:v>0.90201050043106001</c:v>
+                </c:pt>
+                <c:pt idx="407">
+                  <c:v>0.89576160907744995</c:v>
+                </c:pt>
+                <c:pt idx="408">
+                  <c:v>0.89721065759659002</c:v>
+                </c:pt>
+                <c:pt idx="409">
+                  <c:v>0.90210103988646995</c:v>
+                </c:pt>
+                <c:pt idx="410">
+                  <c:v>0.90128600597382003</c:v>
+                </c:pt>
+                <c:pt idx="411">
+                  <c:v>0.89612388610839999</c:v>
+                </c:pt>
+                <c:pt idx="412">
+                  <c:v>0.90019923448563</c:v>
+                </c:pt>
+                <c:pt idx="413">
+                  <c:v>0.89594274759293002</c:v>
+                </c:pt>
+                <c:pt idx="414">
+                  <c:v>0.89467489719391002</c:v>
+                </c:pt>
+                <c:pt idx="415">
+                  <c:v>0.90065205097197998</c:v>
+                </c:pt>
+                <c:pt idx="416">
+                  <c:v>0.89784461259841997</c:v>
+                </c:pt>
+                <c:pt idx="417">
+                  <c:v>0.90001809597015003</c:v>
+                </c:pt>
+                <c:pt idx="418">
+                  <c:v>0.90427458286285001</c:v>
+                </c:pt>
+                <c:pt idx="419">
+                  <c:v>0.90010869503020996</c:v>
+                </c:pt>
+                <c:pt idx="420">
+                  <c:v>0.89856910705565995</c:v>
+                </c:pt>
+                <c:pt idx="421">
+                  <c:v>0.89929360151291005</c:v>
+                </c:pt>
+                <c:pt idx="422">
+                  <c:v>0.90463685989380005</c:v>
+                </c:pt>
+                <c:pt idx="423">
+                  <c:v>0.90001809597015003</c:v>
+                </c:pt>
+                <c:pt idx="424">
+                  <c:v>0.90318781137465998</c:v>
+                </c:pt>
+                <c:pt idx="425">
+                  <c:v>0.90472739934920998</c:v>
+                </c:pt>
+                <c:pt idx="426">
+                  <c:v>0.90400290489196999</c:v>
+                </c:pt>
+                <c:pt idx="427">
+                  <c:v>0.90472739934920998</c:v>
+                </c:pt>
+                <c:pt idx="428">
+                  <c:v>0.90382176637650002</c:v>
+                </c:pt>
+                <c:pt idx="429">
+                  <c:v>0.90318781137465998</c:v>
+                </c:pt>
+                <c:pt idx="430">
+                  <c:v>0.90364062786101995</c:v>
+                </c:pt>
+                <c:pt idx="431">
+                  <c:v>0.90101432800293002</c:v>
+                </c:pt>
+                <c:pt idx="432">
+                  <c:v>0.89965587854384999</c:v>
+                </c:pt>
+                <c:pt idx="433">
+                  <c:v>0.90219163894652998</c:v>
+                </c:pt>
+                <c:pt idx="434">
+                  <c:v>0.90599530935286998</c:v>
+                </c:pt>
+                <c:pt idx="435">
+                  <c:v>0.90472739934920998</c:v>
+                </c:pt>
+                <c:pt idx="436">
+                  <c:v>0.90182936191559004</c:v>
+                </c:pt>
+                <c:pt idx="437">
+                  <c:v>0.90210103988646995</c:v>
+                </c:pt>
+                <c:pt idx="438">
+                  <c:v>0.90499907732009999</c:v>
+                </c:pt>
+                <c:pt idx="439">
+                  <c:v>0.90228217840195002</c:v>
+                </c:pt>
+                <c:pt idx="440">
+                  <c:v>0.90454626083374001</c:v>
+                </c:pt>
+                <c:pt idx="441">
+                  <c:v>0.90454626083374001</c:v>
+                </c:pt>
+                <c:pt idx="442">
+                  <c:v>0.90581417083740001</c:v>
+                </c:pt>
+                <c:pt idx="443">
+                  <c:v>0.90608584880829002</c:v>
+                </c:pt>
+                <c:pt idx="444">
+                  <c:v>0.90355008840561002</c:v>
+                </c:pt>
+                <c:pt idx="445">
+                  <c:v>0.90119540691375999</c:v>
+                </c:pt>
+                <c:pt idx="446">
+                  <c:v>0.90427458286285001</c:v>
+                </c:pt>
+                <c:pt idx="447">
+                  <c:v>0.90391230583190996</c:v>
+                </c:pt>
+                <c:pt idx="448">
+                  <c:v>0.90382176637650002</c:v>
+                </c:pt>
+                <c:pt idx="449">
+                  <c:v>0.90690094232559004</c:v>
+                </c:pt>
+                <c:pt idx="450">
+                  <c:v>0.90671980381011996</c:v>
+                </c:pt>
+                <c:pt idx="451">
+                  <c:v>0.90427458286285001</c:v>
+                </c:pt>
+                <c:pt idx="452">
+                  <c:v>0.90662920475006004</c:v>
+                </c:pt>
+                <c:pt idx="453">
+                  <c:v>0.90572357177733998</c:v>
+                </c:pt>
+                <c:pt idx="454">
+                  <c:v>0.90898388624190996</c:v>
+                </c:pt>
+                <c:pt idx="455">
+                  <c:v>0.90970838069916005</c:v>
+                </c:pt>
+                <c:pt idx="456">
+                  <c:v>0.90545189380645996</c:v>
+                </c:pt>
+                <c:pt idx="457">
+                  <c:v>0.90853106975554998</c:v>
+                </c:pt>
+                <c:pt idx="458">
+                  <c:v>0.90599530935286998</c:v>
+                </c:pt>
+                <c:pt idx="459">
+                  <c:v>0.9080782532692</c:v>
+                </c:pt>
+                <c:pt idx="460">
+                  <c:v>0.90934610366821</c:v>
+                </c:pt>
+                <c:pt idx="461">
+                  <c:v>0.90499907732009999</c:v>
+                </c:pt>
+                <c:pt idx="462">
+                  <c:v>0.90635752677917003</c:v>
+                </c:pt>
+                <c:pt idx="463">
+                  <c:v>0.90508967638016002</c:v>
+                </c:pt>
+                <c:pt idx="464">
+                  <c:v>0.90825939178466997</c:v>
+                </c:pt>
+                <c:pt idx="465">
+                  <c:v>0.90871220827103005</c:v>
+                </c:pt>
+                <c:pt idx="466">
+                  <c:v>0.90345948934554998</c:v>
+                </c:pt>
+                <c:pt idx="467">
+                  <c:v>0.90934610366821</c:v>
+                </c:pt>
+                <c:pt idx="468">
+                  <c:v>0.90653866529464999</c:v>
+                </c:pt>
+                <c:pt idx="469">
+                  <c:v>0.90744429826735995</c:v>
+                </c:pt>
+                <c:pt idx="470">
+                  <c:v>0.91161018610000999</c:v>
+                </c:pt>
+                <c:pt idx="471">
+                  <c:v>0.90463685989380005</c:v>
+                </c:pt>
+                <c:pt idx="472">
+                  <c:v>0.90871220827103005</c:v>
+                </c:pt>
+                <c:pt idx="473">
+                  <c:v>0.91450822353363004</c:v>
+                </c:pt>
+                <c:pt idx="474">
+                  <c:v>0.91070455312729004</c:v>
+                </c:pt>
+                <c:pt idx="475">
+                  <c:v>0.91088569164276001</c:v>
+                </c:pt>
+                <c:pt idx="476">
+                  <c:v>0.91079515218734997</c:v>
+                </c:pt>
+                <c:pt idx="477">
+                  <c:v>0.90898388624190996</c:v>
+                </c:pt>
+                <c:pt idx="478">
+                  <c:v>0.90536135435104004</c:v>
+                </c:pt>
+                <c:pt idx="479">
+                  <c:v>0.91441768407821999</c:v>
+                </c:pt>
+                <c:pt idx="480">
+                  <c:v>0.91206300258635997</c:v>
+                </c:pt>
+                <c:pt idx="481">
+                  <c:v>0.90816879272461004</c:v>
+                </c:pt>
+                <c:pt idx="482">
+                  <c:v>0.91233474016189997</c:v>
+                </c:pt>
+                <c:pt idx="483">
+                  <c:v>0.91550445556641002</c:v>
+                </c:pt>
+                <c:pt idx="484">
+                  <c:v>0.90527075529098999</c:v>
+                </c:pt>
+                <c:pt idx="485">
+                  <c:v>0.90925556421279996</c:v>
+                </c:pt>
+                <c:pt idx="486">
+                  <c:v>0.91034233570098999</c:v>
+                </c:pt>
+                <c:pt idx="487">
+                  <c:v>0.91369318962097001</c:v>
+                </c:pt>
+                <c:pt idx="488">
+                  <c:v>0.91269695758820002</c:v>
+                </c:pt>
+                <c:pt idx="489">
+                  <c:v>0.91206300258635997</c:v>
+                </c:pt>
+                <c:pt idx="490">
+                  <c:v>0.90635752677917003</c:v>
+                </c:pt>
+                <c:pt idx="491">
+                  <c:v>0.9080782532692</c:v>
+                </c:pt>
+                <c:pt idx="492">
+                  <c:v>0.91360259056090998</c:v>
+                </c:pt>
+                <c:pt idx="493">
+                  <c:v>0.91604781150818004</c:v>
+                </c:pt>
+                <c:pt idx="494">
+                  <c:v>0.90889328718185003</c:v>
+                </c:pt>
+                <c:pt idx="495">
+                  <c:v>0.91342145204544001</c:v>
+                </c:pt>
+                <c:pt idx="496">
+                  <c:v>0.91541385650634999</c:v>
+                </c:pt>
+                <c:pt idx="497">
+                  <c:v>0.91179132461547996</c:v>
+                </c:pt>
+                <c:pt idx="498">
+                  <c:v>0.91007065773009999</c:v>
+                </c:pt>
+                <c:pt idx="499">
+                  <c:v>0.91912698745728005</c:v>
+                </c:pt>
+                <c:pt idx="502">
+                  <c:v>0</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="1"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-DAE7-4FC7-A5AE-38F16B2E86C9}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Worksheet!$E$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>val_accuracy</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:yVal>
+            <c:numRef>
+              <c:f>Worksheet!$E$2:$E$504</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="503"/>
+                <c:pt idx="0">
+                  <c:v>0.45530521869659002</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.45530521869659002</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.45530521869659002</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.45530521869659002</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.45457848906517001</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.45530521869659002</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0.47928780317307002</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0.45530521869659002</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0.50799417495728005</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0.51598834991455</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>0.51053780317306996</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>0.49672964215278997</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>0.48292151093482999</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>0.57049417495728005</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>0.61373543739319003</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>0.60356104373931996</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>0.57558137178420998</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>0.66497093439101995</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>0.66133719682693004</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>0.64534884691238004</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>0.64498543739319003</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>0.66933137178420998</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>0.63081395626068004</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>0.65661334991455</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>0.68640989065169999</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>0.70966571569443004</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>0.71511626243590998</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>0.70857560634613004</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>0.75290697813034002</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>0.74491280317306996</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>0.77834302186965998</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>0.77906978130340998</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>0.77906978130340998</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>0.77834302186965998</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>0.78779071569443004</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>0.79069769382476995</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>0.78851741552353005</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>0.77688956260680997</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>0.80305230617523005</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>0.79215115308761996</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>0.79469478130340998</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>0.80232560634613004</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>0.79505813121795998</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>0.80850291252135997</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>0.80523258447646995</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>0.80922967195510997</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>0.80159884691238004</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>0.79505813121795998</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>0.80813956260680997</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>0.79106104373931996</c:v>
+                </c:pt>
+                <c:pt idx="50">
+                  <c:v>0.77688956260680997</c:v>
+                </c:pt>
+                <c:pt idx="51">
+                  <c:v>0.81649708747864003</c:v>
+                </c:pt>
+                <c:pt idx="52">
+                  <c:v>0.80595928430556996</c:v>
+                </c:pt>
+                <c:pt idx="53">
+                  <c:v>0.82667154073714999</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>0.78706395626068004</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>0.81686043739319003</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>0.82521802186965998</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>0.82848834991455</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>0.82376456260680997</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>0.82013082504271995</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>0.82921510934830001</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>0.83466571569443004</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>0.82885175943375</c:v>
+                </c:pt>
+                <c:pt idx="63">
+                  <c:v>0.83502906560898005</c:v>
+                </c:pt>
+                <c:pt idx="64">
+                  <c:v>0.83720928430556996</c:v>
+                </c:pt>
+                <c:pt idx="65">
+                  <c:v>0.83357560634613004</c:v>
+                </c:pt>
+                <c:pt idx="66">
+                  <c:v>0.83466571569443004</c:v>
+                </c:pt>
+                <c:pt idx="67">
+                  <c:v>0.83175873756409002</c:v>
+                </c:pt>
+                <c:pt idx="68">
+                  <c:v>0.83248543739319003</c:v>
+                </c:pt>
+                <c:pt idx="69">
+                  <c:v>0.83539241552353005</c:v>
+                </c:pt>
+                <c:pt idx="70">
+                  <c:v>0.82957845926285001</c:v>
+                </c:pt>
+                <c:pt idx="71">
+                  <c:v>0.82667154073714999</c:v>
+                </c:pt>
+                <c:pt idx="72">
+                  <c:v>0.83466571569443004</c:v>
+                </c:pt>
+                <c:pt idx="73">
+                  <c:v>0.83030521869659002</c:v>
+                </c:pt>
+                <c:pt idx="74">
+                  <c:v>0.83648258447646995</c:v>
+                </c:pt>
+                <c:pt idx="75">
+                  <c:v>0.83575582504271995</c:v>
+                </c:pt>
+                <c:pt idx="76">
+                  <c:v>0.84011626243590998</c:v>
+                </c:pt>
+                <c:pt idx="77">
+                  <c:v>0.83684593439101995</c:v>
+                </c:pt>
+                <c:pt idx="78">
+                  <c:v>0.83648258447646995</c:v>
+                </c:pt>
+                <c:pt idx="79">
+                  <c:v>0.84084302186965998</c:v>
+                </c:pt>
+                <c:pt idx="80">
+                  <c:v>0.84084302186965998</c:v>
+                </c:pt>
+                <c:pt idx="81">
+                  <c:v>0.84156978130340998</c:v>
+                </c:pt>
+                <c:pt idx="82">
+                  <c:v>0.83648258447646995</c:v>
+                </c:pt>
+                <c:pt idx="83">
+                  <c:v>0.84047967195510997</c:v>
+                </c:pt>
+                <c:pt idx="84">
+                  <c:v>0.84338665008545</c:v>
+                </c:pt>
+                <c:pt idx="85">
+                  <c:v>0.84084302186965998</c:v>
+                </c:pt>
+                <c:pt idx="86">
+                  <c:v>0.83720928430556996</c:v>
+                </c:pt>
+                <c:pt idx="87">
+                  <c:v>0.84665697813034002</c:v>
+                </c:pt>
+                <c:pt idx="88">
+                  <c:v>0.84774708747864003</c:v>
+                </c:pt>
+                <c:pt idx="89">
+                  <c:v>0.84593021869659002</c:v>
+                </c:pt>
+                <c:pt idx="90">
+                  <c:v>0.83829939365386996</c:v>
+                </c:pt>
+                <c:pt idx="91">
+                  <c:v>0.83284884691238004</c:v>
+                </c:pt>
+                <c:pt idx="92">
+                  <c:v>0.84302324056625</c:v>
+                </c:pt>
+                <c:pt idx="93">
+                  <c:v>0.83938956260680997</c:v>
+                </c:pt>
+                <c:pt idx="94">
+                  <c:v>0.84447675943375</c:v>
+                </c:pt>
+                <c:pt idx="95">
+                  <c:v>0.83793604373931996</c:v>
+                </c:pt>
+                <c:pt idx="96">
+                  <c:v>0.84411334991455</c:v>
+                </c:pt>
+                <c:pt idx="97">
+                  <c:v>0.84811043739319003</c:v>
+                </c:pt>
+                <c:pt idx="98">
+                  <c:v>0.84302324056625</c:v>
+                </c:pt>
+                <c:pt idx="99">
+                  <c:v>0.84738373756409002</c:v>
+                </c:pt>
+                <c:pt idx="100">
+                  <c:v>0.84338665008545</c:v>
+                </c:pt>
+                <c:pt idx="101">
+                  <c:v>0.83975291252135997</c:v>
+                </c:pt>
+                <c:pt idx="102">
+                  <c:v>0.83938956260680997</c:v>
+                </c:pt>
+                <c:pt idx="103">
+                  <c:v>0.84665697813034002</c:v>
+                </c:pt>
+                <c:pt idx="104">
+                  <c:v>0.84156978130340998</c:v>
+                </c:pt>
+                <c:pt idx="105">
+                  <c:v>0.83902615308761996</c:v>
+                </c:pt>
+                <c:pt idx="106">
+                  <c:v>0.84375</c:v>
+                </c:pt>
+                <c:pt idx="107">
+                  <c:v>0.84738373756409002</c:v>
+                </c:pt>
+                <c:pt idx="108">
+                  <c:v>0.84520345926285001</c:v>
+                </c:pt>
+                <c:pt idx="109">
+                  <c:v>0.84520345926285001</c:v>
+                </c:pt>
+                <c:pt idx="110">
+                  <c:v>0.84484010934830001</c:v>
+                </c:pt>
+                <c:pt idx="111">
+                  <c:v>0.84702032804489003</c:v>
+                </c:pt>
+                <c:pt idx="112">
+                  <c:v>0.84847384691238004</c:v>
+                </c:pt>
+                <c:pt idx="113">
+                  <c:v>0.84593021869659002</c:v>
+                </c:pt>
+                <c:pt idx="114">
+                  <c:v>0.84593021869659002</c:v>
+                </c:pt>
+                <c:pt idx="115">
+                  <c:v>0.84920060634613004</c:v>
+                </c:pt>
+                <c:pt idx="116">
+                  <c:v>0.84811043739319003</c:v>
+                </c:pt>
+                <c:pt idx="117">
+                  <c:v>0.84702032804489003</c:v>
+                </c:pt>
+                <c:pt idx="118">
+                  <c:v>0.84883719682693004</c:v>
+                </c:pt>
+                <c:pt idx="119">
+                  <c:v>0.85392439365386996</c:v>
+                </c:pt>
+                <c:pt idx="120">
+                  <c:v>0.85356104373931996</c:v>
+                </c:pt>
+                <c:pt idx="121">
+                  <c:v>0.84011626243590998</c:v>
+                </c:pt>
+                <c:pt idx="122">
+                  <c:v>0.85428780317306996</c:v>
+                </c:pt>
+                <c:pt idx="123">
+                  <c:v>0.84665697813034002</c:v>
+                </c:pt>
+                <c:pt idx="124">
+                  <c:v>0.84665697813034002</c:v>
+                </c:pt>
+                <c:pt idx="125">
+                  <c:v>0.84665697813034002</c:v>
+                </c:pt>
+                <c:pt idx="126">
+                  <c:v>0.85574126243590998</c:v>
+                </c:pt>
+                <c:pt idx="127">
+                  <c:v>0.85029071569443004</c:v>
+                </c:pt>
+                <c:pt idx="128">
+                  <c:v>0.84484010934830001</c:v>
+                </c:pt>
+                <c:pt idx="129">
+                  <c:v>0.85210758447646995</c:v>
+                </c:pt>
+                <c:pt idx="130">
+                  <c:v>0.84702032804489003</c:v>
+                </c:pt>
+                <c:pt idx="131">
+                  <c:v>0.84738373756409002</c:v>
+                </c:pt>
+                <c:pt idx="132">
+                  <c:v>0.84702032804489003</c:v>
+                </c:pt>
+                <c:pt idx="133">
+                  <c:v>0.85065406560898005</c:v>
+                </c:pt>
+                <c:pt idx="134">
+                  <c:v>0.84265989065169999</c:v>
+                </c:pt>
+                <c:pt idx="135">
+                  <c:v>0.85537791252135997</c:v>
+                </c:pt>
+                <c:pt idx="136">
+                  <c:v>0.84847384691238004</c:v>
+                </c:pt>
+                <c:pt idx="137">
+                  <c:v>0.84593021869659002</c:v>
+                </c:pt>
+                <c:pt idx="138">
+                  <c:v>0.85247093439101995</c:v>
+                </c:pt>
+                <c:pt idx="139">
+                  <c:v>0.85283428430556996</c:v>
+                </c:pt>
+                <c:pt idx="140">
+                  <c:v>0.84811043739319003</c:v>
+                </c:pt>
+                <c:pt idx="141">
+                  <c:v>0.84265989065169999</c:v>
+                </c:pt>
+                <c:pt idx="142">
+                  <c:v>0.84702032804489003</c:v>
+                </c:pt>
+                <c:pt idx="143">
+                  <c:v>0.85646802186965998</c:v>
+                </c:pt>
+                <c:pt idx="144">
+                  <c:v>0.85574126243590998</c:v>
+                </c:pt>
+                <c:pt idx="145">
+                  <c:v>0.85610467195510997</c:v>
+                </c:pt>
+                <c:pt idx="146">
+                  <c:v>0.83611917495728005</c:v>
+                </c:pt>
+                <c:pt idx="147">
+                  <c:v>0.85792154073714999</c:v>
+                </c:pt>
+                <c:pt idx="148">
+                  <c:v>0.84883719682693004</c:v>
+                </c:pt>
+                <c:pt idx="149">
+                  <c:v>0.84992730617523005</c:v>
+                </c:pt>
+                <c:pt idx="150">
+                  <c:v>0.85574126243590998</c:v>
+                </c:pt>
+                <c:pt idx="151">
+                  <c:v>0.85029071569443004</c:v>
+                </c:pt>
+                <c:pt idx="152">
+                  <c:v>0.84447675943375</c:v>
+                </c:pt>
+                <c:pt idx="153">
+                  <c:v>0.84774708747864003</c:v>
+                </c:pt>
+                <c:pt idx="154">
+                  <c:v>0.85210758447646995</c:v>
+                </c:pt>
+                <c:pt idx="155">
+                  <c:v>0.86082845926285001</c:v>
+                </c:pt>
+                <c:pt idx="156">
+                  <c:v>0.85065406560898005</c:v>
+                </c:pt>
+                <c:pt idx="157">
+                  <c:v>0.85828489065169999</c:v>
+                </c:pt>
+                <c:pt idx="158">
+                  <c:v>0.85428780317306996</c:v>
+                </c:pt>
+                <c:pt idx="159">
+                  <c:v>0.85973834991455</c:v>
+                </c:pt>
+                <c:pt idx="160">
+                  <c:v>0.85065406560898005</c:v>
+                </c:pt>
+                <c:pt idx="161">
+                  <c:v>0.85174417495728005</c:v>
+                </c:pt>
+                <c:pt idx="162">
+                  <c:v>0.84920060634613004</c:v>
+                </c:pt>
+                <c:pt idx="163">
+                  <c:v>0.85683137178420998</c:v>
+                </c:pt>
+                <c:pt idx="164">
+                  <c:v>0.85683137178420998</c:v>
+                </c:pt>
+                <c:pt idx="165">
+                  <c:v>0.85501456260680997</c:v>
+                </c:pt>
+                <c:pt idx="166">
+                  <c:v>0.84738373756409002</c:v>
+                </c:pt>
+                <c:pt idx="167">
+                  <c:v>0.85065406560898005</c:v>
+                </c:pt>
+                <c:pt idx="168">
+                  <c:v>0.85428780317306996</c:v>
+                </c:pt>
+                <c:pt idx="169">
+                  <c:v>0.85864824056625</c:v>
+                </c:pt>
+                <c:pt idx="170">
+                  <c:v>0.85174417495728005</c:v>
+                </c:pt>
+                <c:pt idx="171">
+                  <c:v>0.85683137178420998</c:v>
+                </c:pt>
+                <c:pt idx="172">
+                  <c:v>0.84847384691238004</c:v>
+                </c:pt>
+                <c:pt idx="173">
+                  <c:v>0.85101741552353005</c:v>
+                </c:pt>
+                <c:pt idx="174">
+                  <c:v>0.85283428430556996</c:v>
+                </c:pt>
+                <c:pt idx="175">
+                  <c:v>0.85719478130340998</c:v>
+                </c:pt>
+                <c:pt idx="176">
+                  <c:v>0.84774708747864003</c:v>
+                </c:pt>
+                <c:pt idx="177">
+                  <c:v>0.86046510934830001</c:v>
+                </c:pt>
+                <c:pt idx="178">
+                  <c:v>0.83284884691238004</c:v>
+                </c:pt>
+                <c:pt idx="179">
+                  <c:v>0.85210758447646995</c:v>
+                </c:pt>
+                <c:pt idx="180">
+                  <c:v>0.84593021869659002</c:v>
+                </c:pt>
+                <c:pt idx="181">
+                  <c:v>0.85501456260680997</c:v>
+                </c:pt>
+                <c:pt idx="182">
+                  <c:v>0.86155521869659002</c:v>
+                </c:pt>
+                <c:pt idx="183">
+                  <c:v>0.85392439365386996</c:v>
+                </c:pt>
+                <c:pt idx="184">
+                  <c:v>0.85792154073714999</c:v>
+                </c:pt>
+                <c:pt idx="185">
+                  <c:v>0.85610467195510997</c:v>
+                </c:pt>
+                <c:pt idx="186">
+                  <c:v>0.84629362821579002</c:v>
+                </c:pt>
+                <c:pt idx="187">
+                  <c:v>0.85501456260680997</c:v>
+                </c:pt>
+                <c:pt idx="188">
+                  <c:v>0.85610467195510997</c:v>
+                </c:pt>
+                <c:pt idx="189">
+                  <c:v>0.85428780317306996</c:v>
+                </c:pt>
+                <c:pt idx="190">
+                  <c:v>0.85247093439101995</c:v>
+                </c:pt>
+                <c:pt idx="191">
+                  <c:v>0.84556686878204002</c:v>
+                </c:pt>
+                <c:pt idx="192">
+                  <c:v>0.85574126243590998</c:v>
+                </c:pt>
+                <c:pt idx="193">
+                  <c:v>0.84593021869659002</c:v>
+                </c:pt>
+                <c:pt idx="194">
+                  <c:v>0.84811043739319003</c:v>
+                </c:pt>
+                <c:pt idx="195">
+                  <c:v>0.85101741552353005</c:v>
+                </c:pt>
+                <c:pt idx="196">
+                  <c:v>0.85065406560898005</c:v>
+                </c:pt>
+                <c:pt idx="197">
+                  <c:v>0.85755813121795998</c:v>
+                </c:pt>
+                <c:pt idx="198">
+                  <c:v>0.85828489065169999</c:v>
+                </c:pt>
+                <c:pt idx="199">
+                  <c:v>0.86300873756409002</c:v>
+                </c:pt>
+                <c:pt idx="200">
+                  <c:v>0.86446219682693004</c:v>
+                </c:pt>
+                <c:pt idx="201">
+                  <c:v>0.86591571569443004</c:v>
+                </c:pt>
+                <c:pt idx="202">
+                  <c:v>0.85828489065169999</c:v>
+                </c:pt>
+                <c:pt idx="203">
+                  <c:v>0.85864824056625</c:v>
+                </c:pt>
+                <c:pt idx="204">
+                  <c:v>0.86809593439101995</c:v>
+                </c:pt>
+                <c:pt idx="205">
+                  <c:v>0.86409884691238004</c:v>
+                </c:pt>
+                <c:pt idx="206">
+                  <c:v>0.85101741552353005</c:v>
+                </c:pt>
+                <c:pt idx="207">
+                  <c:v>0.86700582504271995</c:v>
+                </c:pt>
+                <c:pt idx="208">
+                  <c:v>0.87136626243590998</c:v>
+                </c:pt>
+                <c:pt idx="209">
+                  <c:v>0.85864824056625</c:v>
+                </c:pt>
+                <c:pt idx="210">
+                  <c:v>0.86446219682693004</c:v>
+                </c:pt>
+                <c:pt idx="211">
+                  <c:v>0.86482560634613004</c:v>
+                </c:pt>
+                <c:pt idx="212">
+                  <c:v>0.84883719682693004</c:v>
+                </c:pt>
+                <c:pt idx="213">
+                  <c:v>0.86155521869659002</c:v>
+                </c:pt>
+                <c:pt idx="214">
+                  <c:v>0.85719478130340998</c:v>
+                </c:pt>
+                <c:pt idx="215">
+                  <c:v>0.85646802186965998</c:v>
+                </c:pt>
+                <c:pt idx="216">
+                  <c:v>0.86482560634613004</c:v>
+                </c:pt>
+                <c:pt idx="217">
+                  <c:v>0.86809593439101995</c:v>
+                </c:pt>
+                <c:pt idx="218">
+                  <c:v>0.86046510934830001</c:v>
+                </c:pt>
+                <c:pt idx="219">
+                  <c:v>0.86482560634613004</c:v>
+                </c:pt>
+                <c:pt idx="220">
+                  <c:v>0.86809593439101995</c:v>
+                </c:pt>
+                <c:pt idx="221">
+                  <c:v>0.86446219682693004</c:v>
+                </c:pt>
+                <c:pt idx="222">
+                  <c:v>0.86700582504271995</c:v>
+                </c:pt>
+                <c:pt idx="223">
+                  <c:v>0.85683137178420998</c:v>
+                </c:pt>
+                <c:pt idx="224">
+                  <c:v>0.87463665008545</c:v>
+                </c:pt>
+                <c:pt idx="225">
+                  <c:v>0.86954939365386996</c:v>
+                </c:pt>
+                <c:pt idx="226">
+                  <c:v>0.86191862821579002</c:v>
+                </c:pt>
+                <c:pt idx="227">
+                  <c:v>0.86482560634613004</c:v>
+                </c:pt>
+                <c:pt idx="228">
+                  <c:v>0.86700582504271995</c:v>
+                </c:pt>
+                <c:pt idx="229">
+                  <c:v>0.86010175943375</c:v>
+                </c:pt>
+                <c:pt idx="230">
+                  <c:v>0.85901165008545</c:v>
+                </c:pt>
+                <c:pt idx="231">
+                  <c:v>0.85901165008545</c:v>
+                </c:pt>
+                <c:pt idx="232">
+                  <c:v>0.86555230617523005</c:v>
+                </c:pt>
+                <c:pt idx="233">
+                  <c:v>0.86918604373931996</c:v>
+                </c:pt>
+                <c:pt idx="234">
+                  <c:v>0.86482560634613004</c:v>
+                </c:pt>
+                <c:pt idx="235">
+                  <c:v>0.85901165008545</c:v>
+                </c:pt>
+                <c:pt idx="236">
+                  <c:v>0.86700582504271995</c:v>
+                </c:pt>
+                <c:pt idx="237">
+                  <c:v>0.86191862821579002</c:v>
+                </c:pt>
+                <c:pt idx="238">
+                  <c:v>0.84883719682693004</c:v>
+                </c:pt>
+                <c:pt idx="239">
+                  <c:v>0.85755813121795998</c:v>
+                </c:pt>
+                <c:pt idx="240">
+                  <c:v>0.86119186878204002</c:v>
+                </c:pt>
+                <c:pt idx="241">
+                  <c:v>0.86446219682693004</c:v>
+                </c:pt>
+                <c:pt idx="242">
+                  <c:v>0.87209302186965998</c:v>
+                </c:pt>
+                <c:pt idx="243">
+                  <c:v>0.86736917495728005</c:v>
+                </c:pt>
+                <c:pt idx="244">
+                  <c:v>0.84229654073714999</c:v>
+                </c:pt>
+                <c:pt idx="245">
+                  <c:v>0.86119186878204002</c:v>
+                </c:pt>
+                <c:pt idx="246">
+                  <c:v>0.85901165008545</c:v>
+                </c:pt>
+                <c:pt idx="247">
+                  <c:v>0.86409884691238004</c:v>
+                </c:pt>
+                <c:pt idx="248">
+                  <c:v>0.86809593439101995</c:v>
+                </c:pt>
+                <c:pt idx="249">
+                  <c:v>0.86010175943375</c:v>
+                </c:pt>
+                <c:pt idx="250">
+                  <c:v>0.86010175943375</c:v>
+                </c:pt>
+                <c:pt idx="251">
+                  <c:v>0.86773258447646995</c:v>
+                </c:pt>
+                <c:pt idx="252">
+                  <c:v>0.86046510934830001</c:v>
+                </c:pt>
+                <c:pt idx="253">
+                  <c:v>0.87863373756409002</c:v>
+                </c:pt>
+                <c:pt idx="254">
+                  <c:v>0.85537791252135997</c:v>
+                </c:pt>
+                <c:pt idx="255">
+                  <c:v>0.86845928430556996</c:v>
+                </c:pt>
+                <c:pt idx="256">
+                  <c:v>0.87390989065169999</c:v>
+                </c:pt>
+                <c:pt idx="257">
+                  <c:v>0.87936043739319003</c:v>
+                </c:pt>
+                <c:pt idx="258">
+                  <c:v>0.859375</c:v>
+                </c:pt>
+                <c:pt idx="259">
+                  <c:v>0.86845928430556996</c:v>
+                </c:pt>
+                <c:pt idx="260">
+                  <c:v>0.87754362821579002</c:v>
+                </c:pt>
+                <c:pt idx="261">
+                  <c:v>0.86591571569443004</c:v>
+                </c:pt>
+                <c:pt idx="262">
+                  <c:v>0.87463665008545</c:v>
+                </c:pt>
+                <c:pt idx="263">
+                  <c:v>0.88263082504271995</c:v>
+                </c:pt>
+                <c:pt idx="264">
+                  <c:v>0.87136626243590998</c:v>
+                </c:pt>
+                <c:pt idx="265">
+                  <c:v>0.87100291252135997</c:v>
+                </c:pt>
+                <c:pt idx="266">
+                  <c:v>0.87245637178420998</c:v>
+                </c:pt>
+                <c:pt idx="267">
+                  <c:v>0.87609010934830001</c:v>
+                </c:pt>
+                <c:pt idx="268">
+                  <c:v>0.86446219682693004</c:v>
+                </c:pt>
+                <c:pt idx="269">
+                  <c:v>0.87645345926285001</c:v>
+                </c:pt>
+                <c:pt idx="270">
+                  <c:v>0.87427324056625</c:v>
+                </c:pt>
+                <c:pt idx="271">
+                  <c:v>0.88045060634613004</c:v>
+                </c:pt>
+                <c:pt idx="272">
+                  <c:v>0.87100291252135997</c:v>
+                </c:pt>
+                <c:pt idx="273">
+                  <c:v>0.87390989065169999</c:v>
+                </c:pt>
+                <c:pt idx="274">
+                  <c:v>0.87681686878204002</c:v>
+                </c:pt>
+                <c:pt idx="275">
+                  <c:v>0.86773258447646995</c:v>
+                </c:pt>
+                <c:pt idx="276">
+                  <c:v>0.86518895626068004</c:v>
+                </c:pt>
+                <c:pt idx="277">
+                  <c:v>0.87027615308761996</c:v>
+                </c:pt>
+                <c:pt idx="278">
+                  <c:v>0.87354654073714999</c:v>
+                </c:pt>
+                <c:pt idx="279">
+                  <c:v>0.86300873756409002</c:v>
+                </c:pt>
+                <c:pt idx="280">
+                  <c:v>0.87754362821579002</c:v>
+                </c:pt>
+                <c:pt idx="281">
+                  <c:v>0.88045060634613004</c:v>
+                </c:pt>
+                <c:pt idx="282">
+                  <c:v>0.84375</c:v>
+                </c:pt>
+                <c:pt idx="283">
+                  <c:v>0.87209302186965998</c:v>
+                </c:pt>
+                <c:pt idx="284">
+                  <c:v>0.87609010934830001</c:v>
+                </c:pt>
+                <c:pt idx="285">
+                  <c:v>0.87100291252135997</c:v>
+                </c:pt>
+                <c:pt idx="286">
+                  <c:v>0.87790697813034002</c:v>
+                </c:pt>
+                <c:pt idx="287">
+                  <c:v>0.86918604373931996</c:v>
+                </c:pt>
+                <c:pt idx="288">
+                  <c:v>0.87572675943375</c:v>
+                </c:pt>
+                <c:pt idx="289">
+                  <c:v>0.88008719682693004</c:v>
+                </c:pt>
+                <c:pt idx="290">
+                  <c:v>0.87790697813034002</c:v>
+                </c:pt>
+                <c:pt idx="291">
+                  <c:v>0.87645345926285001</c:v>
+                </c:pt>
+                <c:pt idx="292">
+                  <c:v>0.87536334991455</c:v>
+                </c:pt>
+                <c:pt idx="293">
+                  <c:v>0.86918604373931996</c:v>
+                </c:pt>
+                <c:pt idx="294">
+                  <c:v>0.87645345926285001</c:v>
+                </c:pt>
+                <c:pt idx="295">
+                  <c:v>0.86809593439101995</c:v>
+                </c:pt>
+                <c:pt idx="296">
+                  <c:v>0.87572675943375</c:v>
+                </c:pt>
+                <c:pt idx="297">
+                  <c:v>0.86845928430556996</c:v>
+                </c:pt>
+                <c:pt idx="298">
+                  <c:v>0.87390989065169999</c:v>
+                </c:pt>
+                <c:pt idx="299">
+                  <c:v>0.87754362821579002</c:v>
+                </c:pt>
+                <c:pt idx="300">
+                  <c:v>0.86228197813034002</c:v>
+                </c:pt>
+                <c:pt idx="301">
+                  <c:v>0.87645345926285001</c:v>
+                </c:pt>
+                <c:pt idx="302">
+                  <c:v>0.86954939365386996</c:v>
+                </c:pt>
+                <c:pt idx="303">
+                  <c:v>0.88517439365386996</c:v>
+                </c:pt>
+                <c:pt idx="304">
+                  <c:v>0.88226741552353005</c:v>
+                </c:pt>
+                <c:pt idx="305">
+                  <c:v>0.87790697813034002</c:v>
+                </c:pt>
+                <c:pt idx="306">
+                  <c:v>0.87281978130340998</c:v>
+                </c:pt>
+                <c:pt idx="307">
+                  <c:v>0.87318313121795998</c:v>
+                </c:pt>
+                <c:pt idx="308">
+                  <c:v>0.87245637178420998</c:v>
+                </c:pt>
+                <c:pt idx="309">
+                  <c:v>0.86809593439101995</c:v>
+                </c:pt>
+                <c:pt idx="310">
+                  <c:v>0.87972384691238004</c:v>
+                </c:pt>
+                <c:pt idx="311">
+                  <c:v>0.87863373756409002</c:v>
+                </c:pt>
+                <c:pt idx="312">
+                  <c:v>0.87281978130340998</c:v>
+                </c:pt>
+                <c:pt idx="313">
+                  <c:v>0.87136626243590998</c:v>
+                </c:pt>
+                <c:pt idx="314">
+                  <c:v>0.87863373756409002</c:v>
+                </c:pt>
+                <c:pt idx="315">
+                  <c:v>0.87572675943375</c:v>
+                </c:pt>
+                <c:pt idx="316">
+                  <c:v>0.87827032804489003</c:v>
+                </c:pt>
+                <c:pt idx="317">
+                  <c:v>0.86373543739319003</c:v>
+                </c:pt>
+                <c:pt idx="318">
+                  <c:v>0.87609010934830001</c:v>
+                </c:pt>
+                <c:pt idx="319">
+                  <c:v>0.88117730617523005</c:v>
+                </c:pt>
+                <c:pt idx="320">
+                  <c:v>0.86845928430556996</c:v>
+                </c:pt>
+                <c:pt idx="321">
+                  <c:v>0.86845928430556996</c:v>
+                </c:pt>
+                <c:pt idx="322">
+                  <c:v>0.87899708747864003</c:v>
+                </c:pt>
+                <c:pt idx="323">
+                  <c:v>0.88481104373931996</c:v>
+                </c:pt>
+                <c:pt idx="324">
+                  <c:v>0.88372093439101995</c:v>
+                </c:pt>
+                <c:pt idx="325">
+                  <c:v>0.88444769382476995</c:v>
+                </c:pt>
+                <c:pt idx="326">
+                  <c:v>0.88408428430556996</c:v>
+                </c:pt>
+                <c:pt idx="327">
+                  <c:v>0.87609010934830001</c:v>
+                </c:pt>
+                <c:pt idx="328">
+                  <c:v>0.88335758447646995</c:v>
+                </c:pt>
+                <c:pt idx="329">
+                  <c:v>0.87827032804489003</c:v>
+                </c:pt>
+                <c:pt idx="330">
+                  <c:v>0.87245637178420998</c:v>
+                </c:pt>
+                <c:pt idx="331">
+                  <c:v>0.85392439365386996</c:v>
+                </c:pt>
+                <c:pt idx="332">
+                  <c:v>0.87936043739319003</c:v>
+                </c:pt>
+                <c:pt idx="333">
+                  <c:v>0.87172967195510997</c:v>
+                </c:pt>
+                <c:pt idx="334">
+                  <c:v>0.87609010934830001</c:v>
+                </c:pt>
+                <c:pt idx="335">
+                  <c:v>0.85501456260680997</c:v>
+                </c:pt>
+                <c:pt idx="336">
+                  <c:v>0.87245637178420998</c:v>
+                </c:pt>
+                <c:pt idx="337">
+                  <c:v>0.87790697813034002</c:v>
+                </c:pt>
+                <c:pt idx="338">
+                  <c:v>0.88553780317306996</c:v>
+                </c:pt>
+                <c:pt idx="339">
+                  <c:v>0.87718021869659002</c:v>
+                </c:pt>
+                <c:pt idx="340">
+                  <c:v>0.88299417495728005</c:v>
+                </c:pt>
+                <c:pt idx="341">
+                  <c:v>0.88517439365386996</c:v>
+                </c:pt>
+                <c:pt idx="342">
+                  <c:v>0.87172967195510997</c:v>
+                </c:pt>
+                <c:pt idx="343">
+                  <c:v>0.88553780317306996</c:v>
+                </c:pt>
+                <c:pt idx="344">
+                  <c:v>0.87936043739319003</c:v>
+                </c:pt>
+                <c:pt idx="345">
+                  <c:v>0.88372093439101995</c:v>
+                </c:pt>
+                <c:pt idx="346">
+                  <c:v>0.88299417495728005</c:v>
+                </c:pt>
+                <c:pt idx="347">
+                  <c:v>0.86845928430556996</c:v>
+                </c:pt>
+                <c:pt idx="348">
+                  <c:v>0.88335758447646995</c:v>
+                </c:pt>
+                <c:pt idx="349">
+                  <c:v>0.88335758447646995</c:v>
+                </c:pt>
+                <c:pt idx="350">
+                  <c:v>0.88880813121795998</c:v>
+                </c:pt>
+                <c:pt idx="351">
+                  <c:v>0.88335758447646995</c:v>
+                </c:pt>
+                <c:pt idx="352">
+                  <c:v>0.88880813121795998</c:v>
+                </c:pt>
+                <c:pt idx="353">
+                  <c:v>0.88662791252135997</c:v>
+                </c:pt>
+                <c:pt idx="354">
+                  <c:v>0.88662791252135997</c:v>
+                </c:pt>
+                <c:pt idx="355">
+                  <c:v>0.88190406560898005</c:v>
+                </c:pt>
+                <c:pt idx="356">
+                  <c:v>0.88917154073714999</c:v>
+                </c:pt>
+                <c:pt idx="357">
+                  <c:v>0.87536334991455</c:v>
+                </c:pt>
+                <c:pt idx="358">
+                  <c:v>0.88408428430556996</c:v>
+                </c:pt>
+                <c:pt idx="359">
+                  <c:v>0.87899708747864003</c:v>
+                </c:pt>
+                <c:pt idx="360">
+                  <c:v>0.88299417495728005</c:v>
+                </c:pt>
+                <c:pt idx="361">
+                  <c:v>0.87790697813034002</c:v>
+                </c:pt>
+                <c:pt idx="362">
+                  <c:v>0.87863373756409002</c:v>
+                </c:pt>
+                <c:pt idx="363">
+                  <c:v>0.88408428430556996</c:v>
+                </c:pt>
+                <c:pt idx="364">
+                  <c:v>0.88844478130340998</c:v>
+                </c:pt>
+                <c:pt idx="365">
+                  <c:v>0.88263082504271995</c:v>
+                </c:pt>
+                <c:pt idx="366">
+                  <c:v>0.88553780317306996</c:v>
+                </c:pt>
+                <c:pt idx="367">
+                  <c:v>0.87936043739319003</c:v>
+                </c:pt>
+                <c:pt idx="368">
+                  <c:v>0.87754362821579002</c:v>
+                </c:pt>
+                <c:pt idx="369">
+                  <c:v>0.88117730617523005</c:v>
+                </c:pt>
+                <c:pt idx="370">
+                  <c:v>0.88590115308761996</c:v>
+                </c:pt>
+                <c:pt idx="371">
+                  <c:v>0.88808137178420998</c:v>
+                </c:pt>
+                <c:pt idx="372">
+                  <c:v>0.88444769382476995</c:v>
+                </c:pt>
+                <c:pt idx="373">
+                  <c:v>0.88335758447646995</c:v>
+                </c:pt>
+                <c:pt idx="374">
+                  <c:v>0.88263082504271995</c:v>
+                </c:pt>
+                <c:pt idx="375">
+                  <c:v>0.87936043739319003</c:v>
+                </c:pt>
+                <c:pt idx="376">
+                  <c:v>0.89171510934830001</c:v>
+                </c:pt>
+                <c:pt idx="377">
+                  <c:v>0.88372093439101995</c:v>
+                </c:pt>
+                <c:pt idx="378">
+                  <c:v>0.88408428430556996</c:v>
+                </c:pt>
+                <c:pt idx="379">
+                  <c:v>0.89389532804489003</c:v>
+                </c:pt>
+                <c:pt idx="380">
+                  <c:v>0.87863373756409002</c:v>
+                </c:pt>
+                <c:pt idx="381">
+                  <c:v>0.88481104373931996</c:v>
+                </c:pt>
+                <c:pt idx="382">
+                  <c:v>0.87972384691238004</c:v>
+                </c:pt>
+                <c:pt idx="383">
+                  <c:v>0.88335758447646995</c:v>
+                </c:pt>
+                <c:pt idx="384">
+                  <c:v>0.88844478130340998</c:v>
+                </c:pt>
+                <c:pt idx="385">
+                  <c:v>0.88408428430556996</c:v>
+                </c:pt>
+                <c:pt idx="386">
+                  <c:v>0.87572675943375</c:v>
+                </c:pt>
+                <c:pt idx="387">
+                  <c:v>0.89026165008545</c:v>
+                </c:pt>
+                <c:pt idx="388">
+                  <c:v>0.88553780317306996</c:v>
+                </c:pt>
+                <c:pt idx="389">
+                  <c:v>0.88372093439101995</c:v>
+                </c:pt>
+                <c:pt idx="390">
+                  <c:v>0.89244186878204002</c:v>
+                </c:pt>
+                <c:pt idx="391">
+                  <c:v>0.88117730617523005</c:v>
+                </c:pt>
+                <c:pt idx="392">
+                  <c:v>0.88154071569443004</c:v>
+                </c:pt>
+                <c:pt idx="393">
+                  <c:v>0.88699126243590998</c:v>
+                </c:pt>
+                <c:pt idx="394">
+                  <c:v>0.88626456260680997</c:v>
+                </c:pt>
+                <c:pt idx="395">
+                  <c:v>0.88590115308761996</c:v>
+                </c:pt>
+                <c:pt idx="396">
+                  <c:v>0.88699126243590998</c:v>
+                </c:pt>
+                <c:pt idx="397">
+                  <c:v>0.88517439365386996</c:v>
+                </c:pt>
+                <c:pt idx="398">
+                  <c:v>0.89244186878204002</c:v>
+                </c:pt>
+                <c:pt idx="399">
+                  <c:v>0.89026165008545</c:v>
+                </c:pt>
+                <c:pt idx="400">
+                  <c:v>0.89135175943375</c:v>
+                </c:pt>
+                <c:pt idx="401">
+                  <c:v>0.88626456260680997</c:v>
+                </c:pt>
+                <c:pt idx="402">
+                  <c:v>0.88735467195510997</c:v>
+                </c:pt>
+                <c:pt idx="403">
+                  <c:v>0.88735467195510997</c:v>
+                </c:pt>
+                <c:pt idx="404">
+                  <c:v>0.89353197813034002</c:v>
+                </c:pt>
+                <c:pt idx="405">
+                  <c:v>0.88263082504271995</c:v>
+                </c:pt>
+                <c:pt idx="406">
+                  <c:v>0.87281978130340998</c:v>
+                </c:pt>
+                <c:pt idx="407">
+                  <c:v>0.88154071569443004</c:v>
+                </c:pt>
+                <c:pt idx="408">
+                  <c:v>0.88808137178420998</c:v>
+                </c:pt>
+                <c:pt idx="409">
+                  <c:v>0.88190406560898005</c:v>
+                </c:pt>
+                <c:pt idx="410">
+                  <c:v>0.88626456260680997</c:v>
+                </c:pt>
+                <c:pt idx="411">
+                  <c:v>0.89244186878204002</c:v>
+                </c:pt>
+                <c:pt idx="412">
+                  <c:v>0.88335758447646995</c:v>
+                </c:pt>
+                <c:pt idx="413">
+                  <c:v>0.88335758447646995</c:v>
+                </c:pt>
+                <c:pt idx="414">
+                  <c:v>0.89026165008545</c:v>
+                </c:pt>
+                <c:pt idx="415">
+                  <c:v>0.88626456260680997</c:v>
+                </c:pt>
+                <c:pt idx="416">
+                  <c:v>0.89135175943375</c:v>
+                </c:pt>
+                <c:pt idx="417">
+                  <c:v>0.89207845926285001</c:v>
+                </c:pt>
+                <c:pt idx="418">
+                  <c:v>0.87863373756409002</c:v>
+                </c:pt>
+                <c:pt idx="419">
+                  <c:v>0.89316862821579002</c:v>
+                </c:pt>
+                <c:pt idx="420">
+                  <c:v>0.88989824056625</c:v>
+                </c:pt>
+                <c:pt idx="421">
+                  <c:v>0.890625</c:v>
+                </c:pt>
+                <c:pt idx="422">
+                  <c:v>0.88117730617523005</c:v>
+                </c:pt>
+                <c:pt idx="423">
+                  <c:v>0.89462208747864003</c:v>
+                </c:pt>
+                <c:pt idx="424">
+                  <c:v>0.88263082504271995</c:v>
+                </c:pt>
+                <c:pt idx="425">
+                  <c:v>0.89425873756409002</c:v>
+                </c:pt>
+                <c:pt idx="426">
+                  <c:v>0.87936043739319003</c:v>
+                </c:pt>
+                <c:pt idx="427">
+                  <c:v>0.88917154073714999</c:v>
+                </c:pt>
+                <c:pt idx="428">
+                  <c:v>0.88699126243590998</c:v>
+                </c:pt>
+                <c:pt idx="429">
+                  <c:v>0.89462208747864003</c:v>
+                </c:pt>
+                <c:pt idx="430">
+                  <c:v>0.88263082504271995</c:v>
+                </c:pt>
+                <c:pt idx="431">
+                  <c:v>0.88299417495728005</c:v>
+                </c:pt>
+                <c:pt idx="432">
+                  <c:v>0.88481104373931996</c:v>
+                </c:pt>
+                <c:pt idx="433">
+                  <c:v>0.88917154073714999</c:v>
+                </c:pt>
+                <c:pt idx="434">
+                  <c:v>0.88953489065169999</c:v>
+                </c:pt>
+                <c:pt idx="435">
+                  <c:v>0.89789241552353005</c:v>
+                </c:pt>
+                <c:pt idx="436">
+                  <c:v>0.89353197813034002</c:v>
+                </c:pt>
+                <c:pt idx="437">
+                  <c:v>0.88917154073714999</c:v>
+                </c:pt>
+                <c:pt idx="438">
+                  <c:v>0.88699126243590998</c:v>
+                </c:pt>
+                <c:pt idx="439">
+                  <c:v>0.890625</c:v>
+                </c:pt>
+                <c:pt idx="440">
+                  <c:v>0.88808137178420998</c:v>
+                </c:pt>
+                <c:pt idx="441">
+                  <c:v>0.89280521869659002</c:v>
+                </c:pt>
+                <c:pt idx="442">
+                  <c:v>0.88844478130340998</c:v>
+                </c:pt>
+                <c:pt idx="443">
+                  <c:v>0.88917154073714999</c:v>
+                </c:pt>
+                <c:pt idx="444">
+                  <c:v>0.89389532804489003</c:v>
+                </c:pt>
+                <c:pt idx="445">
+                  <c:v>0.89643895626068004</c:v>
+                </c:pt>
+                <c:pt idx="446">
+                  <c:v>0.88953489065169999</c:v>
+                </c:pt>
+                <c:pt idx="447">
+                  <c:v>0.89244186878204002</c:v>
+                </c:pt>
+                <c:pt idx="448">
+                  <c:v>0.88226741552353005</c:v>
+                </c:pt>
+                <c:pt idx="449">
+                  <c:v>0.88408428430556996</c:v>
+                </c:pt>
+                <c:pt idx="450">
+                  <c:v>0.88808137178420998</c:v>
+                </c:pt>
+                <c:pt idx="451">
+                  <c:v>0.89680230617523005</c:v>
+                </c:pt>
+                <c:pt idx="452">
+                  <c:v>0.890625</c:v>
+                </c:pt>
+                <c:pt idx="453">
+                  <c:v>0.88953489065169999</c:v>
+                </c:pt>
+                <c:pt idx="454">
+                  <c:v>0.89789241552353005</c:v>
+                </c:pt>
+                <c:pt idx="455">
+                  <c:v>0.88662791252135997</c:v>
+                </c:pt>
+                <c:pt idx="456">
+                  <c:v>0.88226741552353005</c:v>
+                </c:pt>
+                <c:pt idx="457">
+                  <c:v>0.88917154073714999</c:v>
+                </c:pt>
+                <c:pt idx="458">
+                  <c:v>0.88335758447646995</c:v>
+                </c:pt>
+                <c:pt idx="459">
+                  <c:v>0.88917154073714999</c:v>
+                </c:pt>
+                <c:pt idx="460">
+                  <c:v>0.88917154073714999</c:v>
+                </c:pt>
+                <c:pt idx="461">
+                  <c:v>0.89135175943375</c:v>
+                </c:pt>
+                <c:pt idx="462">
+                  <c:v>0.89571219682693004</c:v>
+                </c:pt>
+                <c:pt idx="463">
+                  <c:v>0.89244186878204002</c:v>
+                </c:pt>
+                <c:pt idx="464">
+                  <c:v>0.89389532804489003</c:v>
+                </c:pt>
+                <c:pt idx="465">
+                  <c:v>0.89316862821579002</c:v>
+                </c:pt>
+                <c:pt idx="466">
+                  <c:v>0.89970928430556996</c:v>
+                </c:pt>
+                <c:pt idx="467">
+                  <c:v>0.87936043739319003</c:v>
+                </c:pt>
+                <c:pt idx="468">
+                  <c:v>0.89462208747864003</c:v>
+                </c:pt>
+                <c:pt idx="469">
+                  <c:v>0.88880813121795998</c:v>
+                </c:pt>
+                <c:pt idx="470">
+                  <c:v>0.88917154073714999</c:v>
+                </c:pt>
+                <c:pt idx="471">
+                  <c:v>0.89462208747864003</c:v>
+                </c:pt>
+                <c:pt idx="472">
+                  <c:v>0.89861917495728005</c:v>
+                </c:pt>
+                <c:pt idx="473">
+                  <c:v>0.89316862821579002</c:v>
+                </c:pt>
+                <c:pt idx="474">
+                  <c:v>0.89970928430556996</c:v>
+                </c:pt>
+                <c:pt idx="475">
+                  <c:v>0.89680230617523005</c:v>
+                </c:pt>
+                <c:pt idx="476">
+                  <c:v>0.89825582504271995</c:v>
+                </c:pt>
+                <c:pt idx="477">
+                  <c:v>0.89789241552353005</c:v>
+                </c:pt>
+                <c:pt idx="478">
+                  <c:v>0.89171510934830001</c:v>
+                </c:pt>
+                <c:pt idx="479">
+                  <c:v>0.89389532804489003</c:v>
+                </c:pt>
+                <c:pt idx="480">
+                  <c:v>0.89244186878204002</c:v>
+                </c:pt>
+                <c:pt idx="481">
+                  <c:v>0.88481104373931996</c:v>
+                </c:pt>
+                <c:pt idx="482">
+                  <c:v>0.88808137178420998</c:v>
+                </c:pt>
+                <c:pt idx="483">
+                  <c:v>0.88917154073714999</c:v>
+                </c:pt>
+                <c:pt idx="484">
+                  <c:v>0.88989824056625</c:v>
+                </c:pt>
+                <c:pt idx="485">
+                  <c:v>0.89389532804489003</c:v>
+                </c:pt>
+                <c:pt idx="486">
+                  <c:v>0.88989824056625</c:v>
+                </c:pt>
+                <c:pt idx="487">
+                  <c:v>0.89462208747864003</c:v>
+                </c:pt>
+                <c:pt idx="488">
+                  <c:v>0.88917154073714999</c:v>
+                </c:pt>
+                <c:pt idx="489">
+                  <c:v>0.89571219682693004</c:v>
+                </c:pt>
+                <c:pt idx="490">
+                  <c:v>0.90007269382476995</c:v>
+                </c:pt>
+                <c:pt idx="491">
+                  <c:v>0.89425873756409002</c:v>
+                </c:pt>
+                <c:pt idx="492">
+                  <c:v>0.89571219682693004</c:v>
+                </c:pt>
+                <c:pt idx="493">
+                  <c:v>0.89716571569443004</c:v>
+                </c:pt>
+                <c:pt idx="494">
+                  <c:v>0.89534884691238004</c:v>
+                </c:pt>
+                <c:pt idx="495">
+                  <c:v>0.89898258447646995</c:v>
+                </c:pt>
+                <c:pt idx="496">
+                  <c:v>0.89135175943375</c:v>
+                </c:pt>
+                <c:pt idx="497">
+                  <c:v>0.89498543739319003</c:v>
+                </c:pt>
+                <c:pt idx="498">
+                  <c:v>0.90079939365386996</c:v>
+                </c:pt>
+                <c:pt idx="499">
+                  <c:v>0.89462208747864003</c:v>
+                </c:pt>
+                <c:pt idx="502">
+                  <c:v>0</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="1"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-DAE7-4FC7-A5AE-38F16B2E86C9}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="393590320"/>
+        <c:axId val="393592720"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="393590320"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+          <c:max val="499"/>
+          <c:min val="0"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="pt-BR" sz="1800" b="0"/>
+                  <a:t>Epochs</a:t>
+                </a:r>
+                <a:endParaRPr lang="pt-BR" sz="1400" b="0"/>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="pt-BR"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="pt-BR"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="393592720"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+        <c:majorUnit val="50"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="393592720"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="pt-BR" sz="1800" b="0"/>
+                  <a:t>Accuracy</a:t>
+                </a:r>
+                <a:r>
+                  <a:rPr lang="pt-BR" sz="1600" b="1" baseline="0"/>
+                  <a:t> (%)</a:t>
+                </a:r>
+                <a:endParaRPr lang="pt-BR" sz="1600" b="1"/>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="pt-BR"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="pt-BR"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="393590320"/>
+        <c:crossesAt val="1"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1800" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="pt-BR"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="pt-BR"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.78740157499999996" l="0.511811024" r="0.511811024" t="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart7.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="pt-BR"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="pt-BR" sz="1600" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:sysClr val="windowText" lastClr="000000">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:sysClr>
+                </a:solidFill>
+              </a:rPr>
+              <a:t>Loss curve: ResNet-34, Batch size = 32</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="pt-BR"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:scatterChart>
+        <c:scatterStyle val="smoothMarker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Worksheet!$C$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>loss</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:yVal>
+            <c:numRef>
+              <c:f>Worksheet!$C$2:$C$504</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="503"/>
+                <c:pt idx="0">
+                  <c:v>1.8220196962357</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1.7997058629989999</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1.7869668006896999</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1.7759485244751001</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>1.7629615068436</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>1.7518621683121001</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>1.7384128570557</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>1.7271283864975</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>1.7142506837845</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>1.6977368593216</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>1.6804370880127</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>1.6648204326630001</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>1.6451563835144001</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>1.6208641529083001</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>1.5674746036530001</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>1.5226591825485001</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>1.5041618347168</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>1.4726291894913</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>1.4703197479248</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>1.4524062871932999</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>1.4188872575760001</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>1.3888722658157</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>1.3790192604064999</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>1.3420342206955</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>1.3238011598587001</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>1.2937625646591</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>1.2678511142730999</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>1.2424060106277</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>1.2251121997833001</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>1.2208513021469001</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>1.1439685821533001</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>1.1077009439468</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>1.0961918830871999</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>1.0996718406677</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>1.0918389558792001</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>1.0797024965286</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>1.0764714479446</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>1.0640420913696</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>1.0677284002303999</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>1.0596046447754</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>1.0586481094360001</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>1.0585805177689001</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>1.0558408498764</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>1.0485858917235999</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>1.0395900011063</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>1.0364444255829</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>1.031626701355</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>1.021345615387</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>1.0291260480880999</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>1.0148215293884</c:v>
+                </c:pt>
+                <c:pt idx="50">
+                  <c:v>1.0202832221985001</c:v>
+                </c:pt>
+                <c:pt idx="51">
+                  <c:v>1.0192431211471999</c:v>
+                </c:pt>
+                <c:pt idx="52">
+                  <c:v>1.0116021633148</c:v>
+                </c:pt>
+                <c:pt idx="53">
+                  <c:v>1.0019013881683001</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>1.0050724744796999</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>1.0049693584442001</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>0.99860244989394997</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>0.99219703674315995</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>0.99838870763778997</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>0.99047034978866999</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>0.97003513574599998</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>0.96273803710938</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>0.95237195491791005</c:v>
+                </c:pt>
+                <c:pt idx="63">
+                  <c:v>0.95774883031845004</c:v>
+                </c:pt>
+                <c:pt idx="64">
+                  <c:v>0.95095217227936002</c:v>
+                </c:pt>
+                <c:pt idx="65">
+                  <c:v>0.95320218801498002</c:v>
+                </c:pt>
+                <c:pt idx="66">
+                  <c:v>0.95766872167587003</c:v>
+                </c:pt>
+                <c:pt idx="67">
+                  <c:v>0.94849061965942005</c:v>
+                </c:pt>
+                <c:pt idx="68">
+                  <c:v>0.94718885421752996</c:v>
+                </c:pt>
+                <c:pt idx="69">
+                  <c:v>0.94749629497527998</c:v>
+                </c:pt>
+                <c:pt idx="70">
+                  <c:v>0.94381606578827004</c:v>
+                </c:pt>
+                <c:pt idx="71">
+                  <c:v>0.94294840097427002</c:v>
+                </c:pt>
+                <c:pt idx="72">
+                  <c:v>0.94340324401855002</c:v>
+                </c:pt>
+                <c:pt idx="73">
+                  <c:v>0.94978964328766002</c:v>
+                </c:pt>
+                <c:pt idx="74">
+                  <c:v>0.94966006278991999</c:v>
+                </c:pt>
+                <c:pt idx="75">
+                  <c:v>0.93902522325516002</c:v>
+                </c:pt>
+                <c:pt idx="76">
+                  <c:v>0.94536149501801003</c:v>
+                </c:pt>
+                <c:pt idx="77">
+                  <c:v>0.94117099046706998</c:v>
+                </c:pt>
+                <c:pt idx="78">
+                  <c:v>0.95298004150391002</c:v>
+                </c:pt>
+                <c:pt idx="79">
+                  <c:v>0.94366699457169001</c:v>
+                </c:pt>
+                <c:pt idx="80">
+                  <c:v>0.94172418117523005</c:v>
+                </c:pt>
+                <c:pt idx="81">
+                  <c:v>0.93779116868973</c:v>
+                </c:pt>
+                <c:pt idx="82">
+                  <c:v>0.94177985191345004</c:v>
+                </c:pt>
+                <c:pt idx="83">
+                  <c:v>0.94156479835509999</c:v>
+                </c:pt>
+                <c:pt idx="84">
+                  <c:v>0.93494594097136996</c:v>
+                </c:pt>
+                <c:pt idx="85">
+                  <c:v>0.93493121862410999</c:v>
+                </c:pt>
+                <c:pt idx="86">
+                  <c:v>0.93674916028975996</c:v>
+                </c:pt>
+                <c:pt idx="87">
+                  <c:v>0.93659788370132002</c:v>
+                </c:pt>
+                <c:pt idx="88">
+                  <c:v>0.93648904561996005</c:v>
+                </c:pt>
+                <c:pt idx="89">
+                  <c:v>0.93023079633713002</c:v>
+                </c:pt>
+                <c:pt idx="90">
+                  <c:v>0.93807184696197998</c:v>
+                </c:pt>
+                <c:pt idx="91">
+                  <c:v>0.93844091892241999</c:v>
+                </c:pt>
+                <c:pt idx="92">
+                  <c:v>0.92943626642226995</c:v>
+                </c:pt>
+                <c:pt idx="93">
+                  <c:v>0.93453425168991</c:v>
+                </c:pt>
+                <c:pt idx="94">
+                  <c:v>0.93148839473723999</c:v>
+                </c:pt>
+                <c:pt idx="95">
+                  <c:v>0.93840622901917004</c:v>
+                </c:pt>
+                <c:pt idx="96">
+                  <c:v>0.92672622203827004</c:v>
+                </c:pt>
+                <c:pt idx="97">
+                  <c:v>0.92590487003326005</c:v>
+                </c:pt>
+                <c:pt idx="98">
+                  <c:v>0.92646354436874001</c:v>
+                </c:pt>
+                <c:pt idx="99">
+                  <c:v>0.92315030097961004</c:v>
+                </c:pt>
+                <c:pt idx="100">
+                  <c:v>0.92425185441971003</c:v>
+                </c:pt>
+                <c:pt idx="101">
+                  <c:v>0.93579536676407005</c:v>
+                </c:pt>
+                <c:pt idx="102">
+                  <c:v>0.92528915405273005</c:v>
+                </c:pt>
+                <c:pt idx="103">
+                  <c:v>0.92892414331436002</c:v>
+                </c:pt>
+                <c:pt idx="104">
+                  <c:v>0.93087232112884999</c:v>
+                </c:pt>
+                <c:pt idx="105">
+                  <c:v>0.92467176914214999</c:v>
+                </c:pt>
+                <c:pt idx="106">
+                  <c:v>0.92565852403641002</c:v>
+                </c:pt>
+                <c:pt idx="107">
+                  <c:v>0.91906887292862005</c:v>
+                </c:pt>
+                <c:pt idx="108">
+                  <c:v>0.92220216989517001</c:v>
+                </c:pt>
+                <c:pt idx="109">
+                  <c:v>0.92439061403275002</c:v>
+                </c:pt>
+                <c:pt idx="110">
+                  <c:v>0.92261826992035001</c:v>
+                </c:pt>
+                <c:pt idx="111">
+                  <c:v>0.91444498300552002</c:v>
+                </c:pt>
+                <c:pt idx="112">
+                  <c:v>0.92282289266586004</c:v>
+                </c:pt>
+                <c:pt idx="113">
+                  <c:v>0.92065769433974998</c:v>
+                </c:pt>
+                <c:pt idx="114">
+                  <c:v>0.91958683729171997</c:v>
+                </c:pt>
+                <c:pt idx="115">
+                  <c:v>0.91852867603302002</c:v>
+                </c:pt>
+                <c:pt idx="116">
+                  <c:v>0.91561734676360995</c:v>
+                </c:pt>
+                <c:pt idx="117">
+                  <c:v>0.91597080230713002</c:v>
+                </c:pt>
+                <c:pt idx="118">
+                  <c:v>0.91572695970535001</c:v>
+                </c:pt>
+                <c:pt idx="119">
+                  <c:v>0.92140626907348999</c:v>
+                </c:pt>
+                <c:pt idx="120">
+                  <c:v>0.91679507493973</c:v>
+                </c:pt>
+                <c:pt idx="121">
+                  <c:v>0.91232997179030995</c:v>
+                </c:pt>
+                <c:pt idx="122">
+                  <c:v>0.91025590896606001</c:v>
+                </c:pt>
+                <c:pt idx="123">
+                  <c:v>0.91542041301726995</c:v>
+                </c:pt>
+                <c:pt idx="124">
+                  <c:v>0.91263306140900002</c:v>
+                </c:pt>
+                <c:pt idx="125">
+                  <c:v>0.90867882966994995</c:v>
+                </c:pt>
+                <c:pt idx="126">
+                  <c:v>0.91307079792023005</c:v>
+                </c:pt>
+                <c:pt idx="127">
+                  <c:v>0.90852892398833995</c:v>
+                </c:pt>
+                <c:pt idx="128">
+                  <c:v>0.91323029994964999</c:v>
+                </c:pt>
+                <c:pt idx="129">
+                  <c:v>0.91602152585982999</c:v>
+                </c:pt>
+                <c:pt idx="130">
+                  <c:v>0.91328066587447998</c:v>
+                </c:pt>
+                <c:pt idx="131">
+                  <c:v>0.91155195236205999</c:v>
+                </c:pt>
+                <c:pt idx="132">
+                  <c:v>0.90747863054276001</c:v>
+                </c:pt>
+                <c:pt idx="133">
+                  <c:v>0.90225255489348999</c:v>
+                </c:pt>
+                <c:pt idx="134">
+                  <c:v>0.90189307928085005</c:v>
+                </c:pt>
+                <c:pt idx="135">
+                  <c:v>0.91688519716262995</c:v>
+                </c:pt>
+                <c:pt idx="136">
+                  <c:v>0.91097360849380005</c:v>
+                </c:pt>
+                <c:pt idx="137">
+                  <c:v>0.90885871648787997</c:v>
+                </c:pt>
+                <c:pt idx="138">
+                  <c:v>0.90276789665222001</c:v>
+                </c:pt>
+                <c:pt idx="139">
+                  <c:v>0.90985739231109997</c:v>
+                </c:pt>
+                <c:pt idx="140">
+                  <c:v>0.90744960308074996</c:v>
+                </c:pt>
+                <c:pt idx="141">
+                  <c:v>0.90011453628539995</c:v>
+                </c:pt>
+                <c:pt idx="142">
+                  <c:v>0.90019720792769997</c:v>
+                </c:pt>
+                <c:pt idx="143">
+                  <c:v>0.89979416131973</c:v>
+                </c:pt>
+                <c:pt idx="144">
+                  <c:v>0.89967334270476995</c:v>
+                </c:pt>
+                <c:pt idx="145">
+                  <c:v>0.90481275320053001</c:v>
+                </c:pt>
+                <c:pt idx="146">
+                  <c:v>0.90243858098983998</c:v>
+                </c:pt>
+                <c:pt idx="147">
+                  <c:v>0.89601951837539995</c:v>
+                </c:pt>
+                <c:pt idx="148">
+                  <c:v>0.89788597822188998</c:v>
+                </c:pt>
+                <c:pt idx="149">
+                  <c:v>0.90167868137359997</c:v>
+                </c:pt>
+                <c:pt idx="150">
+                  <c:v>0.90005677938461004</c:v>
+                </c:pt>
+                <c:pt idx="151">
+                  <c:v>0.89438867568970004</c:v>
+                </c:pt>
+                <c:pt idx="152">
+                  <c:v>0.89711326360703003</c:v>
+                </c:pt>
+                <c:pt idx="153">
+                  <c:v>0.89780795574187999</c:v>
+                </c:pt>
+                <c:pt idx="154">
+                  <c:v>0.89448612928391003</c:v>
+                </c:pt>
+                <c:pt idx="155">
+                  <c:v>0.89176917076110995</c:v>
+                </c:pt>
+                <c:pt idx="156">
+                  <c:v>0.90002775192260998</c:v>
+                </c:pt>
+                <c:pt idx="157">
+                  <c:v>0.89409410953521995</c:v>
+                </c:pt>
+                <c:pt idx="158">
+                  <c:v>0.88730990886687999</c:v>
+                </c:pt>
+                <c:pt idx="159">
+                  <c:v>0.89377731084823997</c:v>
+                </c:pt>
+                <c:pt idx="160">
+                  <c:v>0.89018511772155995</c:v>
+                </c:pt>
+                <c:pt idx="161">
+                  <c:v>0.8850291967392</c:v>
+                </c:pt>
+                <c:pt idx="162">
+                  <c:v>0.88888812065125</c:v>
+                </c:pt>
+                <c:pt idx="163">
+                  <c:v>0.89085704088211004</c:v>
+                </c:pt>
+                <c:pt idx="164">
+                  <c:v>0.8879753947258</c:v>
+                </c:pt>
+                <c:pt idx="165">
+                  <c:v>0.88902628421783003</c:v>
+                </c:pt>
+                <c:pt idx="166">
+                  <c:v>0.88434004783630005</c:v>
+                </c:pt>
+                <c:pt idx="167">
+                  <c:v>0.88792014122009</c:v>
+                </c:pt>
+                <c:pt idx="168">
+                  <c:v>0.87950563430786</c:v>
+                </c:pt>
+                <c:pt idx="169">
+                  <c:v>0.88259071111678999</c:v>
+                </c:pt>
+                <c:pt idx="170">
+                  <c:v>0.88631945848464999</c:v>
+                </c:pt>
+                <c:pt idx="171">
+                  <c:v>0.88129281997680997</c:v>
+                </c:pt>
+                <c:pt idx="172">
+                  <c:v>0.88410991430283004</c:v>
+                </c:pt>
+                <c:pt idx="173">
+                  <c:v>0.88801068067551003</c:v>
+                </c:pt>
+                <c:pt idx="174">
+                  <c:v>0.88539874553679998</c:v>
+                </c:pt>
+                <c:pt idx="175">
+                  <c:v>0.87995994091034002</c:v>
+                </c:pt>
+                <c:pt idx="176">
+                  <c:v>0.88344722986221003</c:v>
+                </c:pt>
+                <c:pt idx="177">
+                  <c:v>0.8801297545433</c:v>
+                </c:pt>
+                <c:pt idx="178">
+                  <c:v>0.88705462217330999</c:v>
+                </c:pt>
+                <c:pt idx="179">
+                  <c:v>0.87990111112595004</c:v>
+                </c:pt>
+                <c:pt idx="180">
+                  <c:v>0.88554126024246005</c:v>
+                </c:pt>
+                <c:pt idx="181">
+                  <c:v>0.87088239192963002</c:v>
+                </c:pt>
+                <c:pt idx="182">
+                  <c:v>0.88310956954955999</c:v>
+                </c:pt>
+                <c:pt idx="183">
+                  <c:v>0.87594860792160001</c:v>
+                </c:pt>
+                <c:pt idx="184">
+                  <c:v>0.87109482288360995</c:v>
+                </c:pt>
+                <c:pt idx="185">
+                  <c:v>0.87852185964583995</c:v>
+                </c:pt>
+                <c:pt idx="186">
+                  <c:v>0.87082338333130005</c:v>
+                </c:pt>
+                <c:pt idx="187">
+                  <c:v>0.87214952707291005</c:v>
+                </c:pt>
+                <c:pt idx="188">
+                  <c:v>0.87671089172363004</c:v>
+                </c:pt>
+                <c:pt idx="189">
+                  <c:v>0.87322396039963002</c:v>
+                </c:pt>
+                <c:pt idx="190">
+                  <c:v>0.87520545721053999</c:v>
+                </c:pt>
+                <c:pt idx="191">
+                  <c:v>0.87489455938339</c:v>
+                </c:pt>
+                <c:pt idx="192">
+                  <c:v>0.86829715967178001</c:v>
+                </c:pt>
+                <c:pt idx="193">
+                  <c:v>0.87764602899551003</c:v>
+                </c:pt>
+                <c:pt idx="194">
+                  <c:v>0.86110544204712003</c:v>
+                </c:pt>
+                <c:pt idx="195">
+                  <c:v>0.87531769275664995</c:v>
+                </c:pt>
+                <c:pt idx="196">
+                  <c:v>0.861383497715</c:v>
+                </c:pt>
+                <c:pt idx="197">
+                  <c:v>0.86804360151291005</c:v>
+                </c:pt>
+                <c:pt idx="198">
+                  <c:v>0.87132221460341996</c:v>
+                </c:pt>
+                <c:pt idx="199">
+                  <c:v>0.86677145957946999</c:v>
+                </c:pt>
+                <c:pt idx="200">
+                  <c:v>0.86931759119034002</c:v>
+                </c:pt>
+                <c:pt idx="201">
+                  <c:v>0.87101566791534002</c:v>
+                </c:pt>
+                <c:pt idx="202">
+                  <c:v>0.85913348197937001</c:v>
+                </c:pt>
+                <c:pt idx="203">
+                  <c:v>0.86079251766205001</c:v>
+                </c:pt>
+                <c:pt idx="204">
+                  <c:v>0.87258011102676003</c:v>
+                </c:pt>
+                <c:pt idx="205">
+                  <c:v>0.86063057184219005</c:v>
+                </c:pt>
+                <c:pt idx="206">
+                  <c:v>0.86477720737456998</c:v>
+                </c:pt>
+                <c:pt idx="207">
+                  <c:v>0.86181110143660999</c:v>
+                </c:pt>
+                <c:pt idx="208">
+                  <c:v>0.86565482616425005</c:v>
+                </c:pt>
+                <c:pt idx="209">
+                  <c:v>0.86420923471451006</c:v>
+                </c:pt>
+                <c:pt idx="210">
+                  <c:v>0.86035680770874001</c:v>
+                </c:pt>
+                <c:pt idx="211">
+                  <c:v>0.85680931806563998</c:v>
+                </c:pt>
+                <c:pt idx="212">
+                  <c:v>0.85500133037567005</c:v>
+                </c:pt>
+                <c:pt idx="213">
+                  <c:v>0.87066066265106001</c:v>
+                </c:pt>
+                <c:pt idx="214">
+                  <c:v>0.85667365789412997</c:v>
+                </c:pt>
+                <c:pt idx="215">
+                  <c:v>0.85849714279175005</c:v>
+                </c:pt>
+                <c:pt idx="216">
+                  <c:v>0.86063599586487005</c:v>
+                </c:pt>
+                <c:pt idx="217">
+                  <c:v>0.85861146450043002</c:v>
+                </c:pt>
+                <c:pt idx="218">
+                  <c:v>0.85090881586074996</c:v>
+                </c:pt>
+                <c:pt idx="219">
+                  <c:v>0.85401254892348999</c:v>
+                </c:pt>
+                <c:pt idx="220">
+                  <c:v>0.84844839572905995</c:v>
+                </c:pt>
+                <c:pt idx="221">
+                  <c:v>0.84806972742080999</c:v>
+                </c:pt>
+                <c:pt idx="222">
+                  <c:v>0.84788072109222001</c:v>
+                </c:pt>
+                <c:pt idx="223">
+                  <c:v>0.85355383157730003</c:v>
+                </c:pt>
+                <c:pt idx="224">
+                  <c:v>0.85740649700164995</c:v>
+                </c:pt>
+                <c:pt idx="225">
+                  <c:v>0.84752768278122004</c:v>
+                </c:pt>
+                <c:pt idx="226">
+                  <c:v>0.85052722692490001</c:v>
+                </c:pt>
+                <c:pt idx="227">
+                  <c:v>0.84674811363220004</c:v>
+                </c:pt>
+                <c:pt idx="228">
+                  <c:v>0.85723704099654996</c:v>
+                </c:pt>
+                <c:pt idx="229">
+                  <c:v>0.85046565532684004</c:v>
+                </c:pt>
+                <c:pt idx="230">
+                  <c:v>0.84264916181563998</c:v>
+                </c:pt>
+                <c:pt idx="231">
+                  <c:v>0.85292387008667003</c:v>
+                </c:pt>
+                <c:pt idx="232">
+                  <c:v>0.84818762540817005</c:v>
+                </c:pt>
+                <c:pt idx="233">
+                  <c:v>0.84775096178054998</c:v>
+                </c:pt>
+                <c:pt idx="234">
+                  <c:v>0.84609395265579002</c:v>
+                </c:pt>
+                <c:pt idx="235">
+                  <c:v>0.84717053174973</c:v>
+                </c:pt>
+                <c:pt idx="236">
+                  <c:v>0.84728813171386996</c:v>
+                </c:pt>
+                <c:pt idx="237">
+                  <c:v>0.83915150165557995</c:v>
+                </c:pt>
+                <c:pt idx="238">
+                  <c:v>0.84779024124145996</c:v>
+                </c:pt>
+                <c:pt idx="239">
+                  <c:v>0.84441649913787997</c:v>
+                </c:pt>
+                <c:pt idx="240">
+                  <c:v>0.83923500776291005</c:v>
+                </c:pt>
+                <c:pt idx="241">
+                  <c:v>0.83588922023773005</c:v>
+                </c:pt>
+                <c:pt idx="242">
+                  <c:v>0.84568941593169999</c:v>
+                </c:pt>
+                <c:pt idx="243">
+                  <c:v>0.84137111902237005</c:v>
+                </c:pt>
+                <c:pt idx="244">
+                  <c:v>0.84015947580338002</c:v>
+                </c:pt>
+                <c:pt idx="245">
+                  <c:v>0.83984881639481002</c:v>
+                </c:pt>
+                <c:pt idx="246">
+                  <c:v>0.83846086263657005</c:v>
+                </c:pt>
+                <c:pt idx="247">
+                  <c:v>0.83904236555098999</c:v>
+                </c:pt>
+                <c:pt idx="248">
+                  <c:v>0.83473825454712003</c:v>
+                </c:pt>
+                <c:pt idx="249">
+                  <c:v>0.83805263042449996</c:v>
+                </c:pt>
+                <c:pt idx="250">
+                  <c:v>0.83683311939240002</c:v>
+                </c:pt>
+                <c:pt idx="251">
+                  <c:v>0.82659888267517001</c:v>
+                </c:pt>
+                <c:pt idx="252">
+                  <c:v>0.84275662899017001</c:v>
+                </c:pt>
+                <c:pt idx="253">
+                  <c:v>0.83244627714157005</c:v>
+                </c:pt>
+                <c:pt idx="254">
+                  <c:v>0.83915621042251998</c:v>
+                </c:pt>
+                <c:pt idx="255">
+                  <c:v>0.83027833700179998</c:v>
+                </c:pt>
+                <c:pt idx="256">
+                  <c:v>0.82670605182648005</c:v>
+                </c:pt>
+                <c:pt idx="257">
+                  <c:v>0.82534247636795</c:v>
+                </c:pt>
+                <c:pt idx="258">
+                  <c:v>0.83014810085296997</c:v>
+                </c:pt>
+                <c:pt idx="259">
+                  <c:v>0.82399189472197998</c:v>
+                </c:pt>
+                <c:pt idx="260">
+                  <c:v>0.83439713716507002</c:v>
+                </c:pt>
+                <c:pt idx="261">
+                  <c:v>0.82944959402083995</c:v>
+                </c:pt>
+                <c:pt idx="262">
+                  <c:v>0.82806611061096003</c:v>
+                </c:pt>
+                <c:pt idx="263">
+                  <c:v>0.8230339884758</c:v>
+                </c:pt>
+                <c:pt idx="264">
+                  <c:v>0.83219343423842995</c:v>
+                </c:pt>
+                <c:pt idx="265">
+                  <c:v>0.83373665809631003</c:v>
+                </c:pt>
+                <c:pt idx="266">
+                  <c:v>0.82882297039032005</c:v>
+                </c:pt>
+                <c:pt idx="267">
+                  <c:v>0.82362937927246005</c:v>
+                </c:pt>
+                <c:pt idx="268">
+                  <c:v>0.82576328516006003</c:v>
+                </c:pt>
+                <c:pt idx="269">
+                  <c:v>0.82685756683349998</c:v>
+                </c:pt>
+                <c:pt idx="270">
+                  <c:v>0.83492714166641002</c:v>
+                </c:pt>
+                <c:pt idx="271">
+                  <c:v>0.82591140270232999</c:v>
+                </c:pt>
+                <c:pt idx="272">
+                  <c:v>0.82206284999847001</c:v>
+                </c:pt>
+                <c:pt idx="273">
+                  <c:v>0.81246817111969005</c:v>
+                </c:pt>
+                <c:pt idx="274">
+                  <c:v>0.82018452882767001</c:v>
+                </c:pt>
+                <c:pt idx="275">
+                  <c:v>0.82662820816039995</c:v>
+                </c:pt>
+                <c:pt idx="276">
+                  <c:v>0.82354164123535001</c:v>
+                </c:pt>
+                <c:pt idx="277">
+                  <c:v>0.82937681674956998</c:v>
+                </c:pt>
+                <c:pt idx="278">
+                  <c:v>0.81901872158051003</c:v>
+                </c:pt>
+                <c:pt idx="279">
+                  <c:v>0.80956864356994995</c:v>
+                </c:pt>
+                <c:pt idx="280">
+                  <c:v>0.82483422756195002</c:v>
+                </c:pt>
+                <c:pt idx="281">
+                  <c:v>0.81326097249984997</c:v>
+                </c:pt>
+                <c:pt idx="282">
+                  <c:v>0.81699585914612005</c:v>
+                </c:pt>
+                <c:pt idx="283">
+                  <c:v>0.81603866815567005</c:v>
+                </c:pt>
+                <c:pt idx="284">
+                  <c:v>0.81886643171310003</c:v>
+                </c:pt>
+                <c:pt idx="285">
+                  <c:v>0.81821179389954002</c:v>
+                </c:pt>
+                <c:pt idx="286">
+                  <c:v>0.81150954961777</c:v>
+                </c:pt>
+                <c:pt idx="287">
+                  <c:v>0.81429606676101995</c:v>
+                </c:pt>
+                <c:pt idx="288">
+                  <c:v>0.81354343891143999</c:v>
+                </c:pt>
+                <c:pt idx="289">
+                  <c:v>0.81151700019836004</c:v>
+                </c:pt>
+                <c:pt idx="290">
+                  <c:v>0.81577497720717995</c:v>
+                </c:pt>
+                <c:pt idx="291">
+                  <c:v>0.82042694091796997</c:v>
+                </c:pt>
+                <c:pt idx="292">
+                  <c:v>0.80398201942444003</c:v>
+                </c:pt>
+                <c:pt idx="293">
+                  <c:v>0.81058818101883001</c:v>
+                </c:pt>
+                <c:pt idx="294">
+                  <c:v>0.80554139614105003</c:v>
+                </c:pt>
+                <c:pt idx="295">
+                  <c:v>0.81051284074783003</c:v>
+                </c:pt>
+                <c:pt idx="296">
+                  <c:v>0.81150037050247004</c:v>
+                </c:pt>
+                <c:pt idx="297">
+                  <c:v>0.80741149187088002</c:v>
+                </c:pt>
+                <c:pt idx="298">
+                  <c:v>0.81555581092833995</c:v>
+                </c:pt>
+                <c:pt idx="299">
+                  <c:v>0.81701755523681996</c:v>
+                </c:pt>
+                <c:pt idx="300">
+                  <c:v>0.81028771400452004</c:v>
+                </c:pt>
+                <c:pt idx="301">
+                  <c:v>0.80913126468658003</c:v>
+                </c:pt>
+                <c:pt idx="302">
+                  <c:v>0.80907970666884999</c:v>
+                </c:pt>
+                <c:pt idx="303">
+                  <c:v>0.80781644582748002</c:v>
+                </c:pt>
+                <c:pt idx="304">
+                  <c:v>0.80378496646881004</c:v>
+                </c:pt>
+                <c:pt idx="305">
+                  <c:v>0.80388182401657005</c:v>
+                </c:pt>
+                <c:pt idx="306">
+                  <c:v>0.79721850156784002</c:v>
+                </c:pt>
+                <c:pt idx="307">
+                  <c:v>0.80468767881393</c:v>
+                </c:pt>
+                <c:pt idx="308">
+                  <c:v>0.80514943599701005</c:v>
+                </c:pt>
+                <c:pt idx="309">
+                  <c:v>0.81401067972183005</c:v>
+                </c:pt>
+                <c:pt idx="310">
+                  <c:v>0.79653555154800004</c:v>
+                </c:pt>
+                <c:pt idx="311">
+                  <c:v>0.79478347301482999</c:v>
+                </c:pt>
+                <c:pt idx="312">
+                  <c:v>0.79230606555938998</c:v>
+                </c:pt>
+                <c:pt idx="313">
+                  <c:v>0.80005913972855003</c:v>
+                </c:pt>
+                <c:pt idx="314">
+                  <c:v>0.79529190063476995</c:v>
+                </c:pt>
+                <c:pt idx="315">
+                  <c:v>0.79788738489151001</c:v>
+                </c:pt>
+                <c:pt idx="316">
+                  <c:v>0.79048055410384999</c:v>
+                </c:pt>
+                <c:pt idx="317">
+                  <c:v>0.79422813653946001</c:v>
+                </c:pt>
+                <c:pt idx="318">
+                  <c:v>0.80218118429184004</c:v>
+                </c:pt>
+                <c:pt idx="319">
+                  <c:v>0.79998016357421997</c:v>
+                </c:pt>
+                <c:pt idx="320">
+                  <c:v>0.79510945081711004</c:v>
+                </c:pt>
+                <c:pt idx="321">
+                  <c:v>0.79660218954086004</c:v>
+                </c:pt>
+                <c:pt idx="322">
+                  <c:v>0.78660780191421997</c:v>
+                </c:pt>
+                <c:pt idx="323">
+                  <c:v>0.79737824201583996</c:v>
+                </c:pt>
+                <c:pt idx="324">
+                  <c:v>0.79582726955413996</c:v>
+                </c:pt>
+                <c:pt idx="325">
+                  <c:v>0.79988950490952004</c:v>
+                </c:pt>
+                <c:pt idx="326">
+                  <c:v>0.79148840904235995</c:v>
+                </c:pt>
+                <c:pt idx="327">
+                  <c:v>0.79452604055404996</c:v>
+                </c:pt>
+                <c:pt idx="328">
+                  <c:v>0.79410696029662997</c:v>
+                </c:pt>
+                <c:pt idx="329">
+                  <c:v>0.79363667964935003</c:v>
+                </c:pt>
+                <c:pt idx="330">
+                  <c:v>0.79273909330367998</c:v>
+                </c:pt>
+                <c:pt idx="331">
+                  <c:v>0.79615515470505005</c:v>
+                </c:pt>
+                <c:pt idx="332">
+                  <c:v>0.80096811056136996</c:v>
+                </c:pt>
+                <c:pt idx="333">
+                  <c:v>0.78559917211533004</c:v>
+                </c:pt>
+                <c:pt idx="334">
+                  <c:v>0.79514795541762995</c:v>
+                </c:pt>
+                <c:pt idx="335">
+                  <c:v>0.78679198026657005</c:v>
+                </c:pt>
+                <c:pt idx="336">
+                  <c:v>0.79043447971344005</c:v>
+                </c:pt>
+                <c:pt idx="337">
+                  <c:v>0.78660827875136996</c:v>
+                </c:pt>
+                <c:pt idx="338">
+                  <c:v>0.78908300399779996</c:v>
+                </c:pt>
+                <c:pt idx="339">
+                  <c:v>0.78538727760314997</c:v>
+                </c:pt>
+                <c:pt idx="340">
+                  <c:v>0.77886831760405995</c:v>
+                </c:pt>
+                <c:pt idx="341">
+                  <c:v>0.78369408845901001</c:v>
+                </c:pt>
+                <c:pt idx="342">
+                  <c:v>0.78739041090011996</c:v>
+                </c:pt>
+                <c:pt idx="343">
+                  <c:v>0.78368973731994995</c:v>
+                </c:pt>
+                <c:pt idx="344">
+                  <c:v>0.79124867916107</c:v>
+                </c:pt>
+                <c:pt idx="345">
+                  <c:v>0.78666883707046997</c:v>
+                </c:pt>
+                <c:pt idx="346">
+                  <c:v>0.78181582689285001</c:v>
+                </c:pt>
+                <c:pt idx="347">
+                  <c:v>0.78280240297318004</c:v>
+                </c:pt>
+                <c:pt idx="348">
+                  <c:v>0.78809344768524003</c:v>
+                </c:pt>
+                <c:pt idx="349">
+                  <c:v>0.78057348728179998</c:v>
+                </c:pt>
+                <c:pt idx="350">
+                  <c:v>0.77950751781464001</c:v>
+                </c:pt>
+                <c:pt idx="351">
+                  <c:v>0.77741408348082996</c:v>
+                </c:pt>
+                <c:pt idx="352">
+                  <c:v>0.77740448713303001</c:v>
+                </c:pt>
+                <c:pt idx="353">
+                  <c:v>0.76724016666411998</c:v>
+                </c:pt>
+                <c:pt idx="354">
+                  <c:v>0.79201376438141002</c:v>
+                </c:pt>
+                <c:pt idx="355">
+                  <c:v>0.78258574008941995</c:v>
+                </c:pt>
+                <c:pt idx="356">
+                  <c:v>0.77490258216857999</c:v>
+                </c:pt>
+                <c:pt idx="357">
+                  <c:v>0.78417783975600996</c:v>
+                </c:pt>
+                <c:pt idx="358">
+                  <c:v>0.77579939365386996</c:v>
+                </c:pt>
+                <c:pt idx="359">
+                  <c:v>0.77629256248473999</c:v>
+                </c:pt>
+                <c:pt idx="360">
+                  <c:v>0.77598679065704002</c:v>
+                </c:pt>
+                <c:pt idx="361">
+                  <c:v>0.76716494560241999</c:v>
+                </c:pt>
+                <c:pt idx="362">
+                  <c:v>0.77987432479857999</c:v>
+                </c:pt>
+                <c:pt idx="363">
+                  <c:v>0.78037548065186002</c:v>
+                </c:pt>
+                <c:pt idx="364">
+                  <c:v>0.77818834781646995</c:v>
+                </c:pt>
+                <c:pt idx="365">
+                  <c:v>0.77440768480301003</c:v>
+                </c:pt>
+                <c:pt idx="366">
+                  <c:v>0.76993399858474998</c:v>
+                </c:pt>
+                <c:pt idx="367">
+                  <c:v>0.76897537708282004</c:v>
+                </c:pt>
+                <c:pt idx="368">
+                  <c:v>0.77244794368743996</c:v>
+                </c:pt>
+                <c:pt idx="369">
+                  <c:v>0.76958495378493996</c:v>
+                </c:pt>
+                <c:pt idx="370">
+                  <c:v>0.76319068670273005</c:v>
+                </c:pt>
+                <c:pt idx="371">
+                  <c:v>0.77015978097916005</c:v>
+                </c:pt>
+                <c:pt idx="372">
+                  <c:v>0.76552796363830999</c:v>
+                </c:pt>
+                <c:pt idx="373">
+                  <c:v>0.77848643064499001</c:v>
+                </c:pt>
+                <c:pt idx="374">
+                  <c:v>0.77019625902176003</c:v>
+                </c:pt>
+                <c:pt idx="375">
+                  <c:v>0.76966929435730003</c:v>
+                </c:pt>
+                <c:pt idx="376">
+                  <c:v>0.76392996311187999</c:v>
+                </c:pt>
+                <c:pt idx="377">
+                  <c:v>0.77315652370453003</c:v>
+                </c:pt>
+                <c:pt idx="378">
+                  <c:v>0.76433807611464999</c:v>
+                </c:pt>
+                <c:pt idx="379">
+                  <c:v>0.76721215248107999</c:v>
+                </c:pt>
+                <c:pt idx="380">
+                  <c:v>0.76273334026337003</c:v>
+                </c:pt>
+                <c:pt idx="381">
+                  <c:v>0.77222424745560003</c:v>
+                </c:pt>
+                <c:pt idx="382">
+                  <c:v>0.76908284425734996</c:v>
+                </c:pt>
+                <c:pt idx="383">
+                  <c:v>0.75817751884460005</c:v>
+                </c:pt>
+                <c:pt idx="384">
+                  <c:v>0.76317697763443004</c:v>
+                </c:pt>
+                <c:pt idx="385">
+                  <c:v>0.76540064811706998</c:v>
+                </c:pt>
+                <c:pt idx="386">
+                  <c:v>0.76415526866912997</c:v>
+                </c:pt>
+                <c:pt idx="387">
+                  <c:v>0.75701689720153997</c:v>
+                </c:pt>
+                <c:pt idx="388">
+                  <c:v>0.76558703184127996</c:v>
+                </c:pt>
+                <c:pt idx="389">
+                  <c:v>0.75775384902954002</c:v>
+                </c:pt>
+                <c:pt idx="390">
+                  <c:v>0.76386266946793002</c:v>
+                </c:pt>
+                <c:pt idx="391">
+                  <c:v>0.76331746578216997</c:v>
+                </c:pt>
+                <c:pt idx="392">
+                  <c:v>0.75127804279327004</c:v>
+                </c:pt>
+                <c:pt idx="393">
+                  <c:v>0.75463253259659002</c:v>
+                </c:pt>
+                <c:pt idx="394">
+                  <c:v>0.75599098205565995</c:v>
+                </c:pt>
+                <c:pt idx="395">
+                  <c:v>0.75490856170653997</c:v>
+                </c:pt>
+                <c:pt idx="396">
+                  <c:v>0.75259387493134</c:v>
+                </c:pt>
+                <c:pt idx="397">
+                  <c:v>0.76265293359756003</c:v>
+                </c:pt>
+                <c:pt idx="398">
+                  <c:v>0.75819927453994995</c:v>
+                </c:pt>
+                <c:pt idx="399">
+                  <c:v>0.75306534767151001</c:v>
+                </c:pt>
+                <c:pt idx="400">
+                  <c:v>0.75675880908965998</c:v>
+                </c:pt>
+                <c:pt idx="401">
+                  <c:v>0.75457209348679</c:v>
+                </c:pt>
+                <c:pt idx="402">
+                  <c:v>0.75471311807632002</c:v>
+                </c:pt>
+                <c:pt idx="403">
+                  <c:v>0.74800586700438998</c:v>
+                </c:pt>
+                <c:pt idx="404">
+                  <c:v>0.76077604293822998</c:v>
+                </c:pt>
+                <c:pt idx="405">
+                  <c:v>0.74800264835357999</c:v>
+                </c:pt>
+                <c:pt idx="406">
+                  <c:v>0.73820781707764005</c:v>
+                </c:pt>
+                <c:pt idx="407">
+                  <c:v>0.75398445129394998</c:v>
+                </c:pt>
+                <c:pt idx="408">
+                  <c:v>0.75094240903854004</c:v>
+                </c:pt>
+                <c:pt idx="409">
+                  <c:v>0.74729573726653997</c:v>
+                </c:pt>
+                <c:pt idx="410">
+                  <c:v>0.74444788694382003</c:v>
+                </c:pt>
+                <c:pt idx="411">
+                  <c:v>0.75421166419982999</c:v>
+                </c:pt>
+                <c:pt idx="412">
+                  <c:v>0.74747741222382003</c:v>
+                </c:pt>
+                <c:pt idx="413">
+                  <c:v>0.75749337673187001</c:v>
+                </c:pt>
+                <c:pt idx="414">
+                  <c:v>0.75157546997070002</c:v>
+                </c:pt>
+                <c:pt idx="415">
+                  <c:v>0.74455273151398005</c:v>
+                </c:pt>
+                <c:pt idx="416">
+                  <c:v>0.74904578924178999</c:v>
+                </c:pt>
+                <c:pt idx="417">
+                  <c:v>0.74923390150070002</c:v>
+                </c:pt>
+                <c:pt idx="418">
+                  <c:v>0.73993813991546997</c:v>
+                </c:pt>
+                <c:pt idx="419">
+                  <c:v>0.74715697765349998</c:v>
+                </c:pt>
+                <c:pt idx="420">
+                  <c:v>0.75120037794113004</c:v>
+                </c:pt>
+                <c:pt idx="421">
+                  <c:v>0.74528717994689997</c:v>
+                </c:pt>
+                <c:pt idx="422">
+                  <c:v>0.74132019281386996</c:v>
+                </c:pt>
+                <c:pt idx="423">
+                  <c:v>0.74711698293686002</c:v>
+                </c:pt>
+                <c:pt idx="424">
+                  <c:v>0.74317854642867998</c:v>
+                </c:pt>
+                <c:pt idx="425">
+                  <c:v>0.74167996644973999</c:v>
+                </c:pt>
+                <c:pt idx="426">
+                  <c:v>0.74126893281937001</c:v>
+                </c:pt>
+                <c:pt idx="427">
+                  <c:v>0.73345404863357999</c:v>
+                </c:pt>
+                <c:pt idx="428">
+                  <c:v>0.73497736454009999</c:v>
+                </c:pt>
+                <c:pt idx="429">
+                  <c:v>0.74097150564194003</c:v>
+                </c:pt>
+                <c:pt idx="430">
+                  <c:v>0.74063348770142001</c:v>
+                </c:pt>
+                <c:pt idx="431">
+                  <c:v>0.73842680454253995</c:v>
+                </c:pt>
+                <c:pt idx="432">
+                  <c:v>0.74470186233520996</c:v>
+                </c:pt>
+                <c:pt idx="433">
+                  <c:v>0.73759567737579002</c:v>
+                </c:pt>
+                <c:pt idx="434">
+                  <c:v>0.73688721656799006</c:v>
+                </c:pt>
+                <c:pt idx="435">
+                  <c:v>0.74262821674347002</c:v>
+                </c:pt>
+                <c:pt idx="436">
+                  <c:v>0.73899155855179</c:v>
+                </c:pt>
+                <c:pt idx="437">
+                  <c:v>0.73828816413878995</c:v>
+                </c:pt>
+                <c:pt idx="438">
+                  <c:v>0.73359447717667003</c:v>
+                </c:pt>
+                <c:pt idx="439">
+                  <c:v>0.74134057760239003</c:v>
+                </c:pt>
+                <c:pt idx="440">
+                  <c:v>0.73414790630340998</c:v>
+                </c:pt>
+                <c:pt idx="441">
+                  <c:v>0.7340726852417</c:v>
+                </c:pt>
+                <c:pt idx="442">
+                  <c:v>0.73228865861893</c:v>
+                </c:pt>
+                <c:pt idx="443">
+                  <c:v>0.72981834411621005</c:v>
+                </c:pt>
+                <c:pt idx="444">
+                  <c:v>0.73299008607864002</c:v>
+                </c:pt>
+                <c:pt idx="445">
+                  <c:v>0.73599761724472001</c:v>
+                </c:pt>
+                <c:pt idx="446">
+                  <c:v>0.72997075319289995</c:v>
+                </c:pt>
+                <c:pt idx="447">
+                  <c:v>0.73846572637557995</c:v>
+                </c:pt>
+                <c:pt idx="448">
+                  <c:v>0.73156827688216997</c:v>
+                </c:pt>
+                <c:pt idx="449">
+                  <c:v>0.72662180662154996</c:v>
+                </c:pt>
+                <c:pt idx="450">
+                  <c:v>0.72819876670837003</c:v>
+                </c:pt>
+                <c:pt idx="451">
+                  <c:v>0.73557293415070002</c:v>
+                </c:pt>
+                <c:pt idx="452">
+                  <c:v>0.72585666179657005</c:v>
+                </c:pt>
+                <c:pt idx="453">
+                  <c:v>0.73570972681045999</c:v>
+                </c:pt>
+                <c:pt idx="454">
+                  <c:v>0.72448068857193004</c:v>
+                </c:pt>
+                <c:pt idx="455">
+                  <c:v>0.72691333293914995</c:v>
+                </c:pt>
+                <c:pt idx="456">
+                  <c:v>0.73294490575789994</c:v>
+                </c:pt>
+                <c:pt idx="457">
+                  <c:v>0.72274166345596003</c:v>
+                </c:pt>
+                <c:pt idx="458">
+                  <c:v>0.73066961765288996</c:v>
+                </c:pt>
+                <c:pt idx="459">
+                  <c:v>0.73098814487456998</c:v>
+                </c:pt>
+                <c:pt idx="460">
+                  <c:v>0.72603666782378995</c:v>
+                </c:pt>
+                <c:pt idx="461">
+                  <c:v>0.73130303621292003</c:v>
+                </c:pt>
+                <c:pt idx="462">
+                  <c:v>0.73187202215195002</c:v>
+                </c:pt>
+                <c:pt idx="463">
+                  <c:v>0.72810316085814997</c:v>
+                </c:pt>
+                <c:pt idx="464">
+                  <c:v>0.72132200002669999</c:v>
+                </c:pt>
+                <c:pt idx="465">
+                  <c:v>0.72039002180098999</c:v>
+                </c:pt>
+                <c:pt idx="466">
+                  <c:v>0.72798162698746005</c:v>
+                </c:pt>
+                <c:pt idx="467">
+                  <c:v>0.72135889530181996</c:v>
+                </c:pt>
+                <c:pt idx="468">
+                  <c:v>0.72555428743362005</c:v>
+                </c:pt>
+                <c:pt idx="469">
+                  <c:v>0.72128951549529996</c:v>
+                </c:pt>
+                <c:pt idx="470">
+                  <c:v>0.71767908334732</c:v>
+                </c:pt>
+                <c:pt idx="471">
+                  <c:v>0.72672861814499001</c:v>
+                </c:pt>
+                <c:pt idx="472">
+                  <c:v>0.71905112266541005</c:v>
+                </c:pt>
+                <c:pt idx="473">
+                  <c:v>0.71493321657180997</c:v>
+                </c:pt>
+                <c:pt idx="474">
+                  <c:v>0.72349631786346003</c:v>
+                </c:pt>
+                <c:pt idx="475">
+                  <c:v>0.72004354000091997</c:v>
+                </c:pt>
+                <c:pt idx="476">
+                  <c:v>0.71091711521149004</c:v>
+                </c:pt>
+                <c:pt idx="477">
+                  <c:v>0.72096055746078003</c:v>
+                </c:pt>
+                <c:pt idx="478">
+                  <c:v>0.73136210441589</c:v>
+                </c:pt>
+                <c:pt idx="479">
+                  <c:v>0.71442753076553001</c:v>
+                </c:pt>
+                <c:pt idx="480">
+                  <c:v>0.71611064672470004</c:v>
+                </c:pt>
+                <c:pt idx="481">
+                  <c:v>0.71915876865386996</c:v>
+                </c:pt>
+                <c:pt idx="482">
+                  <c:v>0.71799957752228005</c:v>
+                </c:pt>
+                <c:pt idx="483">
+                  <c:v>0.70769464969634999</c:v>
+                </c:pt>
+                <c:pt idx="484">
+                  <c:v>0.72512584924697998</c:v>
+                </c:pt>
+                <c:pt idx="485">
+                  <c:v>0.72354090213776001</c:v>
+                </c:pt>
+                <c:pt idx="486">
+                  <c:v>0.71961504220963002</c:v>
+                </c:pt>
+                <c:pt idx="487">
+                  <c:v>0.70934492349625</c:v>
+                </c:pt>
+                <c:pt idx="488">
+                  <c:v>0.71758913993835005</c:v>
+                </c:pt>
+                <c:pt idx="489">
+                  <c:v>0.71491730213164995</c:v>
+                </c:pt>
+                <c:pt idx="490">
+                  <c:v>0.72074627876282005</c:v>
+                </c:pt>
+                <c:pt idx="491">
+                  <c:v>0.72355329990386996</c:v>
+                </c:pt>
+                <c:pt idx="492">
+                  <c:v>0.71000105142592995</c:v>
+                </c:pt>
+                <c:pt idx="493">
+                  <c:v>0.70799237489699995</c:v>
+                </c:pt>
+                <c:pt idx="494">
+                  <c:v>0.72284626960753995</c:v>
+                </c:pt>
+                <c:pt idx="495">
+                  <c:v>0.70512926578521995</c:v>
+                </c:pt>
+                <c:pt idx="496">
+                  <c:v>0.71694672107696999</c:v>
+                </c:pt>
+                <c:pt idx="497">
+                  <c:v>0.71460372209548995</c:v>
+                </c:pt>
+                <c:pt idx="498">
+                  <c:v>0.71523970365524003</c:v>
+                </c:pt>
+                <c:pt idx="499">
+                  <c:v>0.70186430215836004</c:v>
+                </c:pt>
+                <c:pt idx="502">
+                  <c:v>0</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="1"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-B8E3-4FB0-BF49-53BAAB51EEA7}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Worksheet!$F$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>val_loss</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:yVal>
+            <c:numRef>
+              <c:f>Worksheet!$F$2:$F$504</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="503"/>
+                <c:pt idx="0">
+                  <c:v>1.8042132854462001</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1.7936296463013</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1.7847944498062001</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1.7707042694091999</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>1.7572311162948999</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>1.7486900091171</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>1.7302137613297</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>1.7205181121826001</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>1.7059650421143</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>1.6800761222839</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>1.6572687625885001</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>1.6532320976257</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>1.6258842945098999</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>1.5841915607452</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>1.5168114900589</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>1.5226324796677</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>1.4765148162841999</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>1.3871923685073999</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>1.3576648235321001</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>1.3803278207778999</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>1.3884224891663</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>1.2929097414016999</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>1.3594517707825</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>1.3329344987869001</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>1.2574387788773</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>1.21324467659</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>1.1826428174973</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>1.2213325500487999</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>1.1254603862762</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>1.1576160192489999</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>1.0709314346312999</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>1.0572290420532</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>1.0630027055739999</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>1.0480352640152</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>1.0342296361923</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>1.0238035917282</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>1.0329437255859</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>1.0364514589310001</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>1.0126775503159</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>1.0087337493896</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>1.02205991745</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>1.002546787262</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>1.0157430171966999</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>0.99476969242096003</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>1.004900932312</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>0.98571091890335005</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>1.0088971853255999</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>1.0263416767119999</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>0.99321043491364003</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>1.0217814445496001</c:v>
+                </c:pt>
+                <c:pt idx="50">
+                  <c:v>1.0303016901016</c:v>
+                </c:pt>
+                <c:pt idx="51">
+                  <c:v>0.96724623441696</c:v>
+                </c:pt>
+                <c:pt idx="52">
+                  <c:v>0.97571039199829002</c:v>
+                </c:pt>
+                <c:pt idx="53">
+                  <c:v>0.95986461639403997</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>1.00903403759</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>0.97198253870009999</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>0.95156389474868996</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>0.95436745882034002</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>0.93927443027496005</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>0.95756608247757002</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>0.93434017896652</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>0.93253821134567005</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>0.93226265907287997</c:v>
+                </c:pt>
+                <c:pt idx="63">
+                  <c:v>0.92964941263198997</c:v>
+                </c:pt>
+                <c:pt idx="64">
+                  <c:v>0.92889511585235995</c:v>
+                </c:pt>
+                <c:pt idx="65">
+                  <c:v>0.92670279741286998</c:v>
+                </c:pt>
+                <c:pt idx="66">
+                  <c:v>0.92509984970092995</c:v>
+                </c:pt>
+                <c:pt idx="67">
+                  <c:v>0.92775529623032005</c:v>
+                </c:pt>
+                <c:pt idx="68">
+                  <c:v>0.92571675777435003</c:v>
+                </c:pt>
+                <c:pt idx="69">
+                  <c:v>0.92597037553786998</c:v>
+                </c:pt>
+                <c:pt idx="70">
+                  <c:v>0.92778211832046997</c:v>
+                </c:pt>
+                <c:pt idx="71">
+                  <c:v>0.93132019042969005</c:v>
+                </c:pt>
+                <c:pt idx="72">
+                  <c:v>0.92653274536133001</c:v>
+                </c:pt>
+                <c:pt idx="73">
+                  <c:v>0.92740380764008001</c:v>
+                </c:pt>
+                <c:pt idx="74">
+                  <c:v>0.91851133108139005</c:v>
+                </c:pt>
+                <c:pt idx="75">
+                  <c:v>0.91907405853270996</c:v>
+                </c:pt>
+                <c:pt idx="76">
+                  <c:v>0.91676861047744995</c:v>
+                </c:pt>
+                <c:pt idx="77">
+                  <c:v>0.92260795831679998</c:v>
+                </c:pt>
+                <c:pt idx="78">
+                  <c:v>0.91750276088714999</c:v>
+                </c:pt>
+                <c:pt idx="79">
+                  <c:v>0.91646355390548995</c:v>
+                </c:pt>
+                <c:pt idx="80">
+                  <c:v>0.91491323709488004</c:v>
+                </c:pt>
+                <c:pt idx="81">
+                  <c:v>0.91335809230803999</c:v>
+                </c:pt>
+                <c:pt idx="82">
+                  <c:v>0.91762524843215998</c:v>
+                </c:pt>
+                <c:pt idx="83">
+                  <c:v>0.91289991140366</c:v>
+                </c:pt>
+                <c:pt idx="84">
+                  <c:v>0.90874373912811002</c:v>
+                </c:pt>
+                <c:pt idx="85">
+                  <c:v>0.91650825738907005</c:v>
+                </c:pt>
+                <c:pt idx="86">
+                  <c:v>0.91419821977615001</c:v>
+                </c:pt>
+                <c:pt idx="87">
+                  <c:v>0.90985029935837003</c:v>
+                </c:pt>
+                <c:pt idx="88">
+                  <c:v>0.90697592496872004</c:v>
+                </c:pt>
+                <c:pt idx="89">
+                  <c:v>0.90925902128220004</c:v>
+                </c:pt>
+                <c:pt idx="90">
+                  <c:v>0.91094791889190996</c:v>
+                </c:pt>
+                <c:pt idx="91">
+                  <c:v>0.91415572166443004</c:v>
+                </c:pt>
+                <c:pt idx="92">
+                  <c:v>0.90640127658844005</c:v>
+                </c:pt>
+                <c:pt idx="93">
+                  <c:v>0.91276806592940996</c:v>
+                </c:pt>
+                <c:pt idx="94">
+                  <c:v>0.90707886219025002</c:v>
+                </c:pt>
+                <c:pt idx="95">
+                  <c:v>0.90813630819321001</c:v>
+                </c:pt>
+                <c:pt idx="96">
+                  <c:v>0.90598148107528997</c:v>
+                </c:pt>
+                <c:pt idx="97">
+                  <c:v>0.90259891748428001</c:v>
+                </c:pt>
+                <c:pt idx="98">
+                  <c:v>0.90507268905640004</c:v>
+                </c:pt>
+                <c:pt idx="99">
+                  <c:v>0.90281754732132002</c:v>
+                </c:pt>
+                <c:pt idx="100">
+                  <c:v>0.91002541780472002</c:v>
+                </c:pt>
+                <c:pt idx="101">
+                  <c:v>0.90912824869155995</c:v>
+                </c:pt>
+                <c:pt idx="102">
+                  <c:v>0.90604889392853005</c:v>
+                </c:pt>
+                <c:pt idx="103">
+                  <c:v>0.90538716316223</c:v>
+                </c:pt>
+                <c:pt idx="104">
+                  <c:v>0.90385711193085005</c:v>
+                </c:pt>
+                <c:pt idx="105">
+                  <c:v>0.91346192359924006</c:v>
+                </c:pt>
+                <c:pt idx="106">
+                  <c:v>0.90195846557616999</c:v>
+                </c:pt>
+                <c:pt idx="107">
+                  <c:v>0.90336531400680997</c:v>
+                </c:pt>
+                <c:pt idx="108">
+                  <c:v>0.90092343091964999</c:v>
+                </c:pt>
+                <c:pt idx="109">
+                  <c:v>0.89835399389267001</c:v>
+                </c:pt>
+                <c:pt idx="110">
+                  <c:v>0.90033715963364003</c:v>
+                </c:pt>
+                <c:pt idx="111">
+                  <c:v>0.90090817213058005</c:v>
+                </c:pt>
+                <c:pt idx="112">
+                  <c:v>0.8956852555275</c:v>
+                </c:pt>
+                <c:pt idx="113">
+                  <c:v>0.89814227819443004</c:v>
+                </c:pt>
+                <c:pt idx="114">
+                  <c:v>0.90015953779221003</c:v>
+                </c:pt>
+                <c:pt idx="115">
+                  <c:v>0.89339154958724998</c:v>
+                </c:pt>
+                <c:pt idx="116">
+                  <c:v>0.89410078525543002</c:v>
+                </c:pt>
+                <c:pt idx="117">
+                  <c:v>0.90171140432357999</c:v>
+                </c:pt>
+                <c:pt idx="118">
+                  <c:v>0.89433085918427002</c:v>
+                </c:pt>
+                <c:pt idx="119">
+                  <c:v>0.89163738489151001</c:v>
+                </c:pt>
+                <c:pt idx="120">
+                  <c:v>0.89235049486160001</c:v>
+                </c:pt>
+                <c:pt idx="121">
+                  <c:v>0.89789760112761996</c:v>
+                </c:pt>
+                <c:pt idx="122">
+                  <c:v>0.89304512739181996</c:v>
+                </c:pt>
+                <c:pt idx="123">
+                  <c:v>0.89360260963439997</c:v>
+                </c:pt>
+                <c:pt idx="124">
+                  <c:v>0.89498740434646995</c:v>
+                </c:pt>
+                <c:pt idx="125">
+                  <c:v>0.89428198337554998</c:v>
+                </c:pt>
+                <c:pt idx="126">
+                  <c:v>0.88765221834182995</c:v>
+                </c:pt>
+                <c:pt idx="127">
+                  <c:v>0.8887357711792</c:v>
+                </c:pt>
+                <c:pt idx="128">
+                  <c:v>0.89442569017410001</c:v>
+                </c:pt>
+                <c:pt idx="129">
+                  <c:v>0.88632470369339</c:v>
+                </c:pt>
+                <c:pt idx="130">
+                  <c:v>0.88917887210846003</c:v>
+                </c:pt>
+                <c:pt idx="131">
+                  <c:v>0.89080488681793002</c:v>
+                </c:pt>
+                <c:pt idx="132">
+                  <c:v>0.89631527662277</c:v>
+                </c:pt>
+                <c:pt idx="133">
+                  <c:v>0.88796758651732999</c:v>
+                </c:pt>
+                <c:pt idx="134">
+                  <c:v>0.89562678337097001</c:v>
+                </c:pt>
+                <c:pt idx="135">
+                  <c:v>0.88303995132446</c:v>
+                </c:pt>
+                <c:pt idx="136">
+                  <c:v>0.89045423269271995</c:v>
+                </c:pt>
+                <c:pt idx="137">
+                  <c:v>0.88874650001526001</c:v>
+                </c:pt>
+                <c:pt idx="138">
+                  <c:v>0.88608533143997004</c:v>
+                </c:pt>
+                <c:pt idx="139">
+                  <c:v>0.88287395238875999</c:v>
+                </c:pt>
+                <c:pt idx="140">
+                  <c:v>0.88446748256683005</c:v>
+                </c:pt>
+                <c:pt idx="141">
+                  <c:v>0.89696210622786998</c:v>
+                </c:pt>
+                <c:pt idx="142">
+                  <c:v>0.89543682336806996</c:v>
+                </c:pt>
+                <c:pt idx="143">
+                  <c:v>0.88344305753707997</c:v>
+                </c:pt>
+                <c:pt idx="144">
+                  <c:v>0.87926614284515003</c:v>
+                </c:pt>
+                <c:pt idx="145">
+                  <c:v>0.88156050443649003</c:v>
+                </c:pt>
+                <c:pt idx="146">
+                  <c:v>0.90432560443877996</c:v>
+                </c:pt>
+                <c:pt idx="147">
+                  <c:v>0.88129150867462003</c:v>
+                </c:pt>
+                <c:pt idx="148">
+                  <c:v>0.88984304666518999</c:v>
+                </c:pt>
+                <c:pt idx="149">
+                  <c:v>0.88845682144164995</c:v>
+                </c:pt>
+                <c:pt idx="150">
+                  <c:v>0.88092690706252996</c:v>
+                </c:pt>
+                <c:pt idx="151">
+                  <c:v>0.88915413618088002</c:v>
+                </c:pt>
+                <c:pt idx="152">
+                  <c:v>0.89432013034821001</c:v>
+                </c:pt>
+                <c:pt idx="153">
+                  <c:v>0.88538670539856001</c:v>
+                </c:pt>
+                <c:pt idx="154">
+                  <c:v>0.88903695344925004</c:v>
+                </c:pt>
+                <c:pt idx="155">
+                  <c:v>0.87568318843841997</c:v>
+                </c:pt>
+                <c:pt idx="156">
+                  <c:v>0.87808012962340998</c:v>
+                </c:pt>
+                <c:pt idx="157">
+                  <c:v>0.87449008226394997</c:v>
+                </c:pt>
+                <c:pt idx="158">
+                  <c:v>0.87498074769973999</c:v>
+                </c:pt>
+                <c:pt idx="159">
+                  <c:v>0.87424272298812999</c:v>
+                </c:pt>
+                <c:pt idx="160">
+                  <c:v>0.87983578443527</c:v>
+                </c:pt>
+                <c:pt idx="161">
+                  <c:v>0.87544411420821999</c:v>
+                </c:pt>
+                <c:pt idx="162">
+                  <c:v>0.87416571378707997</c:v>
+                </c:pt>
+                <c:pt idx="163">
+                  <c:v>0.87328755855560003</c:v>
+                </c:pt>
+                <c:pt idx="164">
+                  <c:v>0.87387335300446001</c:v>
+                </c:pt>
+                <c:pt idx="165">
+                  <c:v>0.88005590438842995</c:v>
+                </c:pt>
+                <c:pt idx="166">
+                  <c:v>0.89601480960846003</c:v>
+                </c:pt>
+                <c:pt idx="167">
+                  <c:v>0.87770682573318004</c:v>
+                </c:pt>
+                <c:pt idx="168">
+                  <c:v>0.87455046176910001</c:v>
+                </c:pt>
+                <c:pt idx="169">
+                  <c:v>0.86887395381927002</c:v>
+                </c:pt>
+                <c:pt idx="170">
+                  <c:v>0.87422966957091996</c:v>
+                </c:pt>
+                <c:pt idx="171">
+                  <c:v>0.86845541000366</c:v>
+                </c:pt>
+                <c:pt idx="172">
+                  <c:v>0.88107317686080999</c:v>
+                </c:pt>
+                <c:pt idx="173">
+                  <c:v>0.87660312652588002</c:v>
+                </c:pt>
+                <c:pt idx="174">
+                  <c:v>0.87413352727890004</c:v>
+                </c:pt>
+                <c:pt idx="175">
+                  <c:v>0.87195640802383001</c:v>
+                </c:pt>
+                <c:pt idx="176">
+                  <c:v>0.89134395122527998</c:v>
+                </c:pt>
+                <c:pt idx="177">
+                  <c:v>0.86843383312224998</c:v>
+                </c:pt>
+                <c:pt idx="178">
+                  <c:v>0.89374983310698997</c:v>
+                </c:pt>
+                <c:pt idx="179">
+                  <c:v>0.87564921379089</c:v>
+                </c:pt>
+                <c:pt idx="180">
+                  <c:v>0.88661938905715998</c:v>
+                </c:pt>
+                <c:pt idx="181">
+                  <c:v>0.87585759162902999</c:v>
+                </c:pt>
+                <c:pt idx="182">
+                  <c:v>0.86301636695862005</c:v>
+                </c:pt>
+                <c:pt idx="183">
+                  <c:v>0.86979383230208995</c:v>
+                </c:pt>
+                <c:pt idx="184">
+                  <c:v>0.86948245763778997</c:v>
+                </c:pt>
+                <c:pt idx="185">
+                  <c:v>0.87213158607482999</c:v>
+                </c:pt>
+                <c:pt idx="186">
+                  <c:v>0.88715469837188998</c:v>
+                </c:pt>
+                <c:pt idx="187">
+                  <c:v>0.87290608882903997</c:v>
+                </c:pt>
+                <c:pt idx="188">
+                  <c:v>0.86806905269623003</c:v>
+                </c:pt>
+                <c:pt idx="189">
+                  <c:v>0.87582689523696999</c:v>
+                </c:pt>
+                <c:pt idx="190">
+                  <c:v>0.87396782636642001</c:v>
+                </c:pt>
+                <c:pt idx="191">
+                  <c:v>0.88605374097823997</c:v>
+                </c:pt>
+                <c:pt idx="192">
+                  <c:v>0.87220144271850997</c:v>
+                </c:pt>
+                <c:pt idx="193">
+                  <c:v>0.88096761703491</c:v>
+                </c:pt>
+                <c:pt idx="194">
+                  <c:v>0.87800455093384</c:v>
+                </c:pt>
+                <c:pt idx="195">
+                  <c:v>0.87128686904907005</c:v>
+                </c:pt>
+                <c:pt idx="196">
+                  <c:v>0.89190495014190996</c:v>
+                </c:pt>
+                <c:pt idx="197">
+                  <c:v>0.87416166067123002</c:v>
+                </c:pt>
+                <c:pt idx="198">
+                  <c:v>0.86528801918029996</c:v>
+                </c:pt>
+                <c:pt idx="199">
+                  <c:v>0.86212617158890004</c:v>
+                </c:pt>
+                <c:pt idx="200">
+                  <c:v>0.86665922403336004</c:v>
+                </c:pt>
+                <c:pt idx="201">
+                  <c:v>0.85514539480208995</c:v>
+                </c:pt>
+                <c:pt idx="202">
+                  <c:v>0.87437421083449995</c:v>
+                </c:pt>
+                <c:pt idx="203">
+                  <c:v>0.86190164089203003</c:v>
+                </c:pt>
+                <c:pt idx="204">
+                  <c:v>0.84894329309464001</c:v>
+                </c:pt>
+                <c:pt idx="205">
+                  <c:v>0.85197192430496005</c:v>
+                </c:pt>
+                <c:pt idx="206">
+                  <c:v>0.87010359764098999</c:v>
+                </c:pt>
+                <c:pt idx="207">
+                  <c:v>0.84931510686874001</c:v>
+                </c:pt>
+                <c:pt idx="208">
+                  <c:v>0.85611271858214999</c:v>
+                </c:pt>
+                <c:pt idx="209">
+                  <c:v>0.86025416851044001</c:v>
+                </c:pt>
+                <c:pt idx="210">
+                  <c:v>0.86115396022796997</c:v>
+                </c:pt>
+                <c:pt idx="211">
+                  <c:v>0.85494637489319003</c:v>
+                </c:pt>
+                <c:pt idx="212">
+                  <c:v>0.87620437145232999</c:v>
+                </c:pt>
+                <c:pt idx="213">
+                  <c:v>0.85418194532393998</c:v>
+                </c:pt>
+                <c:pt idx="214">
+                  <c:v>0.86497676372527998</c:v>
+                </c:pt>
+                <c:pt idx="215">
+                  <c:v>0.8644352555275</c:v>
+                </c:pt>
+                <c:pt idx="216">
+                  <c:v>0.85422259569168002</c:v>
+                </c:pt>
+                <c:pt idx="217">
+                  <c:v>0.85042858123778997</c:v>
+                </c:pt>
+                <c:pt idx="218">
+                  <c:v>0.86051505804062001</c:v>
+                </c:pt>
+                <c:pt idx="219">
+                  <c:v>0.86329692602158004</c:v>
+                </c:pt>
+                <c:pt idx="220">
+                  <c:v>0.86082172393798995</c:v>
+                </c:pt>
+                <c:pt idx="221">
+                  <c:v>0.85761010646820002</c:v>
+                </c:pt>
+                <c:pt idx="222">
+                  <c:v>0.85487234592437999</c:v>
+                </c:pt>
+                <c:pt idx="223">
+                  <c:v>0.86732959747313998</c:v>
+                </c:pt>
+                <c:pt idx="224">
+                  <c:v>0.84842514991759999</c:v>
+                </c:pt>
+                <c:pt idx="225">
+                  <c:v>0.85466897487640003</c:v>
+                </c:pt>
+                <c:pt idx="226">
+                  <c:v>0.85806268453598</c:v>
+                </c:pt>
+                <c:pt idx="227">
+                  <c:v>0.85446512699126997</c:v>
+                </c:pt>
+                <c:pt idx="228">
+                  <c:v>0.85135209560393998</c:v>
+                </c:pt>
+                <c:pt idx="229">
+                  <c:v>0.86077177524566995</c:v>
+                </c:pt>
+                <c:pt idx="230">
+                  <c:v>0.86592590808867997</c:v>
+                </c:pt>
+                <c:pt idx="231">
+                  <c:v>0.85854196548462003</c:v>
+                </c:pt>
+                <c:pt idx="232">
+                  <c:v>0.85097885131836004</c:v>
+                </c:pt>
+                <c:pt idx="233">
+                  <c:v>0.85064691305161</c:v>
+                </c:pt>
+                <c:pt idx="234">
+                  <c:v>0.85990965366364003</c:v>
+                </c:pt>
+                <c:pt idx="235">
+                  <c:v>0.85846978425980003</c:v>
+                </c:pt>
+                <c:pt idx="236">
+                  <c:v>0.85194247961044001</c:v>
+                </c:pt>
+                <c:pt idx="237">
+                  <c:v>0.85461443662643</c:v>
+                </c:pt>
+                <c:pt idx="238">
+                  <c:v>0.87124276161194003</c:v>
+                </c:pt>
+                <c:pt idx="239">
+                  <c:v>0.86034399271010997</c:v>
+                </c:pt>
+                <c:pt idx="240">
+                  <c:v>0.84773415327071999</c:v>
+                </c:pt>
+                <c:pt idx="241">
+                  <c:v>0.85226351022720004</c:v>
+                </c:pt>
+                <c:pt idx="242">
+                  <c:v>0.84771251678466997</c:v>
+                </c:pt>
+                <c:pt idx="243">
+                  <c:v>0.85688340663910001</c:v>
+                </c:pt>
+                <c:pt idx="244">
+                  <c:v>0.88071912527083995</c:v>
+                </c:pt>
+                <c:pt idx="245">
+                  <c:v>0.84602266550063998</c:v>
+                </c:pt>
+                <c:pt idx="246">
+                  <c:v>0.85082405805588002</c:v>
+                </c:pt>
+                <c:pt idx="247">
+                  <c:v>0.85594904422759999</c:v>
+                </c:pt>
+                <c:pt idx="248">
+                  <c:v>0.85645318031311002</c:v>
+                </c:pt>
+                <c:pt idx="249">
+                  <c:v>0.85219413042068004</c:v>
+                </c:pt>
+                <c:pt idx="250">
+                  <c:v>0.84628880023955999</c:v>
+                </c:pt>
+                <c:pt idx="251">
+                  <c:v>0.84221196174622004</c:v>
+                </c:pt>
+                <c:pt idx="252">
+                  <c:v>0.85218852758408004</c:v>
+                </c:pt>
+                <c:pt idx="253">
+                  <c:v>0.82846492528914994</c:v>
+                </c:pt>
+                <c:pt idx="254">
+                  <c:v>0.86292648315429998</c:v>
+                </c:pt>
+                <c:pt idx="255">
+                  <c:v>0.84361290931702004</c:v>
+                </c:pt>
+                <c:pt idx="256">
+                  <c:v>0.83651345968246005</c:v>
+                </c:pt>
+                <c:pt idx="257">
+                  <c:v>0.83885627985000999</c:v>
+                </c:pt>
+                <c:pt idx="258">
+                  <c:v>0.84818083047866999</c:v>
+                </c:pt>
+                <c:pt idx="259">
+                  <c:v>0.84239870309830001</c:v>
+                </c:pt>
+                <c:pt idx="260">
+                  <c:v>0.83516854047775002</c:v>
+                </c:pt>
+                <c:pt idx="261">
+                  <c:v>0.84728664159775002</c:v>
+                </c:pt>
+                <c:pt idx="262">
+                  <c:v>0.84013533592223999</c:v>
+                </c:pt>
+                <c:pt idx="263">
+                  <c:v>0.83442068099975997</c:v>
+                </c:pt>
+                <c:pt idx="264">
+                  <c:v>0.84255158901214999</c:v>
+                </c:pt>
+                <c:pt idx="265">
+                  <c:v>0.84280627965927002</c:v>
+                </c:pt>
+                <c:pt idx="266">
+                  <c:v>0.82890695333481001</c:v>
+                </c:pt>
+                <c:pt idx="267">
+                  <c:v>0.83198869228363004</c:v>
+                </c:pt>
+                <c:pt idx="268">
+                  <c:v>0.85074865818024004</c:v>
+                </c:pt>
+                <c:pt idx="269">
+                  <c:v>0.83376479148865001</c:v>
+                </c:pt>
+                <c:pt idx="270">
+                  <c:v>0.83232593536376998</c:v>
+                </c:pt>
+                <c:pt idx="271">
+                  <c:v>0.83310031890868996</c:v>
+                </c:pt>
+                <c:pt idx="272">
+                  <c:v>0.83759272098541004</c:v>
+                </c:pt>
+                <c:pt idx="273">
+                  <c:v>0.83927059173583995</c:v>
+                </c:pt>
+                <c:pt idx="274">
+                  <c:v>0.82863616943358998</c:v>
+                </c:pt>
+                <c:pt idx="275">
+                  <c:v>0.84242755174636996</c:v>
+                </c:pt>
+                <c:pt idx="276">
+                  <c:v>0.85023844242096003</c:v>
+                </c:pt>
+                <c:pt idx="277">
+                  <c:v>0.83928006887436002</c:v>
+                </c:pt>
+                <c:pt idx="278">
+                  <c:v>0.83603978157043002</c:v>
+                </c:pt>
+                <c:pt idx="279">
+                  <c:v>0.85460227727890004</c:v>
+                </c:pt>
+                <c:pt idx="280">
+                  <c:v>0.83953148126601995</c:v>
+                </c:pt>
+                <c:pt idx="281">
+                  <c:v>0.82718336582184004</c:v>
+                </c:pt>
+                <c:pt idx="282">
+                  <c:v>0.91215604543686002</c:v>
+                </c:pt>
+                <c:pt idx="283">
+                  <c:v>0.83851355314255005</c:v>
+                </c:pt>
+                <c:pt idx="284">
+                  <c:v>0.83668154478072998</c:v>
+                </c:pt>
+                <c:pt idx="285">
+                  <c:v>0.84020465612410999</c:v>
+                </c:pt>
+                <c:pt idx="286">
+                  <c:v>0.84512382745742998</c:v>
+                </c:pt>
+                <c:pt idx="287">
+                  <c:v>0.84751468896866</c:v>
+                </c:pt>
+                <c:pt idx="288">
+                  <c:v>0.83406174182892001</c:v>
+                </c:pt>
+                <c:pt idx="289">
+                  <c:v>0.82407337427139005</c:v>
+                </c:pt>
+                <c:pt idx="290">
+                  <c:v>0.83111804723740001</c:v>
+                </c:pt>
+                <c:pt idx="291">
+                  <c:v>0.83602833747864003</c:v>
+                </c:pt>
+                <c:pt idx="292">
+                  <c:v>0.84086281061171997</c:v>
+                </c:pt>
+                <c:pt idx="293">
+                  <c:v>0.83916473388671997</c:v>
+                </c:pt>
+                <c:pt idx="294">
+                  <c:v>0.83632296323776001</c:v>
+                </c:pt>
+                <c:pt idx="295">
+                  <c:v>0.84623807668686002</c:v>
+                </c:pt>
+                <c:pt idx="296">
+                  <c:v>0.83919376134872004</c:v>
+                </c:pt>
+                <c:pt idx="297">
+                  <c:v>0.83464425802231001</c:v>
+                </c:pt>
+                <c:pt idx="298">
+                  <c:v>0.82753133773804</c:v>
+                </c:pt>
+                <c:pt idx="299">
+                  <c:v>0.82270199060439997</c:v>
+                </c:pt>
+                <c:pt idx="300">
+                  <c:v>0.84554433822632002</c:v>
+                </c:pt>
+                <c:pt idx="301">
+                  <c:v>0.84141635894775002</c:v>
+                </c:pt>
+                <c:pt idx="302">
+                  <c:v>0.83101433515548995</c:v>
+                </c:pt>
+                <c:pt idx="303">
+                  <c:v>0.81964999437331998</c:v>
+                </c:pt>
+                <c:pt idx="304">
+                  <c:v>0.82724052667617998</c:v>
+                </c:pt>
+                <c:pt idx="305">
+                  <c:v>0.82679855823517001</c:v>
+                </c:pt>
+                <c:pt idx="306">
+                  <c:v>0.83623528480529996</c:v>
+                </c:pt>
+                <c:pt idx="307">
+                  <c:v>0.83518087863921997</c:v>
+                </c:pt>
+                <c:pt idx="308">
+                  <c:v>0.83851826190947998</c:v>
+                </c:pt>
+                <c:pt idx="309">
+                  <c:v>0.8347944021225</c:v>
+                </c:pt>
+                <c:pt idx="310">
+                  <c:v>0.82350498437881003</c:v>
+                </c:pt>
+                <c:pt idx="311">
+                  <c:v>0.83403724431991999</c:v>
+                </c:pt>
+                <c:pt idx="312">
+                  <c:v>0.83304065465927002</c:v>
+                </c:pt>
+                <c:pt idx="313">
+                  <c:v>0.84628772735596003</c:v>
+                </c:pt>
+                <c:pt idx="314">
+                  <c:v>0.83562284708023005</c:v>
+                </c:pt>
+                <c:pt idx="315">
+                  <c:v>0.81994688510894997</c:v>
+                </c:pt>
+                <c:pt idx="316">
+                  <c:v>0.82061314582824996</c:v>
+                </c:pt>
+                <c:pt idx="317">
+                  <c:v>0.85915470123291005</c:v>
+                </c:pt>
+                <c:pt idx="318">
+                  <c:v>0.82212144136429</c:v>
+                </c:pt>
+                <c:pt idx="319">
+                  <c:v>0.82297229766846003</c:v>
+                </c:pt>
+                <c:pt idx="320">
+                  <c:v>0.83879220485687001</c:v>
+                </c:pt>
+                <c:pt idx="321">
+                  <c:v>0.84590673446654996</c:v>
+                </c:pt>
+                <c:pt idx="322">
+                  <c:v>0.82590138912201005</c:v>
+                </c:pt>
+                <c:pt idx="323">
+                  <c:v>0.82157057523726995</c:v>
+                </c:pt>
+                <c:pt idx="324">
+                  <c:v>0.82522600889205999</c:v>
+                </c:pt>
+                <c:pt idx="325">
+                  <c:v>0.80974447727203003</c:v>
+                </c:pt>
+                <c:pt idx="326">
+                  <c:v>0.82366782426833995</c:v>
+                </c:pt>
+                <c:pt idx="327">
+                  <c:v>0.83189153671265004</c:v>
+                </c:pt>
+                <c:pt idx="328">
+                  <c:v>0.81333196163177002</c:v>
+                </c:pt>
+                <c:pt idx="329">
+                  <c:v>0.82548725605010997</c:v>
+                </c:pt>
+                <c:pt idx="330">
+                  <c:v>0.84559226036071999</c:v>
+                </c:pt>
+                <c:pt idx="331">
+                  <c:v>0.86897790431975996</c:v>
+                </c:pt>
+                <c:pt idx="332">
+                  <c:v>0.819380402565</c:v>
+                </c:pt>
+                <c:pt idx="333">
+                  <c:v>0.83459579944610995</c:v>
+                </c:pt>
+                <c:pt idx="334">
+                  <c:v>0.82196551561356002</c:v>
+                </c:pt>
+                <c:pt idx="335">
+                  <c:v>0.87316328287125</c:v>
+                </c:pt>
+                <c:pt idx="336">
+                  <c:v>0.83616644144058005</c:v>
+                </c:pt>
+                <c:pt idx="337">
+                  <c:v>0.82423496246338002</c:v>
+                </c:pt>
+                <c:pt idx="338">
+                  <c:v>0.82280749082564997</c:v>
+                </c:pt>
+                <c:pt idx="339">
+                  <c:v>0.82259279489517001</c:v>
+                </c:pt>
+                <c:pt idx="340">
+                  <c:v>0.82434648275375</c:v>
+                </c:pt>
+                <c:pt idx="341">
+                  <c:v>0.81083095073699996</c:v>
+                </c:pt>
+                <c:pt idx="342">
+                  <c:v>0.84486877918242997</c:v>
+                </c:pt>
+                <c:pt idx="343">
+                  <c:v>0.81432723999023005</c:v>
+                </c:pt>
+                <c:pt idx="344">
+                  <c:v>0.83284890651703003</c:v>
+                </c:pt>
+                <c:pt idx="345">
+                  <c:v>0.81742823123931996</c:v>
+                </c:pt>
+                <c:pt idx="346">
+                  <c:v>0.81731265783310003</c:v>
+                </c:pt>
+                <c:pt idx="347">
+                  <c:v>0.84918153285980003</c:v>
+                </c:pt>
+                <c:pt idx="348">
+                  <c:v>0.82243365049362005</c:v>
+                </c:pt>
+                <c:pt idx="349">
+                  <c:v>0.81880044937134</c:v>
+                </c:pt>
+                <c:pt idx="350">
+                  <c:v>0.80887711048125999</c:v>
+                </c:pt>
+                <c:pt idx="351">
+                  <c:v>0.81836551427840998</c:v>
+                </c:pt>
+                <c:pt idx="352">
+                  <c:v>0.81220930814742998</c:v>
+                </c:pt>
+                <c:pt idx="353">
+                  <c:v>0.81094336509705001</c:v>
+                </c:pt>
+                <c:pt idx="354">
+                  <c:v>0.81937736272812001</c:v>
+                </c:pt>
+                <c:pt idx="355">
+                  <c:v>0.81211084127426003</c:v>
+                </c:pt>
+                <c:pt idx="356">
+                  <c:v>0.81074702739715998</c:v>
+                </c:pt>
+                <c:pt idx="357">
+                  <c:v>0.83721524477005005</c:v>
+                </c:pt>
+                <c:pt idx="358">
+                  <c:v>0.80424153804778997</c:v>
+                </c:pt>
+                <c:pt idx="359">
+                  <c:v>0.82922285795212003</c:v>
+                </c:pt>
+                <c:pt idx="360">
+                  <c:v>0.81352144479751998</c:v>
+                </c:pt>
+                <c:pt idx="361">
+                  <c:v>0.82468611001967995</c:v>
+                </c:pt>
+                <c:pt idx="362">
+                  <c:v>0.83061313629150002</c:v>
+                </c:pt>
+                <c:pt idx="363">
+                  <c:v>0.82189637422562001</c:v>
+                </c:pt>
+                <c:pt idx="364">
+                  <c:v>0.80801904201508001</c:v>
+                </c:pt>
+                <c:pt idx="365">
+                  <c:v>0.81654578447341997</c:v>
+                </c:pt>
+                <c:pt idx="366">
+                  <c:v>0.81075310707091996</c:v>
+                </c:pt>
+                <c:pt idx="367">
+                  <c:v>0.83315718173981002</c:v>
+                </c:pt>
+                <c:pt idx="368">
+                  <c:v>0.83269888162613004</c:v>
+                </c:pt>
+                <c:pt idx="369">
+                  <c:v>0.81201207637786998</c:v>
+                </c:pt>
+                <c:pt idx="370">
+                  <c:v>0.81252104043961004</c:v>
+                </c:pt>
+                <c:pt idx="371">
+                  <c:v>0.81165081262589001</c:v>
+                </c:pt>
+                <c:pt idx="372">
+                  <c:v>0.81462496519089</c:v>
+                </c:pt>
+                <c:pt idx="373">
+                  <c:v>0.81011289358139005</c:v>
+                </c:pt>
+                <c:pt idx="374">
+                  <c:v>0.81940150260925004</c:v>
+                </c:pt>
+                <c:pt idx="375">
+                  <c:v>0.83748716115952004</c:v>
+                </c:pt>
+                <c:pt idx="376">
+                  <c:v>0.80553960800170998</c:v>
+                </c:pt>
+                <c:pt idx="377">
+                  <c:v>0.82455468177794999</c:v>
+                </c:pt>
+                <c:pt idx="378">
+                  <c:v>0.82386416196822998</c:v>
+                </c:pt>
+                <c:pt idx="379">
+                  <c:v>0.80602008104323997</c:v>
+                </c:pt>
+                <c:pt idx="380">
+                  <c:v>0.82869791984558006</c:v>
+                </c:pt>
+                <c:pt idx="381">
+                  <c:v>0.81425291299820002</c:v>
+                </c:pt>
+                <c:pt idx="382">
+                  <c:v>0.82916277647018</c:v>
+                </c:pt>
+                <c:pt idx="383">
+                  <c:v>0.81976675987243997</c:v>
+                </c:pt>
+                <c:pt idx="384">
+                  <c:v>0.81282883882523005</c:v>
+                </c:pt>
+                <c:pt idx="385">
+                  <c:v>0.81261914968491</c:v>
+                </c:pt>
+                <c:pt idx="386">
+                  <c:v>0.83232933282851995</c:v>
+                </c:pt>
+                <c:pt idx="387">
+                  <c:v>0.82245981693268</c:v>
+                </c:pt>
+                <c:pt idx="388">
+                  <c:v>0.81341898441314997</c:v>
+                </c:pt>
+                <c:pt idx="389">
+                  <c:v>0.82340788841248003</c:v>
+                </c:pt>
+                <c:pt idx="390">
+                  <c:v>0.80610525608062999</c:v>
+                </c:pt>
+                <c:pt idx="391">
+                  <c:v>0.82113337516785001</c:v>
+                </c:pt>
+                <c:pt idx="392">
+                  <c:v>0.83404010534285999</c:v>
+                </c:pt>
+                <c:pt idx="393">
+                  <c:v>0.82354027032851995</c:v>
+                </c:pt>
+                <c:pt idx="394">
+                  <c:v>0.82136625051498002</c:v>
+                </c:pt>
+                <c:pt idx="395">
+                  <c:v>0.81991326808928999</c:v>
+                </c:pt>
+                <c:pt idx="396">
+                  <c:v>0.82496845722197998</c:v>
+                </c:pt>
+                <c:pt idx="397">
+                  <c:v>0.81364434957503995</c:v>
+                </c:pt>
+                <c:pt idx="398">
+                  <c:v>0.81416827440261996</c:v>
+                </c:pt>
+                <c:pt idx="399">
+                  <c:v>0.80855172872543002</c:v>
+                </c:pt>
+                <c:pt idx="400">
+                  <c:v>0.80935692787169999</c:v>
+                </c:pt>
+                <c:pt idx="401">
+                  <c:v>0.81813073158264005</c:v>
+                </c:pt>
+                <c:pt idx="402">
+                  <c:v>0.82567191123962003</c:v>
+                </c:pt>
+                <c:pt idx="403">
+                  <c:v>0.81759315729141002</c:v>
+                </c:pt>
+                <c:pt idx="404">
+                  <c:v>0.80647242069243996</c:v>
+                </c:pt>
+                <c:pt idx="405">
+                  <c:v>0.82936882972716996</c:v>
+                </c:pt>
+                <c:pt idx="406">
+                  <c:v>0.84861630201339999</c:v>
+                </c:pt>
+                <c:pt idx="407">
+                  <c:v>0.82698059082030995</c:v>
+                </c:pt>
+                <c:pt idx="408">
+                  <c:v>0.82087016105652</c:v>
+                </c:pt>
+                <c:pt idx="409">
+                  <c:v>0.83076834678650002</c:v>
+                </c:pt>
+                <c:pt idx="410">
+                  <c:v>0.81727558374404996</c:v>
+                </c:pt>
+                <c:pt idx="411">
+                  <c:v>0.81011146306991999</c:v>
+                </c:pt>
+                <c:pt idx="412">
+                  <c:v>0.82939916849135997</c:v>
+                </c:pt>
+                <c:pt idx="413">
+                  <c:v>0.82020854949951005</c:v>
+                </c:pt>
+                <c:pt idx="414">
+                  <c:v>0.80342936515808006</c:v>
+                </c:pt>
+                <c:pt idx="415">
+                  <c:v>0.82582432031631003</c:v>
+                </c:pt>
+                <c:pt idx="416">
+                  <c:v>0.81832706928252996</c:v>
+                </c:pt>
+                <c:pt idx="417">
+                  <c:v>0.80425679683685003</c:v>
+                </c:pt>
+                <c:pt idx="418">
+                  <c:v>0.83443510532378995</c:v>
+                </c:pt>
+                <c:pt idx="419">
+                  <c:v>0.80928689241409002</c:v>
+                </c:pt>
+                <c:pt idx="420">
+                  <c:v>0.80298328399658003</c:v>
+                </c:pt>
+                <c:pt idx="421">
+                  <c:v>0.81347334384918002</c:v>
+                </c:pt>
+                <c:pt idx="422">
+                  <c:v>0.84355348348617998</c:v>
+                </c:pt>
+                <c:pt idx="423">
+                  <c:v>0.80133879184723</c:v>
+                </c:pt>
+                <c:pt idx="424">
+                  <c:v>0.81818604469299006</c:v>
+                </c:pt>
+                <c:pt idx="425">
+                  <c:v>0.80403959751128995</c:v>
+                </c:pt>
+                <c:pt idx="426">
+                  <c:v>0.83542722463607999</c:v>
+                </c:pt>
+                <c:pt idx="427">
+                  <c:v>0.82468074560164994</c:v>
+                </c:pt>
+                <c:pt idx="428">
+                  <c:v>0.82247722148894997</c:v>
+                </c:pt>
+                <c:pt idx="429">
+                  <c:v>0.79824286699295</c:v>
+                </c:pt>
+                <c:pt idx="430">
+                  <c:v>0.81632018089294001</c:v>
+                </c:pt>
+                <c:pt idx="431">
+                  <c:v>0.8116095662117</c:v>
+                </c:pt>
+                <c:pt idx="432">
+                  <c:v>0.81261330842972002</c:v>
+                </c:pt>
+                <c:pt idx="433">
+                  <c:v>0.81270486116409002</c:v>
+                </c:pt>
+                <c:pt idx="434">
+                  <c:v>0.80131781101226995</c:v>
+                </c:pt>
+                <c:pt idx="435">
+                  <c:v>0.80725389719009</c:v>
+                </c:pt>
+                <c:pt idx="436">
+                  <c:v>0.80309289693831998</c:v>
+                </c:pt>
+                <c:pt idx="437">
+                  <c:v>0.82209992408751997</c:v>
+                </c:pt>
+                <c:pt idx="438">
+                  <c:v>0.81542807817458995</c:v>
+                </c:pt>
+                <c:pt idx="439">
+                  <c:v>0.79511225223541004</c:v>
+                </c:pt>
+                <c:pt idx="440">
+                  <c:v>0.81998211145401001</c:v>
+                </c:pt>
+                <c:pt idx="441">
+                  <c:v>0.80489879846572998</c:v>
+                </c:pt>
+                <c:pt idx="442">
+                  <c:v>0.81880164146422996</c:v>
+                </c:pt>
+                <c:pt idx="443">
+                  <c:v>0.81046676635741999</c:v>
+                </c:pt>
+                <c:pt idx="444">
+                  <c:v>0.82145112752913996</c:v>
+                </c:pt>
+                <c:pt idx="445">
+                  <c:v>0.80383062362670998</c:v>
+                </c:pt>
+                <c:pt idx="446">
+                  <c:v>0.81416141986847002</c:v>
+                </c:pt>
+                <c:pt idx="447">
+                  <c:v>0.80727410316466996</c:v>
+                </c:pt>
+                <c:pt idx="448">
+                  <c:v>0.82330298423767001</c:v>
+                </c:pt>
+                <c:pt idx="449">
+                  <c:v>0.84251344203948997</c:v>
+                </c:pt>
+                <c:pt idx="450">
+                  <c:v>0.82280462980269997</c:v>
+                </c:pt>
+                <c:pt idx="451">
+                  <c:v>0.79701656103134</c:v>
+                </c:pt>
+                <c:pt idx="452">
+                  <c:v>0.81838786602019997</c:v>
+                </c:pt>
+                <c:pt idx="453">
+                  <c:v>0.81364607810973999</c:v>
+                </c:pt>
+                <c:pt idx="454">
+                  <c:v>0.79519230127335006</c:v>
+                </c:pt>
+                <c:pt idx="455">
+                  <c:v>0.83571004867554</c:v>
+                </c:pt>
+                <c:pt idx="456">
+                  <c:v>0.82894438505172996</c:v>
+                </c:pt>
+                <c:pt idx="457">
+                  <c:v>0.79855149984359997</c:v>
+                </c:pt>
+                <c:pt idx="458">
+                  <c:v>0.82554876804351995</c:v>
+                </c:pt>
+                <c:pt idx="459">
+                  <c:v>0.80745023488998002</c:v>
+                </c:pt>
+                <c:pt idx="460">
+                  <c:v>0.81707692146301003</c:v>
+                </c:pt>
+                <c:pt idx="461">
+                  <c:v>0.81615245342255005</c:v>
+                </c:pt>
+                <c:pt idx="462">
+                  <c:v>0.80094271898269997</c:v>
+                </c:pt>
+                <c:pt idx="463">
+                  <c:v>0.79809385538100996</c:v>
+                </c:pt>
+                <c:pt idx="464">
+                  <c:v>0.79456216096877996</c:v>
+                </c:pt>
+                <c:pt idx="465">
+                  <c:v>0.81474852561950994</c:v>
+                </c:pt>
+                <c:pt idx="466">
+                  <c:v>0.79263645410537997</c:v>
+                </c:pt>
+                <c:pt idx="467">
+                  <c:v>0.84875398874283003</c:v>
+                </c:pt>
+                <c:pt idx="468">
+                  <c:v>0.79368770122527998</c:v>
+                </c:pt>
+                <c:pt idx="469">
+                  <c:v>0.81878477334975996</c:v>
+                </c:pt>
+                <c:pt idx="470">
+                  <c:v>0.80292946100234996</c:v>
+                </c:pt>
+                <c:pt idx="471">
+                  <c:v>0.80002814531326005</c:v>
+                </c:pt>
+                <c:pt idx="472">
+                  <c:v>0.80471605062484997</c:v>
+                </c:pt>
+                <c:pt idx="473">
+                  <c:v>0.80448311567306996</c:v>
+                </c:pt>
+                <c:pt idx="474">
+                  <c:v>0.78705638647079001</c:v>
+                </c:pt>
+                <c:pt idx="475">
+                  <c:v>0.79762560129166005</c:v>
+                </c:pt>
+                <c:pt idx="476">
+                  <c:v>0.80440235137938998</c:v>
+                </c:pt>
+                <c:pt idx="477">
+                  <c:v>0.79538059234618996</c:v>
+                </c:pt>
+                <c:pt idx="478">
+                  <c:v>0.79580616950989003</c:v>
+                </c:pt>
+                <c:pt idx="479">
+                  <c:v>0.79719620943069003</c:v>
+                </c:pt>
+                <c:pt idx="480">
+                  <c:v>0.80864953994750999</c:v>
+                </c:pt>
+                <c:pt idx="481">
+                  <c:v>0.82079732418060003</c:v>
+                </c:pt>
+                <c:pt idx="482">
+                  <c:v>0.81340885162354004</c:v>
+                </c:pt>
+                <c:pt idx="483">
+                  <c:v>0.81523603200911998</c:v>
+                </c:pt>
+                <c:pt idx="484">
+                  <c:v>0.80798482894896995</c:v>
+                </c:pt>
+                <c:pt idx="485">
+                  <c:v>0.80395346879958995</c:v>
+                </c:pt>
+                <c:pt idx="486">
+                  <c:v>0.79763573408126998</c:v>
+                </c:pt>
+                <c:pt idx="487">
+                  <c:v>0.79667568206786998</c:v>
+                </c:pt>
+                <c:pt idx="488">
+                  <c:v>0.81259393692017001</c:v>
+                </c:pt>
+                <c:pt idx="489">
+                  <c:v>0.80622267723082996</c:v>
+                </c:pt>
+                <c:pt idx="490">
+                  <c:v>0.79248470067978005</c:v>
+                </c:pt>
+                <c:pt idx="491">
+                  <c:v>0.79149520397186002</c:v>
+                </c:pt>
+                <c:pt idx="492">
+                  <c:v>0.80219018459320002</c:v>
+                </c:pt>
+                <c:pt idx="493">
+                  <c:v>0.80572944879532005</c:v>
+                </c:pt>
+                <c:pt idx="494">
+                  <c:v>0.80099326372146995</c:v>
+                </c:pt>
+                <c:pt idx="495">
+                  <c:v>0.79776346683501997</c:v>
+                </c:pt>
+                <c:pt idx="496">
+                  <c:v>0.79864722490311002</c:v>
+                </c:pt>
+                <c:pt idx="497">
+                  <c:v>0.79699456691741999</c:v>
+                </c:pt>
+                <c:pt idx="498">
+                  <c:v>0.79877924919127996</c:v>
+                </c:pt>
+                <c:pt idx="499">
+                  <c:v>0.80940788984298995</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="1"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-B8E3-4FB0-BF49-53BAAB51EEA7}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="603335664"/>
+        <c:axId val="609308064"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="603335664"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+          <c:max val="499"/>
+          <c:min val="0"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="pt-BR" sz="1800" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:sysClr val="windowText" lastClr="000000">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:sysClr>
+                    </a:solidFill>
+                  </a:rPr>
+                  <a:t>Epochs</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="pt-BR"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="pt-BR"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="609308064"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="609308064"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="pt-BR" sz="1800" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:sysClr val="windowText" lastClr="000000">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:sysClr>
+                    </a:solidFill>
+                  </a:rPr>
+                  <a:t>Loss</a:t>
+                </a:r>
+                <a:endParaRPr lang="pt-BR" sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:sysClr val="windowText" lastClr="000000">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:sysClr>
+                  </a:solidFill>
+                </a:endParaRPr>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="pt-BR"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="pt-BR"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="603335664"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1800" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="pt-BR"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="pt-BR"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.78740157499999996" l="0.511811024" r="0.511811024" t="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
 <file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
   <a:schemeClr val="accent1"/>
@@ -13796,6 +20779,86 @@
 </file>
 
 <file path=xl/charts/colors5.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors6.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors7.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
   <a:schemeClr val="accent1"/>
   <a:schemeClr val="accent2"/>
@@ -16415,6 +23478,1038 @@
 </cs:chartStyle>
 </file>
 
+<file path=xl/charts/style6.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="227">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style7.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="227">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
@@ -16595,6 +24690,606 @@
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>67</xdr:row>
+      <xdr:rowOff>402</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>7043</xdr:colOff>
+      <xdr:row>97</xdr:row>
+      <xdr:rowOff>186142</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="7" name="Gráfico 6">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{81CAC506-6FAB-42BB-9674-C48B0AB313E6}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId6"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>608360</xdr:colOff>
+      <xdr:row>67</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>27</xdr:col>
+      <xdr:colOff>7043</xdr:colOff>
+      <xdr:row>98</xdr:row>
+      <xdr:rowOff>9525</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="8" name="Gráfico 7">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8567F142-0940-469C-8ADF-8A0551AC036A}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId7"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>24</xdr:col>
+      <xdr:colOff>369403</xdr:colOff>
+      <xdr:row>75</xdr:row>
+      <xdr:rowOff>178904</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>26</xdr:col>
+      <xdr:colOff>371059</xdr:colOff>
+      <xdr:row>79</xdr:row>
+      <xdr:rowOff>72886</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="9" name="Retângulo: Cantos Arredondados 8">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D60ECA29-0514-44F7-B222-14DB61344731}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="17439860" y="14656904"/>
+          <a:ext cx="1227482" cy="655982"/>
+        </a:xfrm>
+        <a:prstGeom prst="roundRect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="bg2"/>
+        </a:solidFill>
+        <a:ln>
+          <a:solidFill>
+            <a:schemeClr val="tx1">
+              <a:lumMod val="65000"/>
+              <a:lumOff val="35000"/>
+            </a:schemeClr>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="pt-BR" sz="1600" b="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>Validation Loss</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>23</xdr:col>
+      <xdr:colOff>91110</xdr:colOff>
+      <xdr:row>87</xdr:row>
+      <xdr:rowOff>157369</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>25</xdr:col>
+      <xdr:colOff>122583</xdr:colOff>
+      <xdr:row>91</xdr:row>
+      <xdr:rowOff>106015</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="10" name="Retângulo: Cantos Arredondados 9">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BA750D0C-9626-4F48-8E5C-6F8A65156D68}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="16548653" y="16921369"/>
+          <a:ext cx="1257300" cy="710646"/>
+        </a:xfrm>
+        <a:prstGeom prst="roundRect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="bg2"/>
+        </a:solidFill>
+        <a:ln>
+          <a:solidFill>
+            <a:schemeClr val="tx1">
+              <a:lumMod val="65000"/>
+              <a:lumOff val="35000"/>
+            </a:schemeClr>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="pt-BR" sz="1600" b="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>Training Loss </a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>41413</xdr:colOff>
+      <xdr:row>75</xdr:row>
+      <xdr:rowOff>8283</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>429040</xdr:colOff>
+      <xdr:row>77</xdr:row>
+      <xdr:rowOff>64603</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="11" name="Conector de Seta Reta 10">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D53066DF-FD72-4EE1-91B8-CC12F5E2154E}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm flipH="1" flipV="1">
+          <a:off x="7918174" y="14486283"/>
+          <a:ext cx="387627" cy="437320"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="28575">
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="dk1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="dk1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="dk1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>109331</xdr:colOff>
+      <xdr:row>72</xdr:row>
+      <xdr:rowOff>107674</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>74544</xdr:colOff>
+      <xdr:row>76</xdr:row>
+      <xdr:rowOff>117609</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="12" name="Conector de Seta Reta 11">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{624D3974-9C1C-435A-97F2-59B69E86D801}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm flipV="1">
+          <a:off x="11663570" y="14014174"/>
+          <a:ext cx="578126" cy="771935"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="28575">
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="dk1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="dk1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="dk1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>25</xdr:col>
+      <xdr:colOff>82826</xdr:colOff>
+      <xdr:row>84</xdr:row>
+      <xdr:rowOff>82826</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>26</xdr:col>
+      <xdr:colOff>165652</xdr:colOff>
+      <xdr:row>88</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="13" name="Conector de Seta Reta 12">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{554CF366-57EF-4326-8F92-5EA389D6E744}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm flipV="1">
+          <a:off x="17766196" y="16275326"/>
+          <a:ext cx="695739" cy="679174"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="28575">
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="dk1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="dk1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="dk1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>23</xdr:col>
+      <xdr:colOff>455544</xdr:colOff>
+      <xdr:row>79</xdr:row>
+      <xdr:rowOff>56322</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>24</xdr:col>
+      <xdr:colOff>405848</xdr:colOff>
+      <xdr:row>82</xdr:row>
+      <xdr:rowOff>24848</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="14" name="Conector de Seta Reta 13">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0AB3C98B-DAD0-4D26-85E5-C88EA3344A30}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm flipH="1">
+          <a:off x="16913087" y="15296322"/>
+          <a:ext cx="563218" cy="540026"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="28575">
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="dk1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="dk1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="dk1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>140804</xdr:colOff>
+      <xdr:row>76</xdr:row>
+      <xdr:rowOff>91109</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>142460</xdr:colOff>
+      <xdr:row>79</xdr:row>
+      <xdr:rowOff>175591</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="15" name="Retângulo: Cantos Arredondados 14">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CC936680-6047-4E9F-B420-AAEDE076AA6F}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="10469217" y="14759609"/>
+          <a:ext cx="1227482" cy="655982"/>
+        </a:xfrm>
+        <a:prstGeom prst="roundRect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="bg2"/>
+        </a:solidFill>
+        <a:ln>
+          <a:solidFill>
+            <a:schemeClr val="tx1">
+              <a:lumMod val="65000"/>
+              <a:lumOff val="35000"/>
+            </a:schemeClr>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="pt-BR" sz="1600" b="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>Validation Accuracy</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>367747</xdr:colOff>
+      <xdr:row>77</xdr:row>
+      <xdr:rowOff>28160</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>369403</xdr:colOff>
+      <xdr:row>80</xdr:row>
+      <xdr:rowOff>112642</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="16" name="Retângulo: Cantos Arredondados 15">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6ECEC77C-41AB-4A60-BDF2-E445EEFFC4F3}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="8244508" y="14887160"/>
+          <a:ext cx="1227482" cy="655982"/>
+        </a:xfrm>
+        <a:prstGeom prst="roundRect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="bg2"/>
+        </a:solidFill>
+        <a:ln>
+          <a:solidFill>
+            <a:schemeClr val="tx1">
+              <a:lumMod val="65000"/>
+              <a:lumOff val="35000"/>
+            </a:schemeClr>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="pt-BR" sz="1600" b="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>Training Accuracy</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
 </xdr:wsDr>
